--- a/Inventory/Cross_Platform_PL.xlsx
+++ b/Inventory/Cross_Platform_PL.xlsx
@@ -94,7 +94,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -110,6 +110,7 @@
     <xf numFmtId="4" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -475,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L192"/>
+  <dimension ref="A1:L265"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9440,27 +9441,3175 @@
         <v/>
       </c>
     </row>
-    <row r="191"/>
     <row r="192">
-      <c r="D192" s="1" t="inlineStr">
-        <is>
-          <t>TOTALS:</t>
-        </is>
-      </c>
-      <c r="E192" s="3">
-        <f>SUM(E2:E190)</f>
-        <v/>
-      </c>
+      <c r="A192" t="n">
+        <v>191</v>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Goldin</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>2012-13 Upper Deck Exquisite Collection UD Black Signatures #B-MI Michael Jordan Signed Card (#33/75) - PSA GEM MT 10</t>
+        </is>
+      </c>
+      <c r="D192" s="1" t="inlineStr"/>
+      <c r="E192" s="3" t="n">
+        <v>10465</v>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Michael Jordan 2012-13 UD Exquisite Black Signatures Autograph #59/75 BGS 9.5</t>
+        </is>
+      </c>
+      <c r="G192" s="2" t="n">
+        <v>5250</v>
+      </c>
+      <c r="H192" t="n">
+        <v>22</v>
+      </c>
+      <c r="I192" s="9" t="n"/>
       <c r="J192" s="3">
-        <f>SUM(J2:J190)</f>
+        <f>IF(I192&lt;&gt;"",I192,G192)</f>
         <v/>
       </c>
       <c r="K192" s="3">
-        <f>SUM(K2:K190)</f>
+        <f>E192-J192</f>
         <v/>
       </c>
       <c r="L192" s="5">
         <f>IF(J192&gt;0,K192/J192,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>192</v>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Goldin</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>2023-24 Topps Chrome 1972 Topps Autographs Gold Refractor #TA-VW Victor Wembanyama Signed Rookie Card (#04/50) - PSA MINT 9</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr"/>
+      <c r="E193" s="2" t="n">
+        <v>7123.1</v>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>2023-24 Topps Chrome Victor Wembanyama 1972 Auto Gold Refractor RC #4/50 Spurs</t>
+        </is>
+      </c>
+      <c r="G193" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H193" t="n">
+        <v>26</v>
+      </c>
+      <c r="I193" s="9" t="n"/>
+      <c r="J193" s="2">
+        <f>IF(I193&lt;&gt;"",I193,G193)</f>
+        <v/>
+      </c>
+      <c r="K193" s="2">
+        <f>E193-J193</f>
+        <v/>
+      </c>
+      <c r="L193" s="4">
+        <f>IF(J193&gt;0,K193/J193,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>193</v>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Goldin</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>2025-26 Topps Silver Pack '80-81 Chrome Basketball Rookie Autographs Orange Refractor #80CR2-CF Cooper Flagg Signed Rookie Card (#17/25) - PSA MINT 9, PSA/DNA GEM MT 10</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr"/>
+      <c r="E194" s="2" t="n">
+        <v>4427.5</v>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Will Riley 2025 Topps Chrome #80CR2-WR Orange Mojo Refractor Rookie Auto RC /25</t>
+        </is>
+      </c>
+      <c r="G194" s="2" t="n">
+        <v>122.5</v>
+      </c>
+      <c r="H194" t="n">
+        <v>30</v>
+      </c>
+      <c r="I194" s="9" t="n"/>
+      <c r="J194" s="2">
+        <f>IF(I194&lt;&gt;"",I194,G194)</f>
+        <v/>
+      </c>
+      <c r="K194" s="2">
+        <f>E194-J194</f>
+        <v/>
+      </c>
+      <c r="L194" s="4">
+        <f>IF(J194&gt;0,K194/J194,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>194</v>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Goldin</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>2018-19 Panini National Treasures Peerless Signatures #PS-KBR Kobe Bryant Signed Card (#03/25) - BGS MINT 9, Beckett 10</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr"/>
+      <c r="E195" s="2" t="n">
+        <v>4025</v>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>2018 National Treasures Kobe Bryant Peerless Auto #6 /25 BGS 9/10</t>
+        </is>
+      </c>
+      <c r="G195" s="2" t="n">
+        <v>6180</v>
+      </c>
+      <c r="H195" t="n">
+        <v>20</v>
+      </c>
+      <c r="I195" s="9" t="n"/>
+      <c r="J195" s="2">
+        <f>IF(I195&lt;&gt;"",I195,G195)</f>
+        <v/>
+      </c>
+      <c r="K195" s="2">
+        <f>E195-J195</f>
+        <v/>
+      </c>
+      <c r="L195" s="4">
+        <f>IF(J195&gt;0,K195/J195,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>195</v>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Goldin</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>2015-16 Panini Noir Autographs Color Gold #NC-KBR Kobe Bryant Signed Card (#4/5) - PSA EX-MT 6 - Pop 1</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr"/>
+      <c r="E196" s="2" t="n">
+        <v>3795</v>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>KOBE BRYANT 2015-16 PANINI NOIR AUTOGRAPH GOLD INK LAKERS AUTO /5 Q3873</t>
+        </is>
+      </c>
+      <c r="G196" s="2" t="n">
+        <v>3550</v>
+      </c>
+      <c r="H196" t="n">
+        <v>24</v>
+      </c>
+      <c r="I196" s="9" t="n"/>
+      <c r="J196" s="2">
+        <f>IF(I196&lt;&gt;"",I196,G196)</f>
+        <v/>
+      </c>
+      <c r="K196" s="2">
+        <f>E196-J196</f>
+        <v/>
+      </c>
+      <c r="L196" s="4">
+        <f>IF(J196&gt;0,K196/J196,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>196</v>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Goldin</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>2018 Panini Kaboom! #K-NJ Neymar Jr. - PSA GEM MT 10</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr"/>
+      <c r="E197" s="2" t="n">
+        <v>3576.5</v>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>2018 Panini Kaboom Neymar Jr. #NJ PSA 10 GEM MINT Brazil Low POP Rare</t>
+        </is>
+      </c>
+      <c r="G197" s="2" t="n">
+        <v>4000</v>
+      </c>
+      <c r="H197" t="n">
+        <v>17</v>
+      </c>
+      <c r="I197" s="9" t="n"/>
+      <c r="J197" s="2">
+        <f>IF(I197&lt;&gt;"",I197,G197)</f>
+        <v/>
+      </c>
+      <c r="K197" s="2">
+        <f>E197-J197</f>
+        <v/>
+      </c>
+      <c r="L197" s="4">
+        <f>IF(J197&gt;0,K197/J197,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>197</v>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Goldin</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>2003-04 Upper Deck Top Prospects Signs of Success #SS-LJ LeBron James Signed Rookie Card - BGS MINT 9, Beckett 10</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr"/>
+      <c r="E198" s="2" t="n">
+        <v>3047.5</v>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>LeBron James Rookie Card 2003 UD Top Prospects Signs Of Success  BGS 9 Auto 10</t>
+        </is>
+      </c>
+      <c r="G198" s="2" t="n">
+        <v>2800</v>
+      </c>
+      <c r="H198" t="n">
+        <v>17</v>
+      </c>
+      <c r="I198" s="9" t="n"/>
+      <c r="J198" s="2">
+        <f>IF(I198&lt;&gt;"",I198,G198)</f>
+        <v/>
+      </c>
+      <c r="K198" s="2">
+        <f>E198-J198</f>
+        <v/>
+      </c>
+      <c r="L198" s="4">
+        <f>IF(J198&gt;0,K198/J198,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>198</v>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Goldin</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>2025-26 Topps Chrome Future Stars Autographs Green Refractor #FS-CF Cooper Flagg Signed Rookie Card (#43/99) - PSA MINT 9, PSA/DNA GEM MT 10</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr"/>
+      <c r="E199" s="2" t="n">
+        <v>2760</v>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>2025-26 Topps Chrome Cooper Flagg Future Stars Auto Green Refractor RC #/99</t>
+        </is>
+      </c>
+      <c r="G199" s="2" t="n">
+        <v>2234</v>
+      </c>
+      <c r="H199" t="n">
+        <v>26</v>
+      </c>
+      <c r="I199" s="9" t="n"/>
+      <c r="J199" s="2">
+        <f>IF(I199&lt;&gt;"",I199,G199)</f>
+        <v/>
+      </c>
+      <c r="K199" s="2">
+        <f>E199-J199</f>
+        <v/>
+      </c>
+      <c r="L199" s="4">
+        <f>IF(J199&gt;0,K199/J199,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>199</v>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Goldin</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>2023-24 Bowman U Best of 2023 Autograph Geometric Red Refractor #B23-CC Caitlin Clark Signed Rookie Card (#01/10) - PSA MINT 9, PSA/DNA GEM MT 10</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr"/>
+      <c r="E200" s="2" t="n">
+        <v>2645</v>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>2023 Bowman U Best CAITLIN CLARK Geo Red Refractor Auto /10 PSA 9/10 Iowa Fever</t>
+        </is>
+      </c>
+      <c r="G200" s="2" t="n">
+        <v>2700</v>
+      </c>
+      <c r="H200" t="n">
+        <v>24</v>
+      </c>
+      <c r="I200" s="9" t="n"/>
+      <c r="J200" s="2">
+        <f>IF(I200&lt;&gt;"",I200,G200)</f>
+        <v/>
+      </c>
+      <c r="K200" s="2">
+        <f>E200-J200</f>
+        <v/>
+      </c>
+      <c r="L200" s="4">
+        <f>IF(J200&gt;0,K200/J200,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>200</v>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Goldin</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>2020-21 Panini Flawless Draft Gem Signatures Ruby #DG-AEW Anthony Edwards Signed Rookie Card (#15/15) - Panini Encased</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr"/>
+      <c r="E201" s="2" t="n">
+        <v>2601.3</v>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>15/15 ≈1/1 2020-21 Panini Flawless Anthony Edwards Ruby Draft Gem Auto RC Rookie</t>
+        </is>
+      </c>
+      <c r="G201" s="2" t="n">
+        <v>2899</v>
+      </c>
+      <c r="H201" t="n">
+        <v>26</v>
+      </c>
+      <c r="I201" s="9" t="n"/>
+      <c r="J201" s="2">
+        <f>IF(I201&lt;&gt;"",I201,G201)</f>
+        <v/>
+      </c>
+      <c r="K201" s="2">
+        <f>E201-J201</f>
+        <v/>
+      </c>
+      <c r="L201" s="4">
+        <f>IF(J201&gt;0,K201/J201,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>201</v>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Goldin</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>2023-24 Topps Chrome UCC Future Stars Autographs SuperFractor #FSA-KM Kobbie Mainoo Signed Card (#1/1) - PSA NM-MT 8</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr"/>
+      <c r="E202" s="2" t="n">
+        <v>2472.5</v>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>2023-24 Topps Royalty Zach LaVine Regalia Relic Patch Platinum Auto #1/1</t>
+        </is>
+      </c>
+      <c r="G202" s="2" t="n">
+        <v>89.89</v>
+      </c>
+      <c r="H202" t="n">
+        <v>22</v>
+      </c>
+      <c r="I202" s="9" t="n"/>
+      <c r="J202" s="2">
+        <f>IF(I202&lt;&gt;"",I202,G202)</f>
+        <v/>
+      </c>
+      <c r="K202" s="2">
+        <f>E202-J202</f>
+        <v/>
+      </c>
+      <c r="L202" s="4">
+        <f>IF(J202&gt;0,K202/J202,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>202</v>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Goldin</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>2022-23 Bowman U Best of '22 Autographs #BOA-VW Victor Wembanyama Signed Rookie Card - PSA GEM MT 10</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr"/>
+      <c r="E203" s="2" t="n">
+        <v>2472.5</v>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>2022-23 Bowman University - Victor Wembanyama Best of 2022 Auto PSA 10</t>
+        </is>
+      </c>
+      <c r="G203" s="2" t="n">
+        <v>1550</v>
+      </c>
+      <c r="H203" t="n">
+        <v>17</v>
+      </c>
+      <c r="I203" s="9" t="n"/>
+      <c r="J203" s="2">
+        <f>IF(I203&lt;&gt;"",I203,G203)</f>
+        <v/>
+      </c>
+      <c r="K203" s="2">
+        <f>E203-J203</f>
+        <v/>
+      </c>
+      <c r="L203" s="4">
+        <f>IF(J203&gt;0,K203/J203,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>203</v>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Goldin</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>2025-26 Topps Chrome Next Stop Signatures Purple Geometric Refractor #NS-CF Cooper Flagg Signed Rookie Card (#68/75) - PSA MINT 9</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr"/>
+      <c r="E204" s="2" t="n">
+        <v>2375.9</v>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>ESTEVAO WILLIAN 2025-26 TOPPS CHROME GEOMETRIC REFRACTOR ROOKIE #68 Q2723</t>
+        </is>
+      </c>
+      <c r="G204" s="2" t="n">
+        <v>9.380000000000001</v>
+      </c>
+      <c r="H204" t="n">
+        <v>25</v>
+      </c>
+      <c r="I204" s="9" t="n"/>
+      <c r="J204" s="2">
+        <f>IF(I204&lt;&gt;"",I204,G204)</f>
+        <v/>
+      </c>
+      <c r="K204" s="2">
+        <f>E204-J204</f>
+        <v/>
+      </c>
+      <c r="L204" s="4">
+        <f>IF(J204&gt;0,K204/J204,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>204</v>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Goldin</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2023 Bowman Draft Picks &amp; Prospects Autographs Red #DPPA-PS Paul Skenes Signed Rookie Card (#2/5) - PSA MINT 9
+</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr"/>
+      <c r="E205" s="2" t="n">
+        <v>2300</v>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>2023 BOWMAN DRAFT DRAFT PICKS &amp; PROSPECTS AUTO RED PAUL SKENES 2/5 PSA 9</t>
+        </is>
+      </c>
+      <c r="G205" s="2" t="n">
+        <v>1580</v>
+      </c>
+      <c r="H205" t="n">
+        <v>26</v>
+      </c>
+      <c r="I205" s="9" t="n"/>
+      <c r="J205" s="2">
+        <f>IF(I205&lt;&gt;"",I205,G205)</f>
+        <v/>
+      </c>
+      <c r="K205" s="2">
+        <f>E205-J205</f>
+        <v/>
+      </c>
+      <c r="L205" s="4">
+        <f>IF(J205&gt;0,K205/J205,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>205</v>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Goldin</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>2023-24 Topps Chrome UCC Black Lazer Autograph #BLA-LY Lamine Yamal Signed Rookie Card - PSA MINT 9, PSA/DNA GEM MT 10</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr"/>
+      <c r="E206" s="2" t="n">
+        <v>2242.5</v>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>2023 TOPPS CHROME UEFA CLUB COMPETITIONS LAMINE YAMAL BLACK LAZER AUTO ROOKIE RC</t>
+        </is>
+      </c>
+      <c r="G206" s="2" t="n">
+        <v>1525</v>
+      </c>
+      <c r="H206" t="n">
+        <v>23</v>
+      </c>
+      <c r="I206" s="9" t="n"/>
+      <c r="J206" s="2">
+        <f>IF(I206&lt;&gt;"",I206,G206)</f>
+        <v/>
+      </c>
+      <c r="K206" s="2">
+        <f>E206-J206</f>
+        <v/>
+      </c>
+      <c r="L206" s="4">
+        <f>IF(J206&gt;0,K206/J206,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>206</v>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Goldin</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>2020-21 Panini One and One Rookie Jersey Autographs Blue #RJA-AED Anthony Edwards Signed Patch Rookie Card (#26/35) - PSA Authentic, PSA/DNA GEM MT 10</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr"/>
+      <c r="E207" s="2" t="n">
+        <v>2127.5</v>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>2020-21 One And One Anthony Edwards Purple RC Patch RPA /35 PSA 10 Auto POP 2</t>
+        </is>
+      </c>
+      <c r="G207" s="2" t="n">
+        <v>2066</v>
+      </c>
+      <c r="H207" t="n">
+        <v>22</v>
+      </c>
+      <c r="I207" s="9" t="n"/>
+      <c r="J207" s="2">
+        <f>IF(I207&lt;&gt;"",I207,G207)</f>
+        <v/>
+      </c>
+      <c r="K207" s="2">
+        <f>E207-J207</f>
+        <v/>
+      </c>
+      <c r="L207" s="4">
+        <f>IF(J207&gt;0,K207/J207,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>207</v>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Goldin</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2019-20 Panini Flawless Premium Ink #PI-SCY Stephen Curry Signed Card (#01/25) - PSA MINT 9, PSA/DNA GEM MT 10 - Pop 1
+</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr"/>
+      <c r="E208" s="2" t="n">
+        <v>2070</v>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>2019 Panini Flawless Premium Ink Stephen Curry /25 on card auto PSA 9/10 Pop. 2!</t>
+        </is>
+      </c>
+      <c r="G208" s="2" t="n">
+        <v>4150</v>
+      </c>
+      <c r="H208" t="n">
+        <v>24</v>
+      </c>
+      <c r="I208" s="9" t="n"/>
+      <c r="J208" s="2">
+        <f>IF(I208&lt;&gt;"",I208,G208)</f>
+        <v/>
+      </c>
+      <c r="K208" s="2">
+        <f>E208-J208</f>
+        <v/>
+      </c>
+      <c r="L208" s="4">
+        <f>IF(J208&gt;0,K208/J208,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>208</v>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Goldin</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2015-16 Panini National Treasures Clutch Factor Jersey Autograph #CF-SCR Stephen Curry Signed Relic Card (#14/25) - PSA MINT 9 - Pop 4
+</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr"/>
+      <c r="E209" s="2" t="n">
+        <v>2070</v>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>2015-16 National Treasures Stephen Curry Clutch Factor Patch Auto /25 PSA 9 Mint</t>
+        </is>
+      </c>
+      <c r="G209" s="2" t="n">
+        <v>2165</v>
+      </c>
+      <c r="H209" t="n">
+        <v>22</v>
+      </c>
+      <c r="I209" s="9" t="n"/>
+      <c r="J209" s="2">
+        <f>IF(I209&lt;&gt;"",I209,G209)</f>
+        <v/>
+      </c>
+      <c r="K209" s="2">
+        <f>E209-J209</f>
+        <v/>
+      </c>
+      <c r="L209" s="4">
+        <f>IF(J209&gt;0,K209/J209,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>209</v>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Goldin</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>2025 Topps Five Star Golden Graphs Blue #GG-YY Yoshinobu Yamamoto Signed Card (#19/20) - Topps Encased</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr"/>
+      <c r="E210" s="2" t="n">
+        <v>1851.5</v>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>Yoshinobu Yamamoto 2025 Topps Five Star Golden Graphs Auto Blue /20 Dodgers</t>
+        </is>
+      </c>
+      <c r="G210" s="2" t="n">
+        <v>700</v>
+      </c>
+      <c r="H210" t="n">
+        <v>22</v>
+      </c>
+      <c r="I210" s="9" t="n"/>
+      <c r="J210" s="2">
+        <f>IF(I210&lt;&gt;"",I210,G210)</f>
+        <v/>
+      </c>
+      <c r="K210" s="2">
+        <f>E210-J210</f>
+        <v/>
+      </c>
+      <c r="L210" s="4">
+        <f>IF(J210&gt;0,K210/J210,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>210</v>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Goldin</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>2008 Upper Deck SP Rookie Threads SP Dual Threads #TD-BJ Kobe Bryant/Michael Jordan Relic Card - BGS NM-MT+ 8.5</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr"/>
+      <c r="E211" s="2" t="n">
+        <v>1841.15</v>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>2008 Sp Rookie Patch Michael Jordan/Kobe Bryant Dual Game Used BGS 8.5</t>
+        </is>
+      </c>
+      <c r="G211" s="2" t="n">
+        <v>2075</v>
+      </c>
+      <c r="H211" t="n">
+        <v>15</v>
+      </c>
+      <c r="I211" s="9" t="n"/>
+      <c r="J211" s="2">
+        <f>IF(I211&lt;&gt;"",I211,G211)</f>
+        <v/>
+      </c>
+      <c r="K211" s="2">
+        <f>E211-J211</f>
+        <v/>
+      </c>
+      <c r="L211" s="4">
+        <f>IF(J211&gt;0,K211/J211,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>211</v>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Goldin</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2024-25 Panini Flawless All-Star Ink Gold #ANB-LUD Luka Doncic Signed Card (#04/10) - Panini Encased
+</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr"/>
+      <c r="E212" s="2" t="n">
+        <v>1840</v>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>2024-25 Panini Flawless Luka Doncic All-NBA Ink Signatures Auto Gold /10</t>
+        </is>
+      </c>
+      <c r="G212" s="2" t="n">
+        <v>2806</v>
+      </c>
+      <c r="H212" t="n">
+        <v>24</v>
+      </c>
+      <c r="I212" s="9" t="n"/>
+      <c r="J212" s="2">
+        <f>IF(I212&lt;&gt;"",I212,G212)</f>
+        <v/>
+      </c>
+      <c r="K212" s="2">
+        <f>E212-J212</f>
+        <v/>
+      </c>
+      <c r="L212" s="4">
+        <f>IF(J212&gt;0,K212/J212,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>212</v>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Goldin</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>2023-24 Topps Now Autographs #VW-6A Victor Wembanyama Signed Rookie Card (#47/99) - PSA MINT 9</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr"/>
+      <c r="E213" s="2" t="n">
+        <v>1667.5</v>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>2023-2024 Victor Wembanyama Topps Mercury RPA Rookie Patch Auto /99 Prizm RC</t>
+        </is>
+      </c>
+      <c r="G213" s="2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H213" t="n">
+        <v>22</v>
+      </c>
+      <c r="I213" s="9" t="n"/>
+      <c r="J213" s="2">
+        <f>IF(I213&lt;&gt;"",I213,G213)</f>
+        <v/>
+      </c>
+      <c r="K213" s="2">
+        <f>E213-J213</f>
+        <v/>
+      </c>
+      <c r="L213" s="4">
+        <f>IF(J213&gt;0,K213/J213,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>213</v>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Goldin</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>2019 Topps Diamond Icons Autographs Gold #DIA-MT Mike Trout Signed Card (#1/1) - BGS GEM MINT 9.5, Beckett 10 - True Gem</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr"/>
+      <c r="E214" s="2" t="n">
+        <v>1610</v>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>1/1 MIKE TROUT BGS 9.5 2019 TOPPS DIAMOND ICONS DIAMOND ICONS AUTO GOLD 1/1</t>
+        </is>
+      </c>
+      <c r="G214" s="2" t="n">
+        <v>1691</v>
+      </c>
+      <c r="H214" t="n">
+        <v>22</v>
+      </c>
+      <c r="I214" s="9" t="n"/>
+      <c r="J214" s="2">
+        <f>IF(I214&lt;&gt;"",I214,G214)</f>
+        <v/>
+      </c>
+      <c r="K214" s="2">
+        <f>E214-J214</f>
+        <v/>
+      </c>
+      <c r="L214" s="4">
+        <f>IF(J214&gt;0,K214/J214,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>214</v>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Goldin</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>2023-24 Panini Contenders Optic 1986 Tribute Autographs International Jade #86-LKD Luka Doncic Signed Card (#3/5) - Panini Encased</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr"/>
+      <c r="E215" s="2" t="n">
+        <v>1493.85</v>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>2023-24 Contenders Optic Luka Doncic Green Cracked Ice 1986 Tribute Auto /5</t>
+        </is>
+      </c>
+      <c r="G215" s="2" t="n">
+        <v>1733</v>
+      </c>
+      <c r="H215" t="n">
+        <v>22</v>
+      </c>
+      <c r="I215" s="9" t="n"/>
+      <c r="J215" s="2">
+        <f>IF(I215&lt;&gt;"",I215,G215)</f>
+        <v/>
+      </c>
+      <c r="K215" s="2">
+        <f>E215-J215</f>
+        <v/>
+      </c>
+      <c r="L215" s="4">
+        <f>IF(J215&gt;0,K215/J215,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>215</v>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Goldin</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>2020-21 Panini National Treasures Treasured Signatures Bronze #TS-LUD Luka Doncic Signed Card (#25/25) - PSA MINT 9</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr"/>
+      <c r="E216" s="2" t="n">
+        <v>1463.95</v>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>2024-25 Select Luka Doncic Few Signatures Tie-Dye Prizm Auto #25/25 Lakers</t>
+        </is>
+      </c>
+      <c r="G216" s="2" t="n">
+        <v>1025</v>
+      </c>
+      <c r="H216" t="n">
+        <v>23</v>
+      </c>
+      <c r="I216" s="9" t="n"/>
+      <c r="J216" s="2">
+        <f>IF(I216&lt;&gt;"",I216,G216)</f>
+        <v/>
+      </c>
+      <c r="K216" s="2">
+        <f>E216-J216</f>
+        <v/>
+      </c>
+      <c r="L216" s="4">
+        <f>IF(J216&gt;0,K216/J216,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>216</v>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Goldin</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>2024-25 Bowman Chrome U Final Exam Autograph #FEA-CF Cooper Flagg Signed Rookie Card - PSA GEM MT 10</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr"/>
+      <c r="E217" s="2" t="n">
+        <v>1449</v>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>2024 Bowman Chrome U Cooper Flagg COURSE LOAD Rookie Auto #CLA-CF PSA 10 #1 PICK</t>
+        </is>
+      </c>
+      <c r="G217" s="2" t="n">
+        <v>1500</v>
+      </c>
+      <c r="H217" t="n">
+        <v>21</v>
+      </c>
+      <c r="I217" s="9" t="n"/>
+      <c r="J217" s="2">
+        <f>IF(I217&lt;&gt;"",I217,G217)</f>
+        <v/>
+      </c>
+      <c r="K217" s="2">
+        <f>E217-J217</f>
+        <v/>
+      </c>
+      <c r="L217" s="4">
+        <f>IF(J217&gt;0,K217/J217,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>217</v>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Goldin</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>2022-23 Panini Immaculate Collection Scorers Club Signatures #SCS-LUD Luka Doncic Signed Card (#23/25) - PSA MINT 9</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr"/>
+      <c r="E218" s="2" t="n">
+        <v>1392.65</v>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>2022 PANINI IMMACULATE COLLECTION LUKA DONCIC SCORERS CLUB AUTO /25 MINT PSA 9</t>
+        </is>
+      </c>
+      <c r="G218" s="2" t="n">
+        <v>1850</v>
+      </c>
+      <c r="H218" t="n">
+        <v>22</v>
+      </c>
+      <c r="I218" s="9" t="n"/>
+      <c r="J218" s="2">
+        <f>IF(I218&lt;&gt;"",I218,G218)</f>
+        <v/>
+      </c>
+      <c r="K218" s="2">
+        <f>E218-J218</f>
+        <v/>
+      </c>
+      <c r="L218" s="4">
+        <f>IF(J218&gt;0,K218/J218,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>218</v>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Goldin</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>2021-22 Topps Chrome PSG Autograph Wave Refractor #AU-KM Kylian Mbappe Signed Card (#41/50) - PSA MINT 9</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr"/>
+      <c r="E219" s="2" t="n">
+        <v>1389.2</v>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>2021-22 Topps Chrome Paris Saint-Germain KYLIAN MBAPPE 41/50 Auto Wave Ref PSA 9</t>
+        </is>
+      </c>
+      <c r="G219" s="2" t="n">
+        <v>1675</v>
+      </c>
+      <c r="H219" t="n">
+        <v>22</v>
+      </c>
+      <c r="I219" s="9" t="n"/>
+      <c r="J219" s="2">
+        <f>IF(I219&lt;&gt;"",I219,G219)</f>
+        <v/>
+      </c>
+      <c r="K219" s="2">
+        <f>E219-J219</f>
+        <v/>
+      </c>
+      <c r="L219" s="4">
+        <f>IF(J219&gt;0,K219/J219,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>219</v>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Goldin</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>2014-15 Panini Flawless Association Autographs Emerald #AA-GA Giannis Antetokounmpo Signed Card (#1/5) - PSA NM 7</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr"/>
+      <c r="E220" s="2" t="n">
+        <v>1151.15</v>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>2014 Panini National Treasures Giannis Antetokounmpo Association Autograph # 1/5</t>
+        </is>
+      </c>
+      <c r="G220" s="2" t="n">
+        <v>1634</v>
+      </c>
+      <c r="H220" t="n">
+        <v>20</v>
+      </c>
+      <c r="I220" s="9" t="n"/>
+      <c r="J220" s="2">
+        <f>IF(I220&lt;&gt;"",I220,G220)</f>
+        <v/>
+      </c>
+      <c r="K220" s="2">
+        <f>E220-J220</f>
+        <v/>
+      </c>
+      <c r="L220" s="4">
+        <f>IF(J220&gt;0,K220/J220,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>220</v>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Goldin</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>2023-24 Topps Finest Masters Autograph Red/Black Vapor Geometric Refractor #MA-SC Stephen Curry Signed Card (#01/10) - Topps Sealed</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr"/>
+      <c r="E221" s="2" t="n">
+        <v>1150</v>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>2023/24 TOPPS FINEST MASTERS STEPHEN CURRY ON CARD AUTO RED VAPOR 01/10  🦄</t>
+        </is>
+      </c>
+      <c r="G221" s="2" t="n">
+        <v>1395</v>
+      </c>
+      <c r="H221" t="n">
+        <v>21</v>
+      </c>
+      <c r="I221" s="9" t="n"/>
+      <c r="J221" s="2">
+        <f>IF(I221&lt;&gt;"",I221,G221)</f>
+        <v/>
+      </c>
+      <c r="K221" s="2">
+        <f>E221-J221</f>
+        <v/>
+      </c>
+      <c r="L221" s="4">
+        <f>IF(J221&gt;0,K221/J221,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>221</v>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Goldin</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>2022-23 Panini Noir Autographed Prime Black and White #ANB-LUD Luka Doncic Signed Card (#17/25) - Panini Encased</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr"/>
+      <c r="E222" s="2" t="n">
+        <v>1150</v>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>2018 PANINI SPECTRA RISING STAR NEON PINK #17 LUKA DONCIC RC /25 BGS 8.5 AUTO 10</t>
+        </is>
+      </c>
+      <c r="G222" s="2" t="n">
+        <v>1875</v>
+      </c>
+      <c r="H222" t="n">
+        <v>25</v>
+      </c>
+      <c r="I222" s="9" t="n"/>
+      <c r="J222" s="2">
+        <f>IF(I222&lt;&gt;"",I222,G222)</f>
+        <v/>
+      </c>
+      <c r="K222" s="2">
+        <f>E222-J222</f>
+        <v/>
+      </c>
+      <c r="L222" s="4">
+        <f>IF(J222&gt;0,K222/J222,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>222</v>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Goldin</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2024-25 Bowman's Best University Prospect Jumbo Relic Autographs Gold Geometric Refractor #PJRA-CF Cooper Flagg Signed Relic Rookie Card (#38/50) - BGS NM-MT+ 8.5, Beckett 10
+</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr"/>
+      <c r="E223" s="2" t="n">
+        <v>1150</v>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>2025 BOWMAN MEGA BOX CHROME PROSPECTS GOLD REFRACTOR #38 LUIS PENA 34/50 PSA 10</t>
+        </is>
+      </c>
+      <c r="G223" s="2" t="n">
+        <v>275</v>
+      </c>
+      <c r="H223" t="n">
+        <v>21</v>
+      </c>
+      <c r="I223" s="9" t="n"/>
+      <c r="J223" s="2">
+        <f>IF(I223&lt;&gt;"",I223,G223)</f>
+        <v/>
+      </c>
+      <c r="K223" s="2">
+        <f>E223-J223</f>
+        <v/>
+      </c>
+      <c r="L223" s="4">
+        <f>IF(J223&gt;0,K223/J223,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>223</v>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Goldin</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>2020-21 Panini National Treasures Rookie Private Signings Association #PSA-AED Anthony Edwards Signed Rookie Card - PSA MINT 9 - Pop 4</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr"/>
+      <c r="E224" s="2" t="n">
+        <v>1150</v>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>Anthony Edwards 2020 Panini Select Red Rookie Jersey Auto RPA Mint 9 Low Pop</t>
+        </is>
+      </c>
+      <c r="G224" s="2" t="n">
+        <v>750</v>
+      </c>
+      <c r="H224" t="n">
+        <v>17</v>
+      </c>
+      <c r="I224" s="9" t="n"/>
+      <c r="J224" s="2">
+        <f>IF(I224&lt;&gt;"",I224,G224)</f>
+        <v/>
+      </c>
+      <c r="K224" s="2">
+        <f>E224-J224</f>
+        <v/>
+      </c>
+      <c r="L224" s="4">
+        <f>IF(J224&gt;0,K224/J224,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>224</v>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Goldin</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>2019-20 Panini One and One First-Team Signatures #FT-SCY Stephen Curry Signed Card (#08/25) - BGS MINT 9, Beckett 10 - Pop 3</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr"/>
+      <c r="E225" s="2" t="n">
+        <v>1122.4</v>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>2019-20 Panini One And One Stephen Curry First Team Signatures Auto /25 BGS 9/10</t>
+        </is>
+      </c>
+      <c r="G225" s="2" t="n">
+        <v>1713.99</v>
+      </c>
+      <c r="H225" t="n">
+        <v>22</v>
+      </c>
+      <c r="I225" s="9" t="n"/>
+      <c r="J225" s="2">
+        <f>IF(I225&lt;&gt;"",I225,G225)</f>
+        <v/>
+      </c>
+      <c r="K225" s="2">
+        <f>E225-J225</f>
+        <v/>
+      </c>
+      <c r="L225" s="4">
+        <f>IF(J225&gt;0,K225/J225,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>225</v>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Goldin</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>2024-25 Topps Regalia Relic Signatures #RRS-SC Stephen Curry Signed Game-Used Patch Card (#03/15) - Topps Encased</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr"/>
+      <c r="E226" s="2" t="n">
+        <v>1104</v>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>2024 Topps Now MLS Stephen Curry/Lionel Messi #128 Night PSA 10 GEM MT &amp;03228</t>
+        </is>
+      </c>
+      <c r="G226" s="2" t="n">
+        <v>185</v>
+      </c>
+      <c r="H226" t="n">
+        <v>15</v>
+      </c>
+      <c r="I226" s="9" t="n"/>
+      <c r="J226" s="2">
+        <f>IF(I226&lt;&gt;"",I226,G226)</f>
+        <v/>
+      </c>
+      <c r="K226" s="2">
+        <f>E226-J226</f>
+        <v/>
+      </c>
+      <c r="L226" s="4">
+        <f>IF(J226&gt;0,K226/J226,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>226</v>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Goldin</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>2020-21 Panini One and One Rookie Dual Jersey Autograph #RDJ-AED Anthony Edwards Signed Relic Rookie Card (#90/99) - PSA MINT 9, PSA/DNA GEM MT 10</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr"/>
+      <c r="E227" s="2" t="n">
+        <v>1092.5</v>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>2020-21 One And One Anthony Edwards RC Dual Jersey Patch Auto RJA /99 PSA 9/10</t>
+        </is>
+      </c>
+      <c r="G227" s="2" t="n">
+        <v>1854</v>
+      </c>
+      <c r="H227" t="n">
+        <v>20</v>
+      </c>
+      <c r="I227" s="9" t="n"/>
+      <c r="J227" s="2">
+        <f>IF(I227&lt;&gt;"",I227,G227)</f>
+        <v/>
+      </c>
+      <c r="K227" s="2">
+        <f>E227-J227</f>
+        <v/>
+      </c>
+      <c r="L227" s="4">
+        <f>IF(J227&gt;0,K227/J227,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>227</v>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Goldin</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>1995-96 Upper Deck 23k Gold 50,000 Print Run Michael Jordan (#12516/50000) - PSA GEM MT 10</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr"/>
+      <c r="E228" s="2" t="n">
+        <v>977.5</v>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>POP 12 PSA 10 Michael Jordan 1995 Upper Deck 23k Gold MJ 7% Gem Rate #'d WOW!</t>
+        </is>
+      </c>
+      <c r="G228" s="2" t="n">
+        <v>1750</v>
+      </c>
+      <c r="H228" t="n">
+        <v>17</v>
+      </c>
+      <c r="I228" s="9" t="n"/>
+      <c r="J228" s="2">
+        <f>IF(I228&lt;&gt;"",I228,G228)</f>
+        <v/>
+      </c>
+      <c r="K228" s="2">
+        <f>E228-J228</f>
+        <v/>
+      </c>
+      <c r="L228" s="4">
+        <f>IF(J228&gt;0,K228/J228,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>228</v>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Goldin</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>2020-21 Panini Contenders Optic Veteran Seasons Ticket Autograph Orange #VT-JTA Jayson Tatum Signed Card (#06/15) - PSA GEM MT 10, PSA/DNA GEM MT 10</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr"/>
+      <c r="E229" s="2" t="n">
+        <v>874</v>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>2020-21 Contenders Optic Jayson Tatum Veteran Auto Orange /15 PSA 10 AUTO 10</t>
+        </is>
+      </c>
+      <c r="G229" s="2" t="n">
+        <v>933</v>
+      </c>
+      <c r="H229" t="n">
+        <v>24</v>
+      </c>
+      <c r="I229" s="9" t="n"/>
+      <c r="J229" s="2">
+        <f>IF(I229&lt;&gt;"",I229,G229)</f>
+        <v/>
+      </c>
+      <c r="K229" s="2">
+        <f>E229-J229</f>
+        <v/>
+      </c>
+      <c r="L229" s="4">
+        <f>IF(J229&gt;0,K229/J229,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>229</v>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Goldin</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>2022-23 Panini One And One Precision Rookie Jersey Autographs Ruby '25 Black Box #PRJ-PB5 Paolo Banchero Signed Patch Rookie Card (#1/1) - Panini Encased</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr"/>
+      <c r="E230" s="2" t="n">
+        <v>868.25</v>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>PAOLO BANCHERO 2022-23 PANINI ONE &amp; ONE BLACK BX ROOKIE PATCH AUTO RPA RC 1/1</t>
+        </is>
+      </c>
+      <c r="G230" s="2" t="n">
+        <v>1698</v>
+      </c>
+      <c r="H230" t="n">
+        <v>26</v>
+      </c>
+      <c r="I230" s="9" t="n"/>
+      <c r="J230" s="2">
+        <f>IF(I230&lt;&gt;"",I230,G230)</f>
+        <v/>
+      </c>
+      <c r="K230" s="2">
+        <f>E230-J230</f>
+        <v/>
+      </c>
+      <c r="L230" s="4">
+        <f>IF(J230&gt;0,K230/J230,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>230</v>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Goldin</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>2021-22 Panini Donruss Optic Fast Break Signatures Gold #FB-AEW Anthony Edwards Signed Card (#04/10) - PSA MINT 9 - Pop 3</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr"/>
+      <c r="E231" s="2" t="n">
+        <v>868.25</v>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>2021-2022 Optic ANTHONY EDWARDS Gold Fast Break Auto /10 PSA 9 Timberwolves</t>
+        </is>
+      </c>
+      <c r="G231" s="2" t="n">
+        <v>1050</v>
+      </c>
+      <c r="H231" t="n">
+        <v>20</v>
+      </c>
+      <c r="I231" s="9" t="n"/>
+      <c r="J231" s="2">
+        <f>IF(I231&lt;&gt;"",I231,G231)</f>
+        <v/>
+      </c>
+      <c r="K231" s="2">
+        <f>E231-J231</f>
+        <v/>
+      </c>
+      <c r="L231" s="4">
+        <f>IF(J231&gt;0,K231/J231,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>231</v>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Goldin</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2022 Leaf Decadence Octet Autographs #O-03 Curry/Iverson/Johnson/Lillard/West/Frazier/Dantley/Erving Multi-Signed Card (#1/4) - Leaf Encased
+</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr"/>
+      <c r="E232" s="2" t="n">
+        <v>862.5</v>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>CURRY IVERSON MAGIC ERVING LILLARD WEST - 2022 Leaf Decadence OCTET 8 AUTO /4</t>
+        </is>
+      </c>
+      <c r="G232" s="2" t="n">
+        <v>880</v>
+      </c>
+      <c r="H232" t="n">
+        <v>20</v>
+      </c>
+      <c r="I232" s="9" t="n"/>
+      <c r="J232" s="2">
+        <f>IF(I232&lt;&gt;"",I232,G232)</f>
+        <v/>
+      </c>
+      <c r="K232" s="2">
+        <f>E232-J232</f>
+        <v/>
+      </c>
+      <c r="L232" s="4">
+        <f>IF(J232&gt;0,K232/J232,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>232</v>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Goldin</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>2024-25 Panini One and One Logoman #LM-CDY Cody Williams Logoman Patch Rookie Card (#2/5) - Panini Encased</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr"/>
+      <c r="E233" s="2" t="n">
+        <v>833.75</v>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>2024-25 Panini One And One Cody Williams Logoman Patch Jersey RC Rookie Jazz /5</t>
+        </is>
+      </c>
+      <c r="G233" s="2" t="n">
+        <v>810.87</v>
+      </c>
+      <c r="H233" t="n">
+        <v>26</v>
+      </c>
+      <c r="I233" s="9" t="n"/>
+      <c r="J233" s="2">
+        <f>IF(I233&lt;&gt;"",I233,G233)</f>
+        <v/>
+      </c>
+      <c r="K233" s="2">
+        <f>E233-J233</f>
+        <v/>
+      </c>
+      <c r="L233" s="4">
+        <f>IF(J233&gt;0,K233/J233,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>233</v>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Goldin</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>2023-24 Bowman Chrome U 2007-08 Bowman Gold #07B-22 Caitlin Clark Rookie Card (#32/50) - PSA GEM MT 10</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr"/>
+      <c r="E234" s="2" t="n">
+        <v>829.15</v>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>2023 BOWMAN UNIVERSITY CHROME 2007-08 BOWMAN #07B22 CAITLIN CLARK 32/50 PSA 10</t>
+        </is>
+      </c>
+      <c r="G234" s="2" t="n">
+        <v>811</v>
+      </c>
+      <c r="H234" t="n">
+        <v>30</v>
+      </c>
+      <c r="I234" s="9" t="n"/>
+      <c r="J234" s="2">
+        <f>IF(I234&lt;&gt;"",I234,G234)</f>
+        <v/>
+      </c>
+      <c r="K234" s="2">
+        <f>E234-J234</f>
+        <v/>
+      </c>
+      <c r="L234" s="4">
+        <f>IF(J234&gt;0,K234/J234,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>234</v>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Goldin</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>2017-18 Panini Noir Rookie Patch Autograph (RPA) Black and White #303 Jayson Tatum Signed Patch Rookie Card (#05/99) - Panini Encased</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr"/>
+      <c r="E235" s="2" t="n">
+        <v>805</v>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>2017-18 Panini Noir Jayson Tatum RC Patch Auto Black &amp; White /99 RPA</t>
+        </is>
+      </c>
+      <c r="G235" s="2" t="n">
+        <v>831</v>
+      </c>
+      <c r="H235" t="n">
+        <v>26</v>
+      </c>
+      <c r="I235" s="9" t="n"/>
+      <c r="J235" s="2">
+        <f>IF(I235&lt;&gt;"",I235,G235)</f>
+        <v/>
+      </c>
+      <c r="K235" s="2">
+        <f>E235-J235</f>
+        <v/>
+      </c>
+      <c r="L235" s="4">
+        <f>IF(J235&gt;0,K235/J235,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>235</v>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Goldin</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>2017-18 Panini Flawless Momentous Autographs Gold #MA-GA Giannis Antetokounmpo Signed Card (#04/10) - Panini Encased</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr"/>
+      <c r="E236" s="2" t="n">
+        <v>776.25</v>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>2017-18 Panini Flawless Giannis Antetokounmpo Momentous Auto Gold /10</t>
+        </is>
+      </c>
+      <c r="G236" s="2" t="n">
+        <v>1125</v>
+      </c>
+      <c r="H236" t="n">
+        <v>26</v>
+      </c>
+      <c r="I236" s="9" t="n"/>
+      <c r="J236" s="2">
+        <f>IF(I236&lt;&gt;"",I236,G236)</f>
+        <v/>
+      </c>
+      <c r="K236" s="2">
+        <f>E236-J236</f>
+        <v/>
+      </c>
+      <c r="L236" s="4">
+        <f>IF(J236&gt;0,K236/J236,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>236</v>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Goldin</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>2017-18 Panini Flawless Premium Ink Signatures #PI-GA Giannis Antetokounmpo Signed Card (#12/25) - BGS GEM MINT 9.5, Beckett 10</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr"/>
+      <c r="E237" s="2" t="n">
+        <v>776.25</v>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>Giannis Antetokounmpo 2017 Panini Flawless Premium Ink Auto 12/25 BGS 9.5/10</t>
+        </is>
+      </c>
+      <c r="G237" s="2" t="n">
+        <v>1357</v>
+      </c>
+      <c r="H237" t="n">
+        <v>24</v>
+      </c>
+      <c r="I237" s="9" t="n"/>
+      <c r="J237" s="2">
+        <f>IF(I237&lt;&gt;"",I237,G237)</f>
+        <v/>
+      </c>
+      <c r="K237" s="2">
+        <f>E237-J237</f>
+        <v/>
+      </c>
+      <c r="L237" s="4">
+        <f>IF(J237&gt;0,K237/J237,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>237</v>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Goldin</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>2022-23 Panini Flawless Excellence Signatures '25 Black Box #ES-CHG Chet Holmgren Signed Rookie Card (#1/1) - Panini Encased</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr"/>
+      <c r="E238" s="2" t="n">
+        <v>776.25</v>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>Chet Holmgren 2022-23 Panini Flawless Gold Rookie Auto RC Card Black Box 1/1</t>
+        </is>
+      </c>
+      <c r="G238" s="2" t="n">
+        <v>1551</v>
+      </c>
+      <c r="H238" t="n">
+        <v>24</v>
+      </c>
+      <c r="I238" s="9" t="n"/>
+      <c r="J238" s="2">
+        <f>IF(I238&lt;&gt;"",I238,G238)</f>
+        <v/>
+      </c>
+      <c r="K238" s="2">
+        <f>E238-J238</f>
+        <v/>
+      </c>
+      <c r="L238" s="4">
+        <f>IF(J238&gt;0,K238/J238,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>238</v>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Goldin</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>2025-26 Topps All Kings #AK-4 Giannis Antetokounmpo - PSA MINT 9</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr"/>
+      <c r="E239" s="2" t="n">
+        <v>707.25</v>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>2025-26 Topps Chrome Giannis Antetokounmpo Activators GOLD REFRACTOR 49/50</t>
+        </is>
+      </c>
+      <c r="G239" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="H239" t="n">
+        <v>15</v>
+      </c>
+      <c r="I239" s="9" t="n"/>
+      <c r="J239" s="2">
+        <f>IF(I239&lt;&gt;"",I239,G239)</f>
+        <v/>
+      </c>
+      <c r="K239" s="2">
+        <f>E239-J239</f>
+        <v/>
+      </c>
+      <c r="L239" s="4">
+        <f>IF(J239&gt;0,K239/J239,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>239</v>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Goldin</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2023-24 Topps Chrome Sapphire Autograph Red Refractor #CG-TM Tyrese Maxey Signed Card (#5/5) - PSA GEM MT 10 - Pop 1 </t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr"/>
+      <c r="E240" s="2" t="n">
+        <v>633.65</v>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>2023 TOPPS CHROME SAPPHIRE ED TOPPS CHROME AUTOS RED TYRESE MAXEY 5/5 PSA 10</t>
+        </is>
+      </c>
+      <c r="G240" s="2" t="n">
+        <v>260</v>
+      </c>
+      <c r="H240" t="n">
+        <v>26</v>
+      </c>
+      <c r="I240" s="9" t="n"/>
+      <c r="J240" s="2">
+        <f>IF(I240&lt;&gt;"",I240,G240)</f>
+        <v/>
+      </c>
+      <c r="K240" s="2">
+        <f>E240-J240</f>
+        <v/>
+      </c>
+      <c r="L240" s="4">
+        <f>IF(J240&gt;0,K240/J240,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>240</v>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Goldin</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>2023-24 Panini Immaculate Collection Immaculate Legends #ILE-YM Yao Ming Signed Card (#31/49) - Panini Encased</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr"/>
+      <c r="E241" s="2" t="n">
+        <v>575</v>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>2023-24 Panini Immaculate Legends Yao Ming On Card Auto /49 Houston Rockets HOF</t>
+        </is>
+      </c>
+      <c r="G241" s="2" t="n">
+        <v>436.5</v>
+      </c>
+      <c r="H241" t="n">
+        <v>20</v>
+      </c>
+      <c r="I241" s="9" t="n"/>
+      <c r="J241" s="2">
+        <f>IF(I241&lt;&gt;"",I241,G241)</f>
+        <v/>
+      </c>
+      <c r="K241" s="2">
+        <f>E241-J241</f>
+        <v/>
+      </c>
+      <c r="L241" s="4">
+        <f>IF(J241&gt;0,K241/J241,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>241</v>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Goldin</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>2019-20 Panini Opulence City of Gold Signatures Gold #CG-NJ Nikola Jokic Signed Card (#10/25) - Panini Encased</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr"/>
+      <c r="E242" s="2" t="n">
+        <v>575</v>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>2019-20 Nikola Jokic Opulence City Of Gold On Card Auto /25 Sealed SSP Ebay 1/1</t>
+        </is>
+      </c>
+      <c r="G242" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="H242" t="n">
+        <v>18</v>
+      </c>
+      <c r="I242" s="9" t="n"/>
+      <c r="J242" s="2">
+        <f>IF(I242&lt;&gt;"",I242,G242)</f>
+        <v/>
+      </c>
+      <c r="K242" s="2">
+        <f>E242-J242</f>
+        <v/>
+      </c>
+      <c r="L242" s="4">
+        <f>IF(J242&gt;0,K242/J242,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>242</v>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Goldin</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>2011-2012 Upper Deck Exquisite Collection Personal Touch #PTC-VC Vince Carter Signed Card (#01/30) - BGS MINT 9, Beckett 10</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr"/>
+      <c r="E243" s="2" t="n">
+        <v>575</v>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>2011-12 UD Exquisite Collection VINCE CARTER Auto #01/30 BGS 9 Personal Touch</t>
+        </is>
+      </c>
+      <c r="G243" s="2" t="n">
+        <v>275</v>
+      </c>
+      <c r="H243" t="n">
+        <v>28</v>
+      </c>
+      <c r="I243" s="9" t="n"/>
+      <c r="J243" s="2">
+        <f>IF(I243&lt;&gt;"",I243,G243)</f>
+        <v/>
+      </c>
+      <c r="K243" s="2">
+        <f>E243-J243</f>
+        <v/>
+      </c>
+      <c r="L243" s="4">
+        <f>IF(J243&gt;0,K243/J243,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>243</v>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Goldin</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>2025 Topps Chrome Black Autograph Gold Refractor #CBA-PS Paul Skenes Signed Card (#05/50) - PSA NM-MT+ 8.5, PSA/DNA GEM MT 10</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr"/>
+      <c r="E244" s="2" t="n">
+        <v>517.5</v>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>Paul Skenes 2025 Topps Chrome Black #PS Auto Gold Refractor 05/50</t>
+        </is>
+      </c>
+      <c r="G244" s="2" t="n">
+        <v>420</v>
+      </c>
+      <c r="H244" t="n">
+        <v>28</v>
+      </c>
+      <c r="I244" s="9" t="n"/>
+      <c r="J244" s="2">
+        <f>IF(I244&lt;&gt;"",I244,G244)</f>
+        <v/>
+      </c>
+      <c r="K244" s="2">
+        <f>E244-J244</f>
+        <v/>
+      </c>
+      <c r="L244" s="4">
+        <f>IF(J244&gt;0,K244/J244,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>244</v>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Goldin</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>2019-20 Panini One and One First-Team Signatures Blue #FT-FJK Nikola Jokic Signed Card (#08/49) - Panini Encased</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr"/>
+      <c r="E245" s="2" t="n">
+        <v>517.5</v>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>2019-20 Panini One And One Nikola Jokic #FT-NJK First Team Signatures Auto /49</t>
+        </is>
+      </c>
+      <c r="G245" s="2" t="n">
+        <v>369</v>
+      </c>
+      <c r="H245" t="n">
+        <v>22</v>
+      </c>
+      <c r="I245" s="9" t="n"/>
+      <c r="J245" s="2">
+        <f>IF(I245&lt;&gt;"",I245,G245)</f>
+        <v/>
+      </c>
+      <c r="K245" s="2">
+        <f>E245-J245</f>
+        <v/>
+      </c>
+      <c r="L245" s="4">
+        <f>IF(J245&gt;0,K245/J245,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>245</v>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Goldin</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>2021-22 Panini Chronicles Hometown Heroes Gold #HHR-CCU Cade Cunningham Signed Rookie Card (#01/10) - Panini Encased</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr"/>
+      <c r="E246" s="2" t="n">
+        <v>494.5</v>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>2021-22 Panini Hometown Heroes Cade Cunningham Rookie Auto Gold 1/10! Sealed!</t>
+        </is>
+      </c>
+      <c r="G246" s="2" t="n">
+        <v>425</v>
+      </c>
+      <c r="H246" t="n">
+        <v>22</v>
+      </c>
+      <c r="I246" s="9" t="n"/>
+      <c r="J246" s="2">
+        <f>IF(I246&lt;&gt;"",I246,G246)</f>
+        <v/>
+      </c>
+      <c r="K246" s="2">
+        <f>E246-J246</f>
+        <v/>
+      </c>
+      <c r="L246" s="4">
+        <f>IF(J246&gt;0,K246/J246,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>246</v>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Goldin</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>2023 Topps NPB Chrome Topps 2001 Orange Refractor #01-1 Yoshinobu Yamamoto (#01/25) - PSA MINT 9</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr"/>
+      <c r="E247" s="2" t="n">
+        <v>488.75</v>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>2023 Yoshinobu Yamamoto 1/25 Topps NPB Chrome Orange Refractor #O1-1 PSA9 MINT</t>
+        </is>
+      </c>
+      <c r="G247" s="2" t="n">
+        <v>552.49</v>
+      </c>
+      <c r="H247" t="n">
+        <v>24</v>
+      </c>
+      <c r="I247" s="9" t="n"/>
+      <c r="J247" s="2">
+        <f>IF(I247&lt;&gt;"",I247,G247)</f>
+        <v/>
+      </c>
+      <c r="K247" s="2">
+        <f>E247-J247</f>
+        <v/>
+      </c>
+      <c r="L247" s="4">
+        <f>IF(J247&gt;0,K247/J247,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>247</v>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Goldin</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>2025-26 Topps Chrome Rock Stars #RS-17 Dylan Harper Rookie Card - PSA GEM MT 10</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr"/>
+      <c r="E248" s="2" t="n">
+        <v>485.3</v>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>2025-26 Topps Chrome - Autograph Issue Rookies Dylan Harper #TAUR2-DH (AU, RC)</t>
+        </is>
+      </c>
+      <c r="G248" s="2" t="n">
+        <v>275</v>
+      </c>
+      <c r="H248" t="n">
+        <v>19</v>
+      </c>
+      <c r="I248" s="9" t="n"/>
+      <c r="J248" s="2">
+        <f>IF(I248&lt;&gt;"",I248,G248)</f>
+        <v/>
+      </c>
+      <c r="K248" s="2">
+        <f>E248-J248</f>
+        <v/>
+      </c>
+      <c r="L248" s="4">
+        <f>IF(J248&gt;0,K248/J248,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>248</v>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Goldin</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>2019-20 Panini Prizm Sensational Swatches Prizms Orange Ice #SS-SCU Stephen Curry Signed Relic Card - BGS Authentic Sticker Autograph</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr"/>
+      <c r="E249" s="2" t="n">
+        <v>485.3</v>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>Stephen Curry 2019 Panini National #52 Galactic Windows /5 SSP PSA 10 GEM MINT</t>
+        </is>
+      </c>
+      <c r="G249" s="2" t="n">
+        <v>625</v>
+      </c>
+      <c r="H249" t="n">
+        <v>15</v>
+      </c>
+      <c r="I249" s="9" t="n"/>
+      <c r="J249" s="2">
+        <f>IF(I249&lt;&gt;"",I249,G249)</f>
+        <v/>
+      </c>
+      <c r="K249" s="2">
+        <f>E249-J249</f>
+        <v/>
+      </c>
+      <c r="L249" s="4">
+        <f>IF(J249&gt;0,K249/J249,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>249</v>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Goldin</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>2009-10 Upper Deck SP Game Used 3 Star Swatches #3S-BMJ Kobe Bryant/LeBron James/Oscar Robertson Relic Card (#182/299) - BGS NM-MT 8</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr"/>
+      <c r="E250" s="2" t="n">
+        <v>440.45</v>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>KOBE BRYANT LEBRON JAMES 2009-10 UD SP GAME USED 3 STAR PATCH /299 BGS 8 Q0034</t>
+        </is>
+      </c>
+      <c r="G250" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H250" t="n">
+        <v>18</v>
+      </c>
+      <c r="I250" s="9" t="n"/>
+      <c r="J250" s="2">
+        <f>IF(I250&lt;&gt;"",I250,G250)</f>
+        <v/>
+      </c>
+      <c r="K250" s="2">
+        <f>E250-J250</f>
+        <v/>
+      </c>
+      <c r="L250" s="4">
+        <f>IF(J250&gt;0,K250/J250,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>250</v>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Goldin</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>2025 Topps Five Star Pentamerous Penmanship #PP-RS Roki Sasaki Signed Rookie Card (#20/25) - Topps Encased</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr"/>
+      <c r="E251" s="2" t="n">
+        <v>379.5</v>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>2025 Topps Five Star Roki Sasaki Pentamerous Penmanship /25 Dodgers</t>
+        </is>
+      </c>
+      <c r="G251" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="H251" t="n">
+        <v>20</v>
+      </c>
+      <c r="I251" s="9" t="n"/>
+      <c r="J251" s="2">
+        <f>IF(I251&lt;&gt;"",I251,G251)</f>
+        <v/>
+      </c>
+      <c r="K251" s="2">
+        <f>E251-J251</f>
+        <v/>
+      </c>
+      <c r="L251" s="4">
+        <f>IF(J251&gt;0,K251/J251,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>251</v>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Goldin</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>2024-25 Panini Instant NIL Autographs #VJED-1 VJ Edgecombe Signed Rookie Card (#08/99) - Panini Encased</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr"/>
+      <c r="E252" s="2" t="n">
+        <v>373.75</v>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>2024-25 Panini Instant NCAA NIL VJ Edgecombe Rookie RC Card Silver Auto SP 8/99</t>
+        </is>
+      </c>
+      <c r="G252" s="2" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="H252" t="n">
+        <v>22</v>
+      </c>
+      <c r="I252" s="9" t="n"/>
+      <c r="J252" s="2">
+        <f>IF(I252&lt;&gt;"",I252,G252)</f>
+        <v/>
+      </c>
+      <c r="K252" s="2">
+        <f>E252-J252</f>
+        <v/>
+      </c>
+      <c r="L252" s="4">
+        <f>IF(J252&gt;0,K252/J252,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>252</v>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Goldin</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>1996-97 Upper Deck Michael Jordan Greater Heights #GH6 Michael Jordan - BGS GEM MINT 9.5</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr"/>
+      <c r="E253" s="2" t="n">
+        <v>316.25</v>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>MICHAEL JORDAN 1996 UPPER DECK GREATER HEIGHTS W/SHAQ BGS 9.5 GEM ULTRA RARE</t>
+        </is>
+      </c>
+      <c r="G253" s="2" t="n">
+        <v>259</v>
+      </c>
+      <c r="H253" t="n">
+        <v>15</v>
+      </c>
+      <c r="I253" s="9" t="n"/>
+      <c r="J253" s="2">
+        <f>IF(I253&lt;&gt;"",I253,G253)</f>
+        <v/>
+      </c>
+      <c r="K253" s="2">
+        <f>E253-J253</f>
+        <v/>
+      </c>
+      <c r="L253" s="4">
+        <f>IF(J253&gt;0,K253/J253,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>253</v>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Goldin</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>2024-25 Panini NSCC VIP Gold Color Blast #EH Erling Haaland (#16/44) - PSA MINT 9</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr"/>
+      <c r="E254" s="2" t="n">
+        <v>293.25</v>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>2024 Panini National VIP Gold ERLING HAALAND Color Blast /44 PSA 9 Norway</t>
+        </is>
+      </c>
+      <c r="G254" s="2" t="n">
+        <v>475</v>
+      </c>
+      <c r="H254" t="n">
+        <v>22</v>
+      </c>
+      <c r="I254" s="9" t="n"/>
+      <c r="J254" s="2">
+        <f>IF(I254&lt;&gt;"",I254,G254)</f>
+        <v/>
+      </c>
+      <c r="K254" s="2">
+        <f>E254-J254</f>
+        <v/>
+      </c>
+      <c r="L254" s="4">
+        <f>IF(J254&gt;0,K254/J254,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>254</v>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Goldin</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>2014-15 Panini Flawless Association Autographs Gold #AA-JE Julius Erving Signed Card (#03/10) - BGS NM-MT 8</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr"/>
+      <c r="E255" s="2" t="n">
+        <v>292.1</v>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>JULIUS ERVING 2025 PANINI VIP #17 GOLD MEMORABILIA 02/10</t>
+        </is>
+      </c>
+      <c r="G255" s="2" t="n">
+        <v>225</v>
+      </c>
+      <c r="H255" t="n">
+        <v>15</v>
+      </c>
+      <c r="I255" s="9" t="n"/>
+      <c r="J255" s="2">
+        <f>IF(I255&lt;&gt;"",I255,G255)</f>
+        <v/>
+      </c>
+      <c r="K255" s="2">
+        <f>E255-J255</f>
+        <v/>
+      </c>
+      <c r="L255" s="4">
+        <f>IF(J255&gt;0,K255/J255,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>255</v>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Goldin</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>2019-20 Panini Immaculate Collection Shadowbox Signatures '25 Black Box #SS-VCT Vince Carter Signed Card (#1/1) - Panini Encased</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr"/>
+      <c r="E256" s="2" t="n">
+        <v>281.75</v>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>2019-20 Panini Immaculate Vince Carter Black Box 1/1 Auto</t>
+        </is>
+      </c>
+      <c r="G256" s="2" t="n">
+        <v>699</v>
+      </c>
+      <c r="H256" t="n">
+        <v>22</v>
+      </c>
+      <c r="I256" s="9" t="n"/>
+      <c r="J256" s="2">
+        <f>IF(I256&lt;&gt;"",I256,G256)</f>
+        <v/>
+      </c>
+      <c r="K256" s="2">
+        <f>E256-J256</f>
+        <v/>
+      </c>
+      <c r="L256" s="4">
+        <f>IF(J256&gt;0,K256/J256,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>256</v>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Goldin</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>2024-25 Panini Flawless Vault Memorabilia #FVM-KAT Karl-Anthony Towns Patch Card (#12/25) - PSA NM-MT 8</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr"/>
+      <c r="E257" s="2" t="n">
+        <v>247.25</v>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>2024-25 Flawless Karl - Anthony Towns NIKE SWOOSH /25</t>
+        </is>
+      </c>
+      <c r="G257" s="2" t="n">
+        <v>342</v>
+      </c>
+      <c r="H257" t="n">
+        <v>18</v>
+      </c>
+      <c r="I257" s="9" t="n"/>
+      <c r="J257" s="2">
+        <f>IF(I257&lt;&gt;"",I257,G257)</f>
+        <v/>
+      </c>
+      <c r="K257" s="2">
+        <f>E257-J257</f>
+        <v/>
+      </c>
+      <c r="L257" s="4">
+        <f>IF(J257&gt;0,K257/J257,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>257</v>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Goldin</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>2013-14 Upper Deck All-Time Greats Signatures #ATG-J02 Magic Johnson Signed Card (#16/50) - BGS GEM MINT 9.5</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr"/>
+      <c r="E258" s="2" t="n">
+        <v>235.75</v>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>Magic Johnson - 2013 Upper Deck All Time Greats Signatures 16/50 BGS 9.5/10 Auto</t>
+        </is>
+      </c>
+      <c r="G258" s="2" t="n">
+        <v>475</v>
+      </c>
+      <c r="H258" t="n">
+        <v>20</v>
+      </c>
+      <c r="I258" s="9" t="n"/>
+      <c r="J258" s="2">
+        <f>IF(I258&lt;&gt;"",I258,G258)</f>
+        <v/>
+      </c>
+      <c r="K258" s="2">
+        <f>E258-J258</f>
+        <v/>
+      </c>
+      <c r="L258" s="4">
+        <f>IF(J258&gt;0,K258/J258,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>258</v>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Goldin</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>2020-21 Panini Donruss Optic Signature Series #SS-LBL LaMelo Ball Signed Rookie Card - PSA Authentic, PSA/DNA GEM MT 10</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr"/>
+      <c r="E259" s="2" t="n">
+        <v>195.5</v>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>5300 LaMelo Ball 2020 Panini Donruss Optic Signature Series RC PSA AUTH Auto 10</t>
+        </is>
+      </c>
+      <c r="G259" s="2" t="n">
+        <v>338</v>
+      </c>
+      <c r="H259" t="n">
+        <v>24</v>
+      </c>
+      <c r="I259" s="9" t="n"/>
+      <c r="J259" s="2">
+        <f>IF(I259&lt;&gt;"",I259,G259)</f>
+        <v/>
+      </c>
+      <c r="K259" s="2">
+        <f>E259-J259</f>
+        <v/>
+      </c>
+      <c r="L259" s="4">
+        <f>IF(J259&gt;0,K259/J259,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
+        <v>259</v>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Goldin</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>2022-23 Panini Recon Rookie Recon Signatures Purple #RRS-PBC Paolo Banchero Signed Rookie Card (#12/25) - PSA NM-MT 8, PSA/DNA GEM MT 10</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr"/>
+      <c r="E260" s="2" t="n">
+        <v>149.5</v>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>2024-25 Panini Obsidian Paolo Banchero #12  Vitreous SSP CASE HIT Grade It🔥🔥sp</t>
+        </is>
+      </c>
+      <c r="G260" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="H260" t="n">
+        <v>20</v>
+      </c>
+      <c r="I260" s="9" t="n"/>
+      <c r="J260" s="2">
+        <f>IF(I260&lt;&gt;"",I260,G260)</f>
+        <v/>
+      </c>
+      <c r="K260" s="2">
+        <f>E260-J260</f>
+        <v/>
+      </c>
+      <c r="L260" s="4">
+        <f>IF(J260&gt;0,K260/J260,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
+        <v>260</v>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Goldin</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>2025-26 Topps Rise To Stardom Black Rainbow #RTS-3 VJ Edgecombe Rookie Card (#01/10) - PSA NM-MT 8</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr"/>
+      <c r="E261" s="2" t="n">
+        <v>149.5</v>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>VJ Edgecombe 2025-26 Topps Daily Dribble #DD-33 Black Foil #’d 04/10 76ers RC</t>
+        </is>
+      </c>
+      <c r="G261" s="2" t="n">
+        <v>1079.99</v>
+      </c>
+      <c r="H261" t="n">
+        <v>20</v>
+      </c>
+      <c r="I261" s="9" t="n"/>
+      <c r="J261" s="2">
+        <f>IF(I261&lt;&gt;"",I261,G261)</f>
+        <v/>
+      </c>
+      <c r="K261" s="2">
+        <f>E261-J261</f>
+        <v/>
+      </c>
+      <c r="L261" s="4">
+        <f>IF(J261&gt;0,K261/J261,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
+        <v>261</v>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Goldin</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>2022-23 Topps Finest UCC The Man Blue Refractor #FTM-9 Lionel Messi (#072/150) - PSA MINT 9</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr"/>
+      <c r="E262" s="2" t="n">
+        <v>138</v>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>2022-23 Topps Finest UEFA Club Competitions - The Man Lionel Messi #9 Blue /150</t>
+        </is>
+      </c>
+      <c r="G262" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="H262" t="n">
+        <v>22</v>
+      </c>
+      <c r="I262" s="9" t="n"/>
+      <c r="J262" s="2">
+        <f>IF(I262&lt;&gt;"",I262,G262)</f>
+        <v/>
+      </c>
+      <c r="K262" s="2">
+        <f>E262-J262</f>
+        <v/>
+      </c>
+      <c r="L262" s="4">
+        <f>IF(J262&gt;0,K262/J262,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="n">
+        <v>262</v>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Goldin</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>2012-13 Upper Deck Exquisite Collection Dimensions #D-JE Julius Erving Signed Card</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr"/>
+      <c r="E263" s="2" t="n">
+        <v>117.3</v>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>2012-13 Upper Deck Exquisite Collection Julius Erving Dimensions Auto</t>
+        </is>
+      </c>
+      <c r="G263" s="2" t="n">
+        <v>229</v>
+      </c>
+      <c r="H263" t="n">
+        <v>17</v>
+      </c>
+      <c r="I263" s="9" t="n"/>
+      <c r="J263" s="2">
+        <f>IF(I263&lt;&gt;"",I263,G263)</f>
+        <v/>
+      </c>
+      <c r="K263" s="2">
+        <f>E263-J263</f>
+        <v/>
+      </c>
+      <c r="L263" s="4">
+        <f>IF(J263&gt;0,K263/J263,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="n">
+        <v>263</v>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Goldin</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>2022-23 Panini Immaculate Collection Patch Autographs Jersey Number #IPA-RGO Rudy Gobert Signed Relic Card (#06/27) - Panini Encased</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr"/>
+      <c r="E264" s="2" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>RUDY GOBERT 2022-23 IMMACULATE JERSEY NUMBER PATCH AUTOGRAPH AUTO /27 Q0218</t>
+        </is>
+      </c>
+      <c r="G264" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="H264" t="n">
+        <v>22</v>
+      </c>
+      <c r="I264" s="9" t="n"/>
+      <c r="J264" s="2">
+        <f>IF(I264&lt;&gt;"",I264,G264)</f>
+        <v/>
+      </c>
+      <c r="K264" s="2">
+        <f>E264-J264</f>
+        <v/>
+      </c>
+      <c r="L264" s="4">
+        <f>IF(J264&gt;0,K264/J264,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="265">
+      <c r="D265" s="1" t="inlineStr">
+        <is>
+          <t>TOTALS</t>
+        </is>
+      </c>
+      <c r="E265" s="3">
+        <f>SUM(E2:E264)</f>
+        <v/>
+      </c>
+      <c r="G265" s="2">
+        <f>SUM(G2:G264)</f>
+        <v/>
+      </c>
+      <c r="J265" s="3">
+        <f>SUM(J2:J264)</f>
+        <v/>
+      </c>
+      <c r="K265" s="3">
+        <f>SUM(K2:K264)</f>
+        <v/>
+      </c>
+      <c r="L265" s="4">
+        <f>IF(J265&gt;0,K265/J265,"")</f>
         <v/>
       </c>
     </row>
@@ -9477,58 +12626,53 @@
   </sheetPr>
   <dimension ref="A1:J85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="75" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>Card</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Proceeds</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Best Guess</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Guess Cost</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>YOUR COST</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
+        <is>
+          <t>Sale Date</t>
+        </is>
+      </c>
+      <c r="E1" s="6" t="inlineStr">
+        <is>
+          <t>Net Proceeds</t>
+        </is>
+      </c>
+      <c r="F1" s="7" t="inlineStr">
+        <is>
+          <t>Source (eBay or Fanatics?)</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
+          <t>ENTER COST</t>
+        </is>
+      </c>
+      <c r="H1" s="6" t="inlineStr">
         <is>
           <t>P&amp;L</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Return</t>
-        </is>
-      </c>
+      <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -9541,29 +12685,21 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2012-13 Upper Deck Exquisite Collection UD Black Signatures #B-MI Michael Jordan Signed Card (#33/75) - PSA GEM MT 10</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
+          <t>2019 Panini Flawless Triple Legends Sapphire #TL-MRG Mickey Mantle/Babe Ruth/Lou Gehrig Relic Card (#05/15) - PSA GEM MT 10 - Pop 2</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" s="2" t="n">
-        <v>10465</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" s="3" t="n"/>
-      <c r="I2" s="2">
-        <f>IF(H2&lt;&gt;"",E2-H2,"")</f>
-        <v/>
-      </c>
-      <c r="J2" s="4">
-        <f>IF(H2&lt;&gt;"",I2/H2,"")</f>
-        <v/>
-      </c>
+        <v>8051.15</v>
+      </c>
+      <c r="F2" s="9" t="n"/>
+      <c r="G2" s="15" t="n"/>
+      <c r="H2" s="3">
+        <f>IF(G2&lt;&gt;"",E2-G2,"")</f>
+        <v/>
+      </c>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="4" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -9576,29 +12712,21 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2019 Panini Flawless Triple Legends Sapphire #TL-MRG Mickey Mantle/Babe Ruth/Lou Gehrig Relic Card (#05/15) - PSA GEM MT 10 - Pop 2</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
+          <t>2025 Panini Impeccable WNBA Basketball Factory-Sealed Hobby Case (3 Boxes) - Possible Paige Bueckers, Hailey Van Lith, Kiki Iriafen Rookie Cards</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" s="2" t="n">
-        <v>8051.15</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" s="3" t="n"/>
-      <c r="I3" s="2">
-        <f>IF(H3&lt;&gt;"",E3-H3,"")</f>
-        <v/>
-      </c>
-      <c r="J3" s="4">
-        <f>IF(H3&lt;&gt;"",I3/H3,"")</f>
-        <v/>
-      </c>
+        <v>2876.15</v>
+      </c>
+      <c r="F3" s="9" t="n"/>
+      <c r="G3" s="15" t="n"/>
+      <c r="H3" s="3">
+        <f>IF(G3&lt;&gt;"",E3-G3,"")</f>
+        <v/>
+      </c>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -9611,29 +12739,21 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2023-24 Topps Chrome 1972 Topps Autographs Gold Refractor #TA-VW Victor Wembanyama Signed Rookie Card (#04/50) - PSA MINT 9</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
+          <t>Feb. 27, 2013 - Stephen Curry Signed Full Ticket - Golden State Warriors vs. New York Knicks - Season Highs of 54 Points and 11 3-Pointers - PSA Authentic</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" s="2" t="n">
-        <v>7123.1</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="3" t="n"/>
-      <c r="I4" s="2">
-        <f>IF(H4&lt;&gt;"",E4-H4,"")</f>
-        <v/>
-      </c>
-      <c r="J4" s="4">
-        <f>IF(H4&lt;&gt;"",I4/H4,"")</f>
-        <v/>
-      </c>
+        <v>529</v>
+      </c>
+      <c r="F4" s="9" t="n"/>
+      <c r="G4" s="15" t="n"/>
+      <c r="H4" s="3">
+        <f>IF(G4&lt;&gt;"",E4-G4,"")</f>
+        <v/>
+      </c>
+      <c r="I4" s="2" t="n"/>
+      <c r="J4" s="4" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -9646,29 +12766,21 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2025-26 Topps Silver Pack '80-81 Chrome Basketball Rookie Autographs Orange Refractor #80CR2-CF Cooper Flagg Signed Rookie Card (#17/25) - PSA MINT 9, PSA/DNA GEM MT 10</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
+          <t>Stephen Curry Signed Trading Card - PSA/DNA Authentic</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" s="2" t="n">
-        <v>4427.5</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="3" t="n"/>
-      <c r="I5" s="2">
-        <f>IF(H5&lt;&gt;"",E5-H5,"")</f>
-        <v/>
-      </c>
-      <c r="J5" s="4">
-        <f>IF(H5&lt;&gt;"",I5/H5,"")</f>
-        <v/>
-      </c>
+        <v>380.65</v>
+      </c>
+      <c r="F5" s="9" t="n"/>
+      <c r="G5" s="15" t="n"/>
+      <c r="H5" s="3">
+        <f>IF(G5&lt;&gt;"",E5-G5,"")</f>
+        <v/>
+      </c>
+      <c r="I5" s="2" t="n"/>
+      <c r="J5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -9681,29 +12793,21 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2018-19 Panini National Treasures Peerless Signatures #PS-KBR Kobe Bryant Signed Card (#03/25) - BGS MINT 9, Beckett 10</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
+          <t>1997-98 Fleer Hoops 23k Gold Basketball Texture Bulls Starting Five - PSA GEM MT 10</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" s="2" t="n">
-        <v>4025</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="3" t="n"/>
-      <c r="I6" s="2">
-        <f>IF(H6&lt;&gt;"",E6-H6,"")</f>
-        <v/>
-      </c>
-      <c r="J6" s="4">
-        <f>IF(H6&lt;&gt;"",I6/H6,"")</f>
-        <v/>
-      </c>
+        <v>330.05</v>
+      </c>
+      <c r="F6" s="9" t="n"/>
+      <c r="G6" s="15" t="n"/>
+      <c r="H6" s="3">
+        <f>IF(G6&lt;&gt;"",E6-G6,"")</f>
+        <v/>
+      </c>
+      <c r="I6" s="2" t="n"/>
+      <c r="J6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -9716,29 +12820,21 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2015-16 Panini Noir Autographs Color Gold #NC-KBR Kobe Bryant Signed Card (#4/5) - PSA EX-MT 6 - Pop 1</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
+          <t>2024-25 Topps Deluxe Manchester United Speak of the Devil Autograph Orange Refractor #SD-ZA Zlatan Ibrahimovic Signed Card (#07/25) - PSA MINT 9 - Pop 4</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" s="2" t="n">
-        <v>3795</v>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="3" t="n"/>
-      <c r="I7" s="2">
-        <f>IF(H7&lt;&gt;"",E7-H7,"")</f>
-        <v/>
-      </c>
-      <c r="J7" s="4">
-        <f>IF(H7&lt;&gt;"",I7/H7,"")</f>
-        <v/>
-      </c>
+        <v>178.25</v>
+      </c>
+      <c r="F7" s="9" t="n"/>
+      <c r="G7" s="15" t="n"/>
+      <c r="H7" s="3">
+        <f>IF(G7&lt;&gt;"",E7-G7,"")</f>
+        <v/>
+      </c>
+      <c r="I7" s="2" t="n"/>
+      <c r="J7" s="4" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -9751,29 +12847,21 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2018 Panini Kaboom! #K-NJ Neymar Jr. - PSA GEM MT 10</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
+          <t>Mike Tyson Signed Everlast Boxing Glove - Fiterman Sports</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" s="2" t="n">
-        <v>3576.5</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3" t="n"/>
-      <c r="I8" s="2">
-        <f>IF(H8&lt;&gt;"",E8-H8,"")</f>
-        <v/>
-      </c>
-      <c r="J8" s="4">
-        <f>IF(H8&lt;&gt;"",I8/H8,"")</f>
-        <v/>
-      </c>
+        <v>126.5</v>
+      </c>
+      <c r="F8" s="9" t="n"/>
+      <c r="G8" s="15" t="n"/>
+      <c r="H8" s="3">
+        <f>IF(G8&lt;&gt;"",E8-G8,"")</f>
+        <v/>
+      </c>
+      <c r="I8" s="2" t="n"/>
+      <c r="J8" s="4" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -9786,29 +12874,21 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2003-04 Upper Deck Top Prospects Signs of Success #SS-LJ LeBron James Signed Rookie Card - BGS MINT 9, Beckett 10</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
+          <t>2019-20 Panini One and One Dual Jersey Autographs Purple #DJA-DAF De'Aaron Fox Signed Relic Card (#06/35) - Panini Encased</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" s="2" t="n">
-        <v>3047.5</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="3" t="n"/>
-      <c r="I9" s="2">
-        <f>IF(H9&lt;&gt;"",E9-H9,"")</f>
-        <v/>
-      </c>
-      <c r="J9" s="4">
-        <f>IF(H9&lt;&gt;"",I9/H9,"")</f>
-        <v/>
-      </c>
+        <v>75.90000000000001</v>
+      </c>
+      <c r="F9" s="9" t="n"/>
+      <c r="G9" s="15" t="n"/>
+      <c r="H9" s="3">
+        <f>IF(G9&lt;&gt;"",E9-G9,"")</f>
+        <v/>
+      </c>
+      <c r="I9" s="2" t="n"/>
+      <c r="J9" s="4" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -9821,2610 +12901,553 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2025 Panini Impeccable WNBA Basketball Factory-Sealed Hobby Case (3 Boxes) - Possible Paige Bueckers, Hailey Van Lith, Kiki Iriafen Rookie Cards</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
+          <t>Allen Iverson Signed Trading Card - PSA/DNA Authentic</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" s="2" t="n">
-        <v>2876.15</v>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="3" t="n"/>
-      <c r="I10" s="2">
-        <f>IF(H10&lt;&gt;"",E10-H10,"")</f>
-        <v/>
-      </c>
-      <c r="J10" s="4">
-        <f>IF(H10&lt;&gt;"",I10/H10,"")</f>
-        <v/>
-      </c>
+        <v>71.3</v>
+      </c>
+      <c r="F10" s="9" t="n"/>
+      <c r="G10" s="15" t="n"/>
+      <c r="H10" s="3">
+        <f>IF(G10&lt;&gt;"",E10-G10,"")</f>
+        <v/>
+      </c>
+      <c r="I10" s="2" t="n"/>
+      <c r="J10" s="4" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Goldin</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>2025-26 Topps Chrome Future Stars Autographs Green Refractor #FS-CF Cooper Flagg Signed Rookie Card (#43/99) - PSA MINT 9, PSA/DNA GEM MT 10</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>2760</v>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="3" t="n"/>
-      <c r="I11" s="2">
-        <f>IF(H11&lt;&gt;"",E11-H11,"")</f>
-        <v/>
-      </c>
-      <c r="J11" s="4">
-        <f>IF(H11&lt;&gt;"",I11/H11,"")</f>
-        <v/>
-      </c>
+      <c r="D11" s="1" t="inlineStr">
+        <is>
+          <t>TOTALS</t>
+        </is>
+      </c>
+      <c r="E11" s="3">
+        <f>SUM(E2:E10)</f>
+        <v/>
+      </c>
+      <c r="G11" s="2">
+        <f>SUM(G2:G10)</f>
+        <v/>
+      </c>
+      <c r="H11" s="3">
+        <f>SUM(H2:H10)</f>
+        <v/>
+      </c>
+      <c r="I11" s="2" t="n"/>
+      <c r="J11" s="4" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Goldin</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>2023-24 Bowman U Best of 2023 Autograph Geometric Red Refractor #B23-CC Caitlin Clark Signed Rookie Card (#01/10) - PSA MINT 9, PSA/DNA GEM MT 10</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>2645</v>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E12" s="2" t="n"/>
+      <c r="G12" s="2" t="n"/>
       <c r="H12" s="3" t="n"/>
-      <c r="I12" s="2">
-        <f>IF(H12&lt;&gt;"",E12-H12,"")</f>
-        <v/>
-      </c>
-      <c r="J12" s="4">
-        <f>IF(H12&lt;&gt;"",I12/H12,"")</f>
-        <v/>
-      </c>
+      <c r="I12" s="2" t="n"/>
+      <c r="J12" s="4" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Goldin</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>2020-21 Panini Flawless Draft Gem Signatures Ruby #DG-AEW Anthony Edwards Signed Rookie Card (#15/15) - Panini Encased</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>2601.3</v>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E13" s="2" t="n"/>
+      <c r="G13" s="2" t="n"/>
       <c r="H13" s="3" t="n"/>
-      <c r="I13" s="2">
-        <f>IF(H13&lt;&gt;"",E13-H13,"")</f>
-        <v/>
-      </c>
-      <c r="J13" s="4">
-        <f>IF(H13&lt;&gt;"",I13/H13,"")</f>
-        <v/>
-      </c>
+      <c r="I13" s="2" t="n"/>
+      <c r="J13" s="4" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Goldin</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>2023-24 Topps Chrome UCC Future Stars Autographs SuperFractor #FSA-KM Kobbie Mainoo Signed Card (#1/1) - PSA NM-MT 8</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>2472.5</v>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E14" s="2" t="n"/>
+      <c r="G14" s="2" t="n"/>
       <c r="H14" s="3" t="n"/>
-      <c r="I14" s="2">
-        <f>IF(H14&lt;&gt;"",E14-H14,"")</f>
-        <v/>
-      </c>
-      <c r="J14" s="4">
-        <f>IF(H14&lt;&gt;"",I14/H14,"")</f>
-        <v/>
-      </c>
+      <c r="I14" s="2" t="n"/>
+      <c r="J14" s="4" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Goldin</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>2022-23 Bowman U Best of '22 Autographs #BOA-VW Victor Wembanyama Signed Rookie Card - PSA GEM MT 10</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>2472.5</v>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E15" s="2" t="n"/>
+      <c r="G15" s="2" t="n"/>
       <c r="H15" s="3" t="n"/>
-      <c r="I15" s="2">
-        <f>IF(H15&lt;&gt;"",E15-H15,"")</f>
-        <v/>
-      </c>
-      <c r="J15" s="4">
-        <f>IF(H15&lt;&gt;"",I15/H15,"")</f>
-        <v/>
-      </c>
+      <c r="I15" s="2" t="n"/>
+      <c r="J15" s="4" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Goldin</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>2025-26 Topps Chrome Next Stop Signatures Purple Geometric Refractor #NS-CF Cooper Flagg Signed Rookie Card (#68/75) - PSA MINT 9</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>2375.9</v>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E16" s="2" t="n"/>
+      <c r="G16" s="2" t="n"/>
       <c r="H16" s="3" t="n"/>
-      <c r="I16" s="2">
-        <f>IF(H16&lt;&gt;"",E16-H16,"")</f>
-        <v/>
-      </c>
-      <c r="J16" s="4">
-        <f>IF(H16&lt;&gt;"",I16/H16,"")</f>
-        <v/>
-      </c>
+      <c r="I16" s="2" t="n"/>
+      <c r="J16" s="4" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Goldin</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2023 Bowman Draft Picks &amp; Prospects Autographs Red #DPPA-PS Paul Skenes Signed Rookie Card (#2/5) - PSA MINT 9
-</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>2300</v>
-      </c>
-      <c r="G17" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E17" s="2" t="n"/>
+      <c r="G17" s="2" t="n"/>
       <c r="H17" s="3" t="n"/>
-      <c r="I17" s="2">
-        <f>IF(H17&lt;&gt;"",E17-H17,"")</f>
-        <v/>
-      </c>
-      <c r="J17" s="4">
-        <f>IF(H17&lt;&gt;"",I17/H17,"")</f>
-        <v/>
-      </c>
+      <c r="I17" s="2" t="n"/>
+      <c r="J17" s="4" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Goldin</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>2023-24 Topps Chrome UCC Black Lazer Autograph #BLA-LY Lamine Yamal Signed Rookie Card - PSA MINT 9, PSA/DNA GEM MT 10</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>2242.5</v>
-      </c>
-      <c r="G18" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E18" s="2" t="n"/>
+      <c r="G18" s="2" t="n"/>
       <c r="H18" s="3" t="n"/>
-      <c r="I18" s="2">
-        <f>IF(H18&lt;&gt;"",E18-H18,"")</f>
-        <v/>
-      </c>
-      <c r="J18" s="4">
-        <f>IF(H18&lt;&gt;"",I18/H18,"")</f>
-        <v/>
-      </c>
+      <c r="I18" s="2" t="n"/>
+      <c r="J18" s="4" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Goldin</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>2020-21 Panini One and One Rookie Jersey Autographs Blue #RJA-AED Anthony Edwards Signed Patch Rookie Card (#26/35) - PSA Authentic, PSA/DNA GEM MT 10</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="n">
-        <v>2127.5</v>
-      </c>
-      <c r="G19" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E19" s="2" t="n"/>
+      <c r="G19" s="2" t="n"/>
       <c r="H19" s="3" t="n"/>
-      <c r="I19" s="2">
-        <f>IF(H19&lt;&gt;"",E19-H19,"")</f>
-        <v/>
-      </c>
-      <c r="J19" s="4">
-        <f>IF(H19&lt;&gt;"",I19/H19,"")</f>
-        <v/>
-      </c>
+      <c r="I19" s="2" t="n"/>
+      <c r="J19" s="4" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Goldin</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2019-20 Panini Flawless Premium Ink #PI-SCY Stephen Curry Signed Card (#01/25) - PSA MINT 9, PSA/DNA GEM MT 10 - Pop 1
-</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>2070</v>
-      </c>
-      <c r="G20" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E20" s="2" t="n"/>
+      <c r="G20" s="2" t="n"/>
       <c r="H20" s="3" t="n"/>
-      <c r="I20" s="2">
-        <f>IF(H20&lt;&gt;"",E20-H20,"")</f>
-        <v/>
-      </c>
-      <c r="J20" s="4">
-        <f>IF(H20&lt;&gt;"",I20/H20,"")</f>
-        <v/>
-      </c>
+      <c r="I20" s="2" t="n"/>
+      <c r="J20" s="4" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Goldin</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2015-16 Panini National Treasures Clutch Factor Jersey Autograph #CF-SCR Stephen Curry Signed Relic Card (#14/25) - PSA MINT 9 - Pop 4
-</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="n">
-        <v>2070</v>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E21" s="2" t="n"/>
+      <c r="G21" s="2" t="n"/>
       <c r="H21" s="3" t="n"/>
-      <c r="I21" s="2">
-        <f>IF(H21&lt;&gt;"",E21-H21,"")</f>
-        <v/>
-      </c>
-      <c r="J21" s="4">
-        <f>IF(H21&lt;&gt;"",I21/H21,"")</f>
-        <v/>
-      </c>
+      <c r="I21" s="2" t="n"/>
+      <c r="J21" s="4" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Goldin</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>2025 Topps Five Star Golden Graphs Blue #GG-YY Yoshinobu Yamamoto Signed Card (#19/20) - Topps Encased</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="n">
-        <v>1851.5</v>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E22" s="2" t="n"/>
+      <c r="G22" s="2" t="n"/>
       <c r="H22" s="3" t="n"/>
-      <c r="I22" s="2">
-        <f>IF(H22&lt;&gt;"",E22-H22,"")</f>
-        <v/>
-      </c>
-      <c r="J22" s="4">
-        <f>IF(H22&lt;&gt;"",I22/H22,"")</f>
-        <v/>
-      </c>
+      <c r="I22" s="2" t="n"/>
+      <c r="J22" s="4" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Goldin</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>2008 Upper Deck SP Rookie Threads SP Dual Threads #TD-BJ Kobe Bryant/Michael Jordan Relic Card - BGS NM-MT+ 8.5</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="n">
-        <v>1841.15</v>
-      </c>
-      <c r="G23" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E23" s="2" t="n"/>
+      <c r="G23" s="2" t="n"/>
       <c r="H23" s="3" t="n"/>
-      <c r="I23" s="2">
-        <f>IF(H23&lt;&gt;"",E23-H23,"")</f>
-        <v/>
-      </c>
-      <c r="J23" s="4">
-        <f>IF(H23&lt;&gt;"",I23/H23,"")</f>
-        <v/>
-      </c>
+      <c r="I23" s="2" t="n"/>
+      <c r="J23" s="4" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Goldin</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2024-25 Panini Flawless All-Star Ink Gold #ANB-LUD Luka Doncic Signed Card (#04/10) - Panini Encased
-</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="n">
-        <v>1840</v>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E24" s="2" t="n"/>
+      <c r="G24" s="2" t="n"/>
       <c r="H24" s="3" t="n"/>
-      <c r="I24" s="2">
-        <f>IF(H24&lt;&gt;"",E24-H24,"")</f>
-        <v/>
-      </c>
-      <c r="J24" s="4">
-        <f>IF(H24&lt;&gt;"",I24/H24,"")</f>
-        <v/>
-      </c>
+      <c r="I24" s="2" t="n"/>
+      <c r="J24" s="4" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Goldin</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>2023-24 Topps Now Autographs #VW-6A Victor Wembanyama Signed Rookie Card (#47/99) - PSA MINT 9</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="n">
-        <v>1667.5</v>
-      </c>
-      <c r="G25" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E25" s="2" t="n"/>
+      <c r="G25" s="2" t="n"/>
       <c r="H25" s="3" t="n"/>
-      <c r="I25" s="2">
-        <f>IF(H25&lt;&gt;"",E25-H25,"")</f>
-        <v/>
-      </c>
-      <c r="J25" s="4">
-        <f>IF(H25&lt;&gt;"",I25/H25,"")</f>
-        <v/>
-      </c>
+      <c r="I25" s="2" t="n"/>
+      <c r="J25" s="4" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Goldin</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>2019 Topps Diamond Icons Autographs Gold #DIA-MT Mike Trout Signed Card (#1/1) - BGS GEM MINT 9.5, Beckett 10 - True Gem</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="n">
-        <v>1610</v>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E26" s="2" t="n"/>
+      <c r="G26" s="2" t="n"/>
       <c r="H26" s="3" t="n"/>
-      <c r="I26" s="2">
-        <f>IF(H26&lt;&gt;"",E26-H26,"")</f>
-        <v/>
-      </c>
-      <c r="J26" s="4">
-        <f>IF(H26&lt;&gt;"",I26/H26,"")</f>
-        <v/>
-      </c>
+      <c r="I26" s="2" t="n"/>
+      <c r="J26" s="4" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Goldin</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>2023-24 Panini Contenders Optic 1986 Tribute Autographs International Jade #86-LKD Luka Doncic Signed Card (#3/5) - Panini Encased</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="n">
-        <v>1493.85</v>
-      </c>
-      <c r="G27" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E27" s="2" t="n"/>
+      <c r="G27" s="2" t="n"/>
       <c r="H27" s="3" t="n"/>
-      <c r="I27" s="2">
-        <f>IF(H27&lt;&gt;"",E27-H27,"")</f>
-        <v/>
-      </c>
-      <c r="J27" s="4">
-        <f>IF(H27&lt;&gt;"",I27/H27,"")</f>
-        <v/>
-      </c>
+      <c r="I27" s="2" t="n"/>
+      <c r="J27" s="4" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Goldin</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>2020-21 Panini National Treasures Treasured Signatures Bronze #TS-LUD Luka Doncic Signed Card (#25/25) - PSA MINT 9</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="n">
-        <v>1463.95</v>
-      </c>
-      <c r="G28" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E28" s="2" t="n"/>
+      <c r="G28" s="2" t="n"/>
       <c r="H28" s="3" t="n"/>
-      <c r="I28" s="2">
-        <f>IF(H28&lt;&gt;"",E28-H28,"")</f>
-        <v/>
-      </c>
-      <c r="J28" s="4">
-        <f>IF(H28&lt;&gt;"",I28/H28,"")</f>
-        <v/>
-      </c>
+      <c r="I28" s="2" t="n"/>
+      <c r="J28" s="4" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Goldin</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>2024-25 Bowman Chrome U Final Exam Autograph #FEA-CF Cooper Flagg Signed Rookie Card - PSA GEM MT 10</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="n">
-        <v>1449</v>
-      </c>
-      <c r="G29" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E29" s="2" t="n"/>
+      <c r="G29" s="2" t="n"/>
       <c r="H29" s="3" t="n"/>
-      <c r="I29" s="2">
-        <f>IF(H29&lt;&gt;"",E29-H29,"")</f>
-        <v/>
-      </c>
-      <c r="J29" s="4">
-        <f>IF(H29&lt;&gt;"",I29/H29,"")</f>
-        <v/>
-      </c>
+      <c r="I29" s="2" t="n"/>
+      <c r="J29" s="4" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Goldin</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>2022-23 Panini Immaculate Collection Scorers Club Signatures #SCS-LUD Luka Doncic Signed Card (#23/25) - PSA MINT 9</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="n">
-        <v>1392.65</v>
-      </c>
-      <c r="G30" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E30" s="2" t="n"/>
+      <c r="G30" s="2" t="n"/>
       <c r="H30" s="3" t="n"/>
-      <c r="I30" s="2">
-        <f>IF(H30&lt;&gt;"",E30-H30,"")</f>
-        <v/>
-      </c>
-      <c r="J30" s="4">
-        <f>IF(H30&lt;&gt;"",I30/H30,"")</f>
-        <v/>
-      </c>
+      <c r="I30" s="2" t="n"/>
+      <c r="J30" s="4" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Goldin</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>2021-22 Topps Chrome PSG Autograph Wave Refractor #AU-KM Kylian Mbappe Signed Card (#41/50) - PSA MINT 9</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="n">
-        <v>1389.2</v>
-      </c>
-      <c r="G31" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E31" s="2" t="n"/>
+      <c r="G31" s="2" t="n"/>
       <c r="H31" s="3" t="n"/>
-      <c r="I31" s="2">
-        <f>IF(H31&lt;&gt;"",E31-H31,"")</f>
-        <v/>
-      </c>
-      <c r="J31" s="4">
-        <f>IF(H31&lt;&gt;"",I31/H31,"")</f>
-        <v/>
-      </c>
+      <c r="I31" s="2" t="n"/>
+      <c r="J31" s="4" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Goldin</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>2014-15 Panini Flawless Association Autographs Emerald #AA-GA Giannis Antetokounmpo Signed Card (#1/5) - PSA NM 7</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="n">
-        <v>1151.15</v>
-      </c>
-      <c r="G32" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E32" s="2" t="n"/>
+      <c r="G32" s="2" t="n"/>
       <c r="H32" s="3" t="n"/>
-      <c r="I32" s="2">
-        <f>IF(H32&lt;&gt;"",E32-H32,"")</f>
-        <v/>
-      </c>
-      <c r="J32" s="4">
-        <f>IF(H32&lt;&gt;"",I32/H32,"")</f>
-        <v/>
-      </c>
+      <c r="I32" s="2" t="n"/>
+      <c r="J32" s="4" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Goldin</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>2023-24 Topps Finest Masters Autograph Red/Black Vapor Geometric Refractor #MA-SC Stephen Curry Signed Card (#01/10) - Topps Sealed</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="n">
-        <v>1150</v>
-      </c>
-      <c r="G33" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E33" s="2" t="n"/>
+      <c r="G33" s="2" t="n"/>
       <c r="H33" s="3" t="n"/>
-      <c r="I33" s="2">
-        <f>IF(H33&lt;&gt;"",E33-H33,"")</f>
-        <v/>
-      </c>
-      <c r="J33" s="4">
-        <f>IF(H33&lt;&gt;"",I33/H33,"")</f>
-        <v/>
-      </c>
+      <c r="I33" s="2" t="n"/>
+      <c r="J33" s="4" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Goldin</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>2022-23 Panini Noir Autographed Prime Black and White #ANB-LUD Luka Doncic Signed Card (#17/25) - Panini Encased</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="n">
-        <v>1150</v>
-      </c>
-      <c r="G34" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E34" s="2" t="n"/>
+      <c r="G34" s="2" t="n"/>
       <c r="H34" s="3" t="n"/>
-      <c r="I34" s="2">
-        <f>IF(H34&lt;&gt;"",E34-H34,"")</f>
-        <v/>
-      </c>
-      <c r="J34" s="4">
-        <f>IF(H34&lt;&gt;"",I34/H34,"")</f>
-        <v/>
-      </c>
+      <c r="I34" s="2" t="n"/>
+      <c r="J34" s="4" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Goldin</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2024-25 Bowman's Best University Prospect Jumbo Relic Autographs Gold Geometric Refractor #PJRA-CF Cooper Flagg Signed Relic Rookie Card (#38/50) - BGS NM-MT+ 8.5, Beckett 10
-</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="n">
-        <v>1150</v>
-      </c>
-      <c r="G35" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E35" s="2" t="n"/>
+      <c r="G35" s="2" t="n"/>
       <c r="H35" s="3" t="n"/>
-      <c r="I35" s="2">
-        <f>IF(H35&lt;&gt;"",E35-H35,"")</f>
-        <v/>
-      </c>
-      <c r="J35" s="4">
-        <f>IF(H35&lt;&gt;"",I35/H35,"")</f>
-        <v/>
-      </c>
+      <c r="I35" s="2" t="n"/>
+      <c r="J35" s="4" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Goldin</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>2020-21 Panini National Treasures Rookie Private Signings Association #PSA-AED Anthony Edwards Signed Rookie Card - PSA MINT 9 - Pop 4</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="n">
-        <v>1150</v>
-      </c>
-      <c r="G36" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E36" s="2" t="n"/>
+      <c r="G36" s="2" t="n"/>
       <c r="H36" s="3" t="n"/>
-      <c r="I36" s="2">
-        <f>IF(H36&lt;&gt;"",E36-H36,"")</f>
-        <v/>
-      </c>
-      <c r="J36" s="4">
-        <f>IF(H36&lt;&gt;"",I36/H36,"")</f>
-        <v/>
-      </c>
+      <c r="I36" s="2" t="n"/>
+      <c r="J36" s="4" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Goldin</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>2019-20 Panini One and One First-Team Signatures #FT-SCY Stephen Curry Signed Card (#08/25) - BGS MINT 9, Beckett 10 - Pop 3</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="n">
-        <v>1122.4</v>
-      </c>
-      <c r="G37" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E37" s="2" t="n"/>
+      <c r="G37" s="2" t="n"/>
       <c r="H37" s="3" t="n"/>
-      <c r="I37" s="2">
-        <f>IF(H37&lt;&gt;"",E37-H37,"")</f>
-        <v/>
-      </c>
-      <c r="J37" s="4">
-        <f>IF(H37&lt;&gt;"",I37/H37,"")</f>
-        <v/>
-      </c>
+      <c r="I37" s="2" t="n"/>
+      <c r="J37" s="4" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Goldin</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>2024-25 Topps Regalia Relic Signatures #RRS-SC Stephen Curry Signed Game-Used Patch Card (#03/15) - Topps Encased</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="n">
-        <v>1104</v>
-      </c>
-      <c r="G38" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E38" s="2" t="n"/>
+      <c r="G38" s="2" t="n"/>
       <c r="H38" s="3" t="n"/>
-      <c r="I38" s="2">
-        <f>IF(H38&lt;&gt;"",E38-H38,"")</f>
-        <v/>
-      </c>
-      <c r="J38" s="4">
-        <f>IF(H38&lt;&gt;"",I38/H38,"")</f>
-        <v/>
-      </c>
+      <c r="I38" s="2" t="n"/>
+      <c r="J38" s="4" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Goldin</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>2020-21 Panini One and One Rookie Dual Jersey Autograph #RDJ-AED Anthony Edwards Signed Relic Rookie Card (#90/99) - PSA MINT 9, PSA/DNA GEM MT 10</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="n">
-        <v>1092.5</v>
-      </c>
-      <c r="G39" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E39" s="2" t="n"/>
+      <c r="G39" s="2" t="n"/>
       <c r="H39" s="3" t="n"/>
-      <c r="I39" s="2">
-        <f>IF(H39&lt;&gt;"",E39-H39,"")</f>
-        <v/>
-      </c>
-      <c r="J39" s="4">
-        <f>IF(H39&lt;&gt;"",I39/H39,"")</f>
-        <v/>
-      </c>
+      <c r="I39" s="2" t="n"/>
+      <c r="J39" s="4" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Goldin</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>1995-96 Upper Deck 23k Gold 50,000 Print Run Michael Jordan (#12516/50000) - PSA GEM MT 10</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="n">
-        <v>977.5</v>
-      </c>
-      <c r="G40" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E40" s="2" t="n"/>
+      <c r="G40" s="2" t="n"/>
       <c r="H40" s="3" t="n"/>
-      <c r="I40" s="2">
-        <f>IF(H40&lt;&gt;"",E40-H40,"")</f>
-        <v/>
-      </c>
-      <c r="J40" s="4">
-        <f>IF(H40&lt;&gt;"",I40/H40,"")</f>
-        <v/>
-      </c>
+      <c r="I40" s="2" t="n"/>
+      <c r="J40" s="4" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Goldin</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>2020-21 Panini Contenders Optic Veteran Seasons Ticket Autograph Orange #VT-JTA Jayson Tatum Signed Card (#06/15) - PSA GEM MT 10, PSA/DNA GEM MT 10</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="n">
-        <v>874</v>
-      </c>
-      <c r="G41" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E41" s="2" t="n"/>
+      <c r="G41" s="2" t="n"/>
       <c r="H41" s="3" t="n"/>
-      <c r="I41" s="2">
-        <f>IF(H41&lt;&gt;"",E41-H41,"")</f>
-        <v/>
-      </c>
-      <c r="J41" s="4">
-        <f>IF(H41&lt;&gt;"",I41/H41,"")</f>
-        <v/>
-      </c>
+      <c r="I41" s="2" t="n"/>
+      <c r="J41" s="4" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Goldin</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>2022-23 Panini One And One Precision Rookie Jersey Autographs Ruby '25 Black Box #PRJ-PB5 Paolo Banchero Signed Patch Rookie Card (#1/1) - Panini Encased</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="n">
-        <v>868.25</v>
-      </c>
-      <c r="G42" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E42" s="2" t="n"/>
+      <c r="G42" s="2" t="n"/>
       <c r="H42" s="3" t="n"/>
-      <c r="I42" s="2">
-        <f>IF(H42&lt;&gt;"",E42-H42,"")</f>
-        <v/>
-      </c>
-      <c r="J42" s="4">
-        <f>IF(H42&lt;&gt;"",I42/H42,"")</f>
-        <v/>
-      </c>
+      <c r="I42" s="2" t="n"/>
+      <c r="J42" s="4" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Goldin</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>2021-22 Panini Donruss Optic Fast Break Signatures Gold #FB-AEW Anthony Edwards Signed Card (#04/10) - PSA MINT 9 - Pop 3</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="n">
-        <v>868.25</v>
-      </c>
-      <c r="G43" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E43" s="2" t="n"/>
+      <c r="G43" s="2" t="n"/>
       <c r="H43" s="3" t="n"/>
-      <c r="I43" s="2">
-        <f>IF(H43&lt;&gt;"",E43-H43,"")</f>
-        <v/>
-      </c>
-      <c r="J43" s="4">
-        <f>IF(H43&lt;&gt;"",I43/H43,"")</f>
-        <v/>
-      </c>
+      <c r="I43" s="2" t="n"/>
+      <c r="J43" s="4" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Goldin</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2022 Leaf Decadence Octet Autographs #O-03 Curry/Iverson/Johnson/Lillard/West/Frazier/Dantley/Erving Multi-Signed Card (#1/4) - Leaf Encased
-</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="n">
-        <v>862.5</v>
-      </c>
-      <c r="G44" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E44" s="2" t="n"/>
+      <c r="G44" s="2" t="n"/>
       <c r="H44" s="3" t="n"/>
-      <c r="I44" s="2">
-        <f>IF(H44&lt;&gt;"",E44-H44,"")</f>
-        <v/>
-      </c>
-      <c r="J44" s="4">
-        <f>IF(H44&lt;&gt;"",I44/H44,"")</f>
-        <v/>
-      </c>
+      <c r="I44" s="2" t="n"/>
+      <c r="J44" s="4" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" t="n">
-        <v>44</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Goldin</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>2024-25 Panini One and One Logoman #LM-CDY Cody Williams Logoman Patch Rookie Card (#2/5) - Panini Encased</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="n">
-        <v>833.75</v>
-      </c>
-      <c r="G45" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E45" s="2" t="n"/>
+      <c r="G45" s="2" t="n"/>
       <c r="H45" s="3" t="n"/>
-      <c r="I45" s="2">
-        <f>IF(H45&lt;&gt;"",E45-H45,"")</f>
-        <v/>
-      </c>
-      <c r="J45" s="4">
-        <f>IF(H45&lt;&gt;"",I45/H45,"")</f>
-        <v/>
-      </c>
+      <c r="I45" s="2" t="n"/>
+      <c r="J45" s="4" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" t="n">
-        <v>45</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Goldin</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>2023-24 Bowman Chrome U 2007-08 Bowman Gold #07B-22 Caitlin Clark Rookie Card (#32/50) - PSA GEM MT 10</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>2026-04-05</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="n">
-        <v>829.15</v>
-      </c>
-      <c r="G46" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E46" s="2" t="n"/>
+      <c r="G46" s="2" t="n"/>
       <c r="H46" s="3" t="n"/>
-      <c r="I46" s="2">
-        <f>IF(H46&lt;&gt;"",E46-H46,"")</f>
-        <v/>
-      </c>
-      <c r="J46" s="4">
-        <f>IF(H46&lt;&gt;"",I46/H46,"")</f>
-        <v/>
-      </c>
+      <c r="I46" s="2" t="n"/>
+      <c r="J46" s="4" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Goldin</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>2017-18 Panini Noir Rookie Patch Autograph (RPA) Black and White #303 Jayson Tatum Signed Patch Rookie Card (#05/99) - Panini Encased</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="n">
-        <v>805</v>
-      </c>
-      <c r="G47" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E47" s="2" t="n"/>
+      <c r="G47" s="2" t="n"/>
       <c r="H47" s="3" t="n"/>
-      <c r="I47" s="2">
-        <f>IF(H47&lt;&gt;"",E47-H47,"")</f>
-        <v/>
-      </c>
-      <c r="J47" s="4">
-        <f>IF(H47&lt;&gt;"",I47/H47,"")</f>
-        <v/>
-      </c>
+      <c r="I47" s="2" t="n"/>
+      <c r="J47" s="4" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Goldin</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>2017-18 Panini Flawless Momentous Autographs Gold #MA-GA Giannis Antetokounmpo Signed Card (#04/10) - Panini Encased</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="n">
-        <v>776.25</v>
-      </c>
-      <c r="G48" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E48" s="2" t="n"/>
+      <c r="G48" s="2" t="n"/>
       <c r="H48" s="3" t="n"/>
-      <c r="I48" s="2">
-        <f>IF(H48&lt;&gt;"",E48-H48,"")</f>
-        <v/>
-      </c>
-      <c r="J48" s="4">
-        <f>IF(H48&lt;&gt;"",I48/H48,"")</f>
-        <v/>
-      </c>
+      <c r="I48" s="2" t="n"/>
+      <c r="J48" s="4" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Goldin</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>2017-18 Panini Flawless Premium Ink Signatures #PI-GA Giannis Antetokounmpo Signed Card (#12/25) - BGS GEM MINT 9.5, Beckett 10</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="n">
-        <v>776.25</v>
-      </c>
-      <c r="G49" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E49" s="2" t="n"/>
+      <c r="G49" s="2" t="n"/>
       <c r="H49" s="3" t="n"/>
-      <c r="I49" s="2">
-        <f>IF(H49&lt;&gt;"",E49-H49,"")</f>
-        <v/>
-      </c>
-      <c r="J49" s="4">
-        <f>IF(H49&lt;&gt;"",I49/H49,"")</f>
-        <v/>
-      </c>
+      <c r="I49" s="2" t="n"/>
+      <c r="J49" s="4" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Goldin</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>2022-23 Panini Flawless Excellence Signatures '25 Black Box #ES-CHG Chet Holmgren Signed Rookie Card (#1/1) - Panini Encased</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="n">
-        <v>776.25</v>
-      </c>
-      <c r="G50" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E50" s="2" t="n"/>
+      <c r="G50" s="2" t="n"/>
       <c r="H50" s="3" t="n"/>
-      <c r="I50" s="2">
-        <f>IF(H50&lt;&gt;"",E50-H50,"")</f>
-        <v/>
-      </c>
-      <c r="J50" s="4">
-        <f>IF(H50&lt;&gt;"",I50/H50,"")</f>
-        <v/>
-      </c>
+      <c r="I50" s="2" t="n"/>
+      <c r="J50" s="4" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Goldin</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>2025-26 Topps All Kings #AK-4 Giannis Antetokounmpo - PSA MINT 9</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="n">
-        <v>707.25</v>
-      </c>
-      <c r="G51" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E51" s="2" t="n"/>
+      <c r="G51" s="2" t="n"/>
       <c r="H51" s="3" t="n"/>
-      <c r="I51" s="2">
-        <f>IF(H51&lt;&gt;"",E51-H51,"")</f>
-        <v/>
-      </c>
-      <c r="J51" s="4">
-        <f>IF(H51&lt;&gt;"",I51/H51,"")</f>
-        <v/>
-      </c>
+      <c r="I51" s="2" t="n"/>
+      <c r="J51" s="4" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" t="n">
-        <v>51</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Goldin</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2023-24 Topps Chrome Sapphire Autograph Red Refractor #CG-TM Tyrese Maxey Signed Card (#5/5) - PSA GEM MT 10 - Pop 1 </t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="n">
-        <v>633.65</v>
-      </c>
-      <c r="G52" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E52" s="2" t="n"/>
+      <c r="G52" s="2" t="n"/>
       <c r="H52" s="3" t="n"/>
-      <c r="I52" s="2">
-        <f>IF(H52&lt;&gt;"",E52-H52,"")</f>
-        <v/>
-      </c>
-      <c r="J52" s="4">
-        <f>IF(H52&lt;&gt;"",I52/H52,"")</f>
-        <v/>
-      </c>
+      <c r="I52" s="2" t="n"/>
+      <c r="J52" s="4" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" t="n">
-        <v>52</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Goldin</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>2023-24 Panini Immaculate Collection Immaculate Legends #ILE-YM Yao Ming Signed Card (#31/49) - Panini Encased</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="n">
-        <v>575</v>
-      </c>
-      <c r="G53" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E53" s="2" t="n"/>
+      <c r="G53" s="2" t="n"/>
       <c r="H53" s="3" t="n"/>
-      <c r="I53" s="2">
-        <f>IF(H53&lt;&gt;"",E53-H53,"")</f>
-        <v/>
-      </c>
-      <c r="J53" s="4">
-        <f>IF(H53&lt;&gt;"",I53/H53,"")</f>
-        <v/>
-      </c>
+      <c r="I53" s="2" t="n"/>
+      <c r="J53" s="4" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" t="n">
-        <v>53</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Goldin</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>2019-20 Panini Opulence City of Gold Signatures Gold #CG-NJ Nikola Jokic Signed Card (#10/25) - Panini Encased</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="n">
-        <v>575</v>
-      </c>
-      <c r="G54" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E54" s="2" t="n"/>
+      <c r="G54" s="2" t="n"/>
       <c r="H54" s="3" t="n"/>
-      <c r="I54" s="2">
-        <f>IF(H54&lt;&gt;"",E54-H54,"")</f>
-        <v/>
-      </c>
-      <c r="J54" s="4">
-        <f>IF(H54&lt;&gt;"",I54/H54,"")</f>
-        <v/>
-      </c>
+      <c r="I54" s="2" t="n"/>
+      <c r="J54" s="4" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" t="n">
-        <v>54</v>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Goldin</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>2011-2012 Upper Deck Exquisite Collection Personal Touch #PTC-VC Vince Carter Signed Card (#01/30) - BGS MINT 9, Beckett 10</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="n">
-        <v>575</v>
-      </c>
-      <c r="G55" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E55" s="2" t="n"/>
+      <c r="G55" s="2" t="n"/>
       <c r="H55" s="3" t="n"/>
-      <c r="I55" s="2">
-        <f>IF(H55&lt;&gt;"",E55-H55,"")</f>
-        <v/>
-      </c>
-      <c r="J55" s="4">
-        <f>IF(H55&lt;&gt;"",I55/H55,"")</f>
-        <v/>
-      </c>
+      <c r="I55" s="2" t="n"/>
+      <c r="J55" s="4" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" t="n">
-        <v>55</v>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Goldin</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Feb. 27, 2013 - Stephen Curry Signed Full Ticket - Golden State Warriors vs. New York Knicks - Season Highs of 54 Points and 11 3-Pointers - PSA Authentic</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="n">
-        <v>529</v>
-      </c>
-      <c r="G56" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E56" s="2" t="n"/>
+      <c r="G56" s="2" t="n"/>
       <c r="H56" s="3" t="n"/>
-      <c r="I56" s="2">
-        <f>IF(H56&lt;&gt;"",E56-H56,"")</f>
-        <v/>
-      </c>
-      <c r="J56" s="4">
-        <f>IF(H56&lt;&gt;"",I56/H56,"")</f>
-        <v/>
-      </c>
+      <c r="I56" s="2" t="n"/>
+      <c r="J56" s="4" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" t="n">
-        <v>56</v>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Goldin</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>2025 Topps Chrome Black Autograph Gold Refractor #CBA-PS Paul Skenes Signed Card (#05/50) - PSA NM-MT+ 8.5, PSA/DNA GEM MT 10</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="n">
-        <v>517.5</v>
-      </c>
-      <c r="G57" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E57" s="2" t="n"/>
+      <c r="G57" s="2" t="n"/>
       <c r="H57" s="3" t="n"/>
-      <c r="I57" s="2">
-        <f>IF(H57&lt;&gt;"",E57-H57,"")</f>
-        <v/>
-      </c>
-      <c r="J57" s="4">
-        <f>IF(H57&lt;&gt;"",I57/H57,"")</f>
-        <v/>
-      </c>
+      <c r="I57" s="2" t="n"/>
+      <c r="J57" s="4" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" t="n">
-        <v>57</v>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Goldin</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>2019-20 Panini One and One First-Team Signatures Blue #FT-FJK Nikola Jokic Signed Card (#08/49) - Panini Encased</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="n">
-        <v>517.5</v>
-      </c>
-      <c r="G58" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E58" s="2" t="n"/>
+      <c r="G58" s="2" t="n"/>
       <c r="H58" s="3" t="n"/>
-      <c r="I58" s="2">
-        <f>IF(H58&lt;&gt;"",E58-H58,"")</f>
-        <v/>
-      </c>
-      <c r="J58" s="4">
-        <f>IF(H58&lt;&gt;"",I58/H58,"")</f>
-        <v/>
-      </c>
+      <c r="I58" s="2" t="n"/>
+      <c r="J58" s="4" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" t="n">
-        <v>58</v>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Goldin</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>2021-22 Panini Chronicles Hometown Heroes Gold #HHR-CCU Cade Cunningham Signed Rookie Card (#01/10) - Panini Encased</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="n">
-        <v>494.5</v>
-      </c>
-      <c r="G59" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E59" s="2" t="n"/>
+      <c r="G59" s="2" t="n"/>
       <c r="H59" s="3" t="n"/>
-      <c r="I59" s="2">
-        <f>IF(H59&lt;&gt;"",E59-H59,"")</f>
-        <v/>
-      </c>
-      <c r="J59" s="4">
-        <f>IF(H59&lt;&gt;"",I59/H59,"")</f>
-        <v/>
-      </c>
+      <c r="I59" s="2" t="n"/>
+      <c r="J59" s="4" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" t="n">
-        <v>59</v>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Goldin</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>2023 Topps NPB Chrome Topps 2001 Orange Refractor #01-1 Yoshinobu Yamamoto (#01/25) - PSA MINT 9</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="n">
-        <v>488.75</v>
-      </c>
-      <c r="G60" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E60" s="2" t="n"/>
+      <c r="G60" s="2" t="n"/>
       <c r="H60" s="3" t="n"/>
-      <c r="I60" s="2">
-        <f>IF(H60&lt;&gt;"",E60-H60,"")</f>
-        <v/>
-      </c>
-      <c r="J60" s="4">
-        <f>IF(H60&lt;&gt;"",I60/H60,"")</f>
-        <v/>
-      </c>
+      <c r="I60" s="2" t="n"/>
+      <c r="J60" s="4" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" t="n">
-        <v>60</v>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Goldin</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>2025-26 Topps Chrome Rock Stars #RS-17 Dylan Harper Rookie Card - PSA GEM MT 10</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="n">
-        <v>485.3</v>
-      </c>
-      <c r="G61" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E61" s="2" t="n"/>
+      <c r="G61" s="2" t="n"/>
       <c r="H61" s="3" t="n"/>
-      <c r="I61" s="2">
-        <f>IF(H61&lt;&gt;"",E61-H61,"")</f>
-        <v/>
-      </c>
-      <c r="J61" s="4">
-        <f>IF(H61&lt;&gt;"",I61/H61,"")</f>
-        <v/>
-      </c>
+      <c r="I61" s="2" t="n"/>
+      <c r="J61" s="4" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" t="n">
-        <v>61</v>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Goldin</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>2019-20 Panini Prizm Sensational Swatches Prizms Orange Ice #SS-SCU Stephen Curry Signed Relic Card - BGS Authentic Sticker Autograph</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="n">
-        <v>485.3</v>
-      </c>
-      <c r="G62" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E62" s="2" t="n"/>
+      <c r="G62" s="2" t="n"/>
       <c r="H62" s="3" t="n"/>
-      <c r="I62" s="2">
-        <f>IF(H62&lt;&gt;"",E62-H62,"")</f>
-        <v/>
-      </c>
-      <c r="J62" s="4">
-        <f>IF(H62&lt;&gt;"",I62/H62,"")</f>
-        <v/>
-      </c>
+      <c r="I62" s="2" t="n"/>
+      <c r="J62" s="4" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" t="n">
-        <v>62</v>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Goldin</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>2009-10 Upper Deck SP Game Used 3 Star Swatches #3S-BMJ Kobe Bryant/LeBron James/Oscar Robertson Relic Card (#182/299) - BGS NM-MT 8</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="n">
-        <v>440.45</v>
-      </c>
-      <c r="G63" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E63" s="2" t="n"/>
+      <c r="G63" s="2" t="n"/>
       <c r="H63" s="3" t="n"/>
-      <c r="I63" s="2">
-        <f>IF(H63&lt;&gt;"",E63-H63,"")</f>
-        <v/>
-      </c>
-      <c r="J63" s="4">
-        <f>IF(H63&lt;&gt;"",I63/H63,"")</f>
-        <v/>
-      </c>
+      <c r="I63" s="2" t="n"/>
+      <c r="J63" s="4" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" t="n">
-        <v>63</v>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Goldin</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Stephen Curry Signed Trading Card - PSA/DNA Authentic</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="n">
-        <v>380.65</v>
-      </c>
-      <c r="G64" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E64" s="2" t="n"/>
+      <c r="G64" s="2" t="n"/>
       <c r="H64" s="3" t="n"/>
-      <c r="I64" s="2">
-        <f>IF(H64&lt;&gt;"",E64-H64,"")</f>
-        <v/>
-      </c>
-      <c r="J64" s="4">
-        <f>IF(H64&lt;&gt;"",I64/H64,"")</f>
-        <v/>
-      </c>
+      <c r="I64" s="2" t="n"/>
+      <c r="J64" s="4" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" t="n">
-        <v>64</v>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Goldin</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>2025 Topps Five Star Pentamerous Penmanship #PP-RS Roki Sasaki Signed Rookie Card (#20/25) - Topps Encased</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="n">
-        <v>379.5</v>
-      </c>
-      <c r="G65" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E65" s="2" t="n"/>
+      <c r="G65" s="2" t="n"/>
       <c r="H65" s="3" t="n"/>
-      <c r="I65" s="2">
-        <f>IF(H65&lt;&gt;"",E65-H65,"")</f>
-        <v/>
-      </c>
-      <c r="J65" s="4">
-        <f>IF(H65&lt;&gt;"",I65/H65,"")</f>
-        <v/>
-      </c>
+      <c r="I65" s="2" t="n"/>
+      <c r="J65" s="4" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" t="n">
-        <v>65</v>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Goldin</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>2024-25 Panini Instant NIL Autographs #VJED-1 VJ Edgecombe Signed Rookie Card (#08/99) - Panini Encased</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>2026-04-05</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="n">
-        <v>373.75</v>
-      </c>
-      <c r="G66" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E66" s="2" t="n"/>
+      <c r="G66" s="2" t="n"/>
       <c r="H66" s="3" t="n"/>
-      <c r="I66" s="2">
-        <f>IF(H66&lt;&gt;"",E66-H66,"")</f>
-        <v/>
-      </c>
-      <c r="J66" s="4">
-        <f>IF(H66&lt;&gt;"",I66/H66,"")</f>
-        <v/>
-      </c>
+      <c r="I66" s="2" t="n"/>
+      <c r="J66" s="4" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" t="n">
-        <v>66</v>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Goldin</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>1997-98 Fleer Hoops 23k Gold Basketball Texture Bulls Starting Five - PSA GEM MT 10</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="n">
-        <v>330.05</v>
-      </c>
-      <c r="G67" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E67" s="2" t="n"/>
+      <c r="G67" s="2" t="n"/>
       <c r="H67" s="3" t="n"/>
-      <c r="I67" s="2">
-        <f>IF(H67&lt;&gt;"",E67-H67,"")</f>
-        <v/>
-      </c>
-      <c r="J67" s="4">
-        <f>IF(H67&lt;&gt;"",I67/H67,"")</f>
-        <v/>
-      </c>
+      <c r="I67" s="2" t="n"/>
+      <c r="J67" s="4" t="n"/>
     </row>
     <row r="68">
-      <c r="A68" t="n">
-        <v>67</v>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Goldin</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>1996-97 Upper Deck Michael Jordan Greater Heights #GH6 Michael Jordan - BGS GEM MINT 9.5</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="n">
-        <v>316.25</v>
-      </c>
-      <c r="G68" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E68" s="2" t="n"/>
+      <c r="G68" s="2" t="n"/>
       <c r="H68" s="3" t="n"/>
-      <c r="I68" s="2">
-        <f>IF(H68&lt;&gt;"",E68-H68,"")</f>
-        <v/>
-      </c>
-      <c r="J68" s="4">
-        <f>IF(H68&lt;&gt;"",I68/H68,"")</f>
-        <v/>
-      </c>
+      <c r="I68" s="2" t="n"/>
+      <c r="J68" s="4" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" t="n">
-        <v>68</v>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Goldin</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>2024-25 Panini NSCC VIP Gold Color Blast #EH Erling Haaland (#16/44) - PSA MINT 9</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="n">
-        <v>293.25</v>
-      </c>
-      <c r="G69" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E69" s="2" t="n"/>
+      <c r="G69" s="2" t="n"/>
       <c r="H69" s="3" t="n"/>
-      <c r="I69" s="2">
-        <f>IF(H69&lt;&gt;"",E69-H69,"")</f>
-        <v/>
-      </c>
-      <c r="J69" s="4">
-        <f>IF(H69&lt;&gt;"",I69/H69,"")</f>
-        <v/>
-      </c>
+      <c r="I69" s="2" t="n"/>
+      <c r="J69" s="4" t="n"/>
     </row>
     <row r="70">
-      <c r="A70" t="n">
-        <v>69</v>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Goldin</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>2014-15 Panini Flawless Association Autographs Gold #AA-JE Julius Erving Signed Card (#03/10) - BGS NM-MT 8</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="n">
-        <v>292.1</v>
-      </c>
-      <c r="G70" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E70" s="2" t="n"/>
+      <c r="G70" s="2" t="n"/>
       <c r="H70" s="3" t="n"/>
-      <c r="I70" s="2">
-        <f>IF(H70&lt;&gt;"",E70-H70,"")</f>
-        <v/>
-      </c>
-      <c r="J70" s="4">
-        <f>IF(H70&lt;&gt;"",I70/H70,"")</f>
-        <v/>
-      </c>
+      <c r="I70" s="2" t="n"/>
+      <c r="J70" s="4" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" t="n">
-        <v>70</v>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Goldin</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>2019-20 Panini Immaculate Collection Shadowbox Signatures '25 Black Box #SS-VCT Vince Carter Signed Card (#1/1) - Panini Encased</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="E71" s="2" t="n">
-        <v>281.75</v>
-      </c>
-      <c r="G71" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E71" s="2" t="n"/>
+      <c r="G71" s="2" t="n"/>
       <c r="H71" s="3" t="n"/>
-      <c r="I71" s="2">
-        <f>IF(H71&lt;&gt;"",E71-H71,"")</f>
-        <v/>
-      </c>
-      <c r="J71" s="4">
-        <f>IF(H71&lt;&gt;"",I71/H71,"")</f>
-        <v/>
-      </c>
+      <c r="I71" s="2" t="n"/>
+      <c r="J71" s="4" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" t="n">
-        <v>71</v>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Goldin</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>2024-25 Panini Flawless Vault Memorabilia #FVM-KAT Karl-Anthony Towns Patch Card (#12/25) - PSA NM-MT 8</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="n">
-        <v>247.25</v>
-      </c>
-      <c r="G72" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E72" s="2" t="n"/>
+      <c r="G72" s="2" t="n"/>
       <c r="H72" s="3" t="n"/>
-      <c r="I72" s="2">
-        <f>IF(H72&lt;&gt;"",E72-H72,"")</f>
-        <v/>
-      </c>
-      <c r="J72" s="4">
-        <f>IF(H72&lt;&gt;"",I72/H72,"")</f>
-        <v/>
-      </c>
+      <c r="I72" s="2" t="n"/>
+      <c r="J72" s="4" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" t="n">
-        <v>72</v>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Goldin</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>2013-14 Upper Deck All-Time Greats Signatures #ATG-J02 Magic Johnson Signed Card (#16/50) - BGS GEM MINT 9.5</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="n">
-        <v>235.75</v>
-      </c>
-      <c r="G73" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E73" s="2" t="n"/>
+      <c r="G73" s="2" t="n"/>
       <c r="H73" s="3" t="n"/>
-      <c r="I73" s="2">
-        <f>IF(H73&lt;&gt;"",E73-H73,"")</f>
-        <v/>
-      </c>
-      <c r="J73" s="4">
-        <f>IF(H73&lt;&gt;"",I73/H73,"")</f>
-        <v/>
-      </c>
+      <c r="I73" s="2" t="n"/>
+      <c r="J73" s="4" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" t="n">
-        <v>73</v>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Goldin</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>2020-21 Panini Donruss Optic Signature Series #SS-LBL LaMelo Ball Signed Rookie Card - PSA Authentic, PSA/DNA GEM MT 10</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="E74" s="2" t="n">
-        <v>195.5</v>
-      </c>
-      <c r="G74" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E74" s="2" t="n"/>
+      <c r="G74" s="2" t="n"/>
       <c r="H74" s="3" t="n"/>
-      <c r="I74" s="2">
-        <f>IF(H74&lt;&gt;"",E74-H74,"")</f>
-        <v/>
-      </c>
-      <c r="J74" s="4">
-        <f>IF(H74&lt;&gt;"",I74/H74,"")</f>
-        <v/>
-      </c>
+      <c r="I74" s="2" t="n"/>
+      <c r="J74" s="4" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" t="n">
-        <v>74</v>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Goldin</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>2024-25 Topps Deluxe Manchester United Speak of the Devil Autograph Orange Refractor #SD-ZA Zlatan Ibrahimovic Signed Card (#07/25) - PSA MINT 9 - Pop 4</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="n">
-        <v>178.25</v>
-      </c>
-      <c r="G75" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E75" s="2" t="n"/>
+      <c r="G75" s="2" t="n"/>
       <c r="H75" s="3" t="n"/>
-      <c r="I75" s="2">
-        <f>IF(H75&lt;&gt;"",E75-H75,"")</f>
-        <v/>
-      </c>
-      <c r="J75" s="4">
-        <f>IF(H75&lt;&gt;"",I75/H75,"")</f>
-        <v/>
-      </c>
+      <c r="I75" s="2" t="n"/>
+      <c r="J75" s="4" t="n"/>
     </row>
     <row r="76">
-      <c r="A76" t="n">
-        <v>75</v>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Goldin</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>2022-23 Panini Recon Rookie Recon Signatures Purple #RRS-PBC Paolo Banchero Signed Rookie Card (#12/25) - PSA NM-MT 8, PSA/DNA GEM MT 10</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="E76" s="2" t="n">
-        <v>149.5</v>
-      </c>
-      <c r="G76" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E76" s="2" t="n"/>
+      <c r="G76" s="2" t="n"/>
       <c r="H76" s="3" t="n"/>
-      <c r="I76" s="2">
-        <f>IF(H76&lt;&gt;"",E76-H76,"")</f>
-        <v/>
-      </c>
-      <c r="J76" s="4">
-        <f>IF(H76&lt;&gt;"",I76/H76,"")</f>
-        <v/>
-      </c>
+      <c r="I76" s="2" t="n"/>
+      <c r="J76" s="4" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" t="n">
-        <v>76</v>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Goldin</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>2025-26 Topps Rise To Stardom Black Rainbow #RTS-3 VJ Edgecombe Rookie Card (#01/10) - PSA NM-MT 8</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="n">
-        <v>149.5</v>
-      </c>
-      <c r="G77" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E77" s="2" t="n"/>
+      <c r="G77" s="2" t="n"/>
       <c r="H77" s="3" t="n"/>
-      <c r="I77" s="2">
-        <f>IF(H77&lt;&gt;"",E77-H77,"")</f>
-        <v/>
-      </c>
-      <c r="J77" s="4">
-        <f>IF(H77&lt;&gt;"",I77/H77,"")</f>
-        <v/>
-      </c>
+      <c r="I77" s="2" t="n"/>
+      <c r="J77" s="4" t="n"/>
     </row>
     <row r="78">
-      <c r="A78" t="n">
-        <v>77</v>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Goldin</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>2022-23 Topps Finest UCC The Man Blue Refractor #FTM-9 Lionel Messi (#072/150) - PSA MINT 9</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="n">
-        <v>138</v>
-      </c>
-      <c r="G78" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E78" s="2" t="n"/>
+      <c r="G78" s="2" t="n"/>
       <c r="H78" s="3" t="n"/>
-      <c r="I78" s="2">
-        <f>IF(H78&lt;&gt;"",E78-H78,"")</f>
-        <v/>
-      </c>
-      <c r="J78" s="4">
-        <f>IF(H78&lt;&gt;"",I78/H78,"")</f>
-        <v/>
-      </c>
+      <c r="I78" s="2" t="n"/>
+      <c r="J78" s="4" t="n"/>
     </row>
     <row r="79">
-      <c r="A79" t="n">
-        <v>78</v>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Goldin</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Mike Tyson Signed Everlast Boxing Glove - Fiterman Sports</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="E79" s="2" t="n">
-        <v>126.5</v>
-      </c>
-      <c r="G79" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E79" s="2" t="n"/>
+      <c r="G79" s="2" t="n"/>
       <c r="H79" s="3" t="n"/>
-      <c r="I79" s="2">
-        <f>IF(H79&lt;&gt;"",E79-H79,"")</f>
-        <v/>
-      </c>
-      <c r="J79" s="4">
-        <f>IF(H79&lt;&gt;"",I79/H79,"")</f>
-        <v/>
-      </c>
+      <c r="I79" s="2" t="n"/>
+      <c r="J79" s="4" t="n"/>
     </row>
     <row r="80">
-      <c r="A80" t="n">
-        <v>79</v>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Goldin</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>2012-13 Upper Deck Exquisite Collection Dimensions #D-JE Julius Erving Signed Card</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="E80" s="2" t="n">
-        <v>117.3</v>
-      </c>
-      <c r="G80" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E80" s="2" t="n"/>
+      <c r="G80" s="2" t="n"/>
       <c r="H80" s="3" t="n"/>
-      <c r="I80" s="2">
-        <f>IF(H80&lt;&gt;"",E80-H80,"")</f>
-        <v/>
-      </c>
-      <c r="J80" s="4">
-        <f>IF(H80&lt;&gt;"",I80/H80,"")</f>
-        <v/>
-      </c>
+      <c r="I80" s="2" t="n"/>
+      <c r="J80" s="4" t="n"/>
     </row>
     <row r="81">
-      <c r="A81" t="n">
-        <v>80</v>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Goldin</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>2019-20 Panini One and One Dual Jersey Autographs Purple #DJA-DAF De'Aaron Fox Signed Relic Card (#06/35) - Panini Encased</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="E81" s="2" t="n">
-        <v>75.90000000000001</v>
-      </c>
-      <c r="G81" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E81" s="2" t="n"/>
+      <c r="G81" s="2" t="n"/>
       <c r="H81" s="3" t="n"/>
-      <c r="I81" s="2">
-        <f>IF(H81&lt;&gt;"",E81-H81,"")</f>
-        <v/>
-      </c>
-      <c r="J81" s="4">
-        <f>IF(H81&lt;&gt;"",I81/H81,"")</f>
-        <v/>
-      </c>
+      <c r="I81" s="2" t="n"/>
+      <c r="J81" s="4" t="n"/>
     </row>
     <row r="82">
-      <c r="A82" t="n">
-        <v>81</v>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Goldin</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Allen Iverson Signed Trading Card - PSA/DNA Authentic</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="n">
-        <v>71.3</v>
-      </c>
-      <c r="G82" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E82" s="2" t="n"/>
+      <c r="G82" s="2" t="n"/>
       <c r="H82" s="3" t="n"/>
-      <c r="I82" s="2">
-        <f>IF(H82&lt;&gt;"",E82-H82,"")</f>
-        <v/>
-      </c>
-      <c r="J82" s="4">
-        <f>IF(H82&lt;&gt;"",I82/H82,"")</f>
-        <v/>
-      </c>
+      <c r="I82" s="2" t="n"/>
+      <c r="J82" s="4" t="n"/>
     </row>
     <row r="83">
-      <c r="A83" t="n">
-        <v>82</v>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Goldin</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>2022-23 Panini Immaculate Collection Patch Autographs Jersey Number #IPA-RGO Rudy Gobert Signed Relic Card (#06/27) - Panini Encased</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="G83" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E83" s="2" t="n"/>
+      <c r="G83" s="2" t="n"/>
       <c r="H83" s="3" t="n"/>
-      <c r="I83" s="2">
-        <f>IF(H83&lt;&gt;"",E83-H83,"")</f>
-        <v/>
-      </c>
-      <c r="J83" s="4">
-        <f>IF(H83&lt;&gt;"",I83/H83,"")</f>
-        <v/>
-      </c>
+      <c r="I83" s="2" t="n"/>
+      <c r="J83" s="4" t="n"/>
     </row>
     <row r="84"/>
     <row r="85">
-      <c r="D85" s="1" t="inlineStr">
-        <is>
-          <t>TOTALS:</t>
-        </is>
-      </c>
-      <c r="E85" s="3">
-        <f>SUM(E2:E83)</f>
-        <v/>
-      </c>
-      <c r="H85" s="3">
-        <f>SUM(H2:H83)</f>
-        <v/>
-      </c>
-      <c r="I85" s="3">
-        <f>SUM(I2:I83)</f>
-        <v/>
-      </c>
+      <c r="D85" s="1" t="n"/>
+      <c r="E85" s="3" t="n"/>
+      <c r="H85" s="3" t="n"/>
+      <c r="I85" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -23252,7 +24275,6 @@
         <v/>
       </c>
     </row>
-    <row r="141"/>
     <row r="142">
       <c r="D142" s="1" t="inlineStr">
         <is>
@@ -26597,7 +27619,6 @@
         <v/>
       </c>
     </row>
-    <row r="95"/>
     <row r="96">
       <c r="D96" s="1" t="inlineStr">
         <is>
@@ -26679,15 +27700,15 @@
         </is>
       </c>
       <c r="B4" s="2">
-        <f>'Goldin Matched'!E192</f>
+        <f>'Goldin Matched'!E265</f>
         <v/>
       </c>
       <c r="C4" s="2">
-        <f>'Goldin Matched'!J192</f>
+        <f>'Goldin Matched'!J265</f>
         <v/>
       </c>
       <c r="D4" s="2">
-        <f>'Goldin Matched'!K192</f>
+        <f>'Goldin Matched'!K265</f>
         <v/>
       </c>
       <c r="E4" s="4">
@@ -26706,11 +27727,11 @@
         <v/>
       </c>
       <c r="C5" s="2">
+        <f>'Goldin Unmatched'!G85</f>
+        <v/>
+      </c>
+      <c r="D5" s="2">
         <f>'Goldin Unmatched'!H85</f>
-        <v/>
-      </c>
-      <c r="D5" s="2">
-        <f>'Goldin Unmatched'!I85</f>
         <v/>
       </c>
       <c r="E5" s="4">

--- a/Inventory/Cross_Platform_PL.xlsx
+++ b/Inventory/Cross_Platform_PL.xlsx
@@ -9498,7 +9498,6 @@
           <t>2023-24 Topps Chrome 1972 Topps Autographs Gold Refractor #TA-VW Victor Wembanyama Signed Rookie Card (#04/50) - PSA MINT 9</t>
         </is>
       </c>
-      <c r="D193" t="inlineStr"/>
       <c r="E193" s="2" t="n">
         <v>7123.1</v>
       </c>
@@ -9541,7 +9540,6 @@
           <t>2025-26 Topps Silver Pack '80-81 Chrome Basketball Rookie Autographs Orange Refractor #80CR2-CF Cooper Flagg Signed Rookie Card (#17/25) - PSA MINT 9, PSA/DNA GEM MT 10</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr"/>
       <c r="E194" s="2" t="n">
         <v>4427.5</v>
       </c>
@@ -9584,7 +9582,6 @@
           <t>2018-19 Panini National Treasures Peerless Signatures #PS-KBR Kobe Bryant Signed Card (#03/25) - BGS MINT 9, Beckett 10</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr"/>
       <c r="E195" s="2" t="n">
         <v>4025</v>
       </c>
@@ -9627,7 +9624,6 @@
           <t>2015-16 Panini Noir Autographs Color Gold #NC-KBR Kobe Bryant Signed Card (#4/5) - PSA EX-MT 6 - Pop 1</t>
         </is>
       </c>
-      <c r="D196" t="inlineStr"/>
       <c r="E196" s="2" t="n">
         <v>3795</v>
       </c>
@@ -9670,7 +9666,6 @@
           <t>2018 Panini Kaboom! #K-NJ Neymar Jr. - PSA GEM MT 10</t>
         </is>
       </c>
-      <c r="D197" t="inlineStr"/>
       <c r="E197" s="2" t="n">
         <v>3576.5</v>
       </c>
@@ -9713,7 +9708,6 @@
           <t>2003-04 Upper Deck Top Prospects Signs of Success #SS-LJ LeBron James Signed Rookie Card - BGS MINT 9, Beckett 10</t>
         </is>
       </c>
-      <c r="D198" t="inlineStr"/>
       <c r="E198" s="2" t="n">
         <v>3047.5</v>
       </c>
@@ -9756,7 +9750,6 @@
           <t>2025-26 Topps Chrome Future Stars Autographs Green Refractor #FS-CF Cooper Flagg Signed Rookie Card (#43/99) - PSA MINT 9, PSA/DNA GEM MT 10</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr"/>
       <c r="E199" s="2" t="n">
         <v>2760</v>
       </c>
@@ -9799,7 +9792,6 @@
           <t>2023-24 Bowman U Best of 2023 Autograph Geometric Red Refractor #B23-CC Caitlin Clark Signed Rookie Card (#01/10) - PSA MINT 9, PSA/DNA GEM MT 10</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr"/>
       <c r="E200" s="2" t="n">
         <v>2645</v>
       </c>
@@ -9842,7 +9834,6 @@
           <t>2020-21 Panini Flawless Draft Gem Signatures Ruby #DG-AEW Anthony Edwards Signed Rookie Card (#15/15) - Panini Encased</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr"/>
       <c r="E201" s="2" t="n">
         <v>2601.3</v>
       </c>
@@ -9885,7 +9876,6 @@
           <t>2023-24 Topps Chrome UCC Future Stars Autographs SuperFractor #FSA-KM Kobbie Mainoo Signed Card (#1/1) - PSA NM-MT 8</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr"/>
       <c r="E202" s="2" t="n">
         <v>2472.5</v>
       </c>
@@ -9928,7 +9918,6 @@
           <t>2022-23 Bowman U Best of '22 Autographs #BOA-VW Victor Wembanyama Signed Rookie Card - PSA GEM MT 10</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr"/>
       <c r="E203" s="2" t="n">
         <v>2472.5</v>
       </c>
@@ -9971,7 +9960,6 @@
           <t>2025-26 Topps Chrome Next Stop Signatures Purple Geometric Refractor #NS-CF Cooper Flagg Signed Rookie Card (#68/75) - PSA MINT 9</t>
         </is>
       </c>
-      <c r="D204" t="inlineStr"/>
       <c r="E204" s="2" t="n">
         <v>2375.9</v>
       </c>
@@ -10015,7 +10003,6 @@
 </t>
         </is>
       </c>
-      <c r="D205" t="inlineStr"/>
       <c r="E205" s="2" t="n">
         <v>2300</v>
       </c>
@@ -10058,7 +10045,6 @@
           <t>2023-24 Topps Chrome UCC Black Lazer Autograph #BLA-LY Lamine Yamal Signed Rookie Card - PSA MINT 9, PSA/DNA GEM MT 10</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr"/>
       <c r="E206" s="2" t="n">
         <v>2242.5</v>
       </c>
@@ -10101,7 +10087,6 @@
           <t>2020-21 Panini One and One Rookie Jersey Autographs Blue #RJA-AED Anthony Edwards Signed Patch Rookie Card (#26/35) - PSA Authentic, PSA/DNA GEM MT 10</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr"/>
       <c r="E207" s="2" t="n">
         <v>2127.5</v>
       </c>
@@ -10145,7 +10130,6 @@
 </t>
         </is>
       </c>
-      <c r="D208" t="inlineStr"/>
       <c r="E208" s="2" t="n">
         <v>2070</v>
       </c>
@@ -10189,7 +10173,6 @@
 </t>
         </is>
       </c>
-      <c r="D209" t="inlineStr"/>
       <c r="E209" s="2" t="n">
         <v>2070</v>
       </c>
@@ -10232,7 +10215,6 @@
           <t>2025 Topps Five Star Golden Graphs Blue #GG-YY Yoshinobu Yamamoto Signed Card (#19/20) - Topps Encased</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr"/>
       <c r="E210" s="2" t="n">
         <v>1851.5</v>
       </c>
@@ -10275,7 +10257,6 @@
           <t>2008 Upper Deck SP Rookie Threads SP Dual Threads #TD-BJ Kobe Bryant/Michael Jordan Relic Card - BGS NM-MT+ 8.5</t>
         </is>
       </c>
-      <c r="D211" t="inlineStr"/>
       <c r="E211" s="2" t="n">
         <v>1841.15</v>
       </c>
@@ -10319,7 +10300,6 @@
 </t>
         </is>
       </c>
-      <c r="D212" t="inlineStr"/>
       <c r="E212" s="2" t="n">
         <v>1840</v>
       </c>
@@ -10362,7 +10342,6 @@
           <t>2023-24 Topps Now Autographs #VW-6A Victor Wembanyama Signed Rookie Card (#47/99) - PSA MINT 9</t>
         </is>
       </c>
-      <c r="D213" t="inlineStr"/>
       <c r="E213" s="2" t="n">
         <v>1667.5</v>
       </c>
@@ -10405,7 +10384,6 @@
           <t>2019 Topps Diamond Icons Autographs Gold #DIA-MT Mike Trout Signed Card (#1/1) - BGS GEM MINT 9.5, Beckett 10 - True Gem</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr"/>
       <c r="E214" s="2" t="n">
         <v>1610</v>
       </c>
@@ -10448,7 +10426,6 @@
           <t>2023-24 Panini Contenders Optic 1986 Tribute Autographs International Jade #86-LKD Luka Doncic Signed Card (#3/5) - Panini Encased</t>
         </is>
       </c>
-      <c r="D215" t="inlineStr"/>
       <c r="E215" s="2" t="n">
         <v>1493.85</v>
       </c>
@@ -10491,7 +10468,6 @@
           <t>2020-21 Panini National Treasures Treasured Signatures Bronze #TS-LUD Luka Doncic Signed Card (#25/25) - PSA MINT 9</t>
         </is>
       </c>
-      <c r="D216" t="inlineStr"/>
       <c r="E216" s="2" t="n">
         <v>1463.95</v>
       </c>
@@ -10534,7 +10510,6 @@
           <t>2024-25 Bowman Chrome U Final Exam Autograph #FEA-CF Cooper Flagg Signed Rookie Card - PSA GEM MT 10</t>
         </is>
       </c>
-      <c r="D217" t="inlineStr"/>
       <c r="E217" s="2" t="n">
         <v>1449</v>
       </c>
@@ -10577,7 +10552,6 @@
           <t>2022-23 Panini Immaculate Collection Scorers Club Signatures #SCS-LUD Luka Doncic Signed Card (#23/25) - PSA MINT 9</t>
         </is>
       </c>
-      <c r="D218" t="inlineStr"/>
       <c r="E218" s="2" t="n">
         <v>1392.65</v>
       </c>
@@ -10620,7 +10594,6 @@
           <t>2021-22 Topps Chrome PSG Autograph Wave Refractor #AU-KM Kylian Mbappe Signed Card (#41/50) - PSA MINT 9</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr"/>
       <c r="E219" s="2" t="n">
         <v>1389.2</v>
       </c>
@@ -10663,7 +10636,6 @@
           <t>2014-15 Panini Flawless Association Autographs Emerald #AA-GA Giannis Antetokounmpo Signed Card (#1/5) - PSA NM 7</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr"/>
       <c r="E220" s="2" t="n">
         <v>1151.15</v>
       </c>
@@ -10706,7 +10678,6 @@
           <t>2023-24 Topps Finest Masters Autograph Red/Black Vapor Geometric Refractor #MA-SC Stephen Curry Signed Card (#01/10) - Topps Sealed</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr"/>
       <c r="E221" s="2" t="n">
         <v>1150</v>
       </c>
@@ -10749,7 +10720,6 @@
           <t>2022-23 Panini Noir Autographed Prime Black and White #ANB-LUD Luka Doncic Signed Card (#17/25) - Panini Encased</t>
         </is>
       </c>
-      <c r="D222" t="inlineStr"/>
       <c r="E222" s="2" t="n">
         <v>1150</v>
       </c>
@@ -10793,7 +10763,6 @@
 </t>
         </is>
       </c>
-      <c r="D223" t="inlineStr"/>
       <c r="E223" s="2" t="n">
         <v>1150</v>
       </c>
@@ -10836,7 +10805,6 @@
           <t>2020-21 Panini National Treasures Rookie Private Signings Association #PSA-AED Anthony Edwards Signed Rookie Card - PSA MINT 9 - Pop 4</t>
         </is>
       </c>
-      <c r="D224" t="inlineStr"/>
       <c r="E224" s="2" t="n">
         <v>1150</v>
       </c>
@@ -10879,7 +10847,6 @@
           <t>2019-20 Panini One and One First-Team Signatures #FT-SCY Stephen Curry Signed Card (#08/25) - BGS MINT 9, Beckett 10 - Pop 3</t>
         </is>
       </c>
-      <c r="D225" t="inlineStr"/>
       <c r="E225" s="2" t="n">
         <v>1122.4</v>
       </c>
@@ -10922,7 +10889,6 @@
           <t>2024-25 Topps Regalia Relic Signatures #RRS-SC Stephen Curry Signed Game-Used Patch Card (#03/15) - Topps Encased</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr"/>
       <c r="E226" s="2" t="n">
         <v>1104</v>
       </c>
@@ -10965,7 +10931,6 @@
           <t>2020-21 Panini One and One Rookie Dual Jersey Autograph #RDJ-AED Anthony Edwards Signed Relic Rookie Card (#90/99) - PSA MINT 9, PSA/DNA GEM MT 10</t>
         </is>
       </c>
-      <c r="D227" t="inlineStr"/>
       <c r="E227" s="2" t="n">
         <v>1092.5</v>
       </c>
@@ -11008,7 +10973,6 @@
           <t>1995-96 Upper Deck 23k Gold 50,000 Print Run Michael Jordan (#12516/50000) - PSA GEM MT 10</t>
         </is>
       </c>
-      <c r="D228" t="inlineStr"/>
       <c r="E228" s="2" t="n">
         <v>977.5</v>
       </c>
@@ -11051,7 +11015,6 @@
           <t>2020-21 Panini Contenders Optic Veteran Seasons Ticket Autograph Orange #VT-JTA Jayson Tatum Signed Card (#06/15) - PSA GEM MT 10, PSA/DNA GEM MT 10</t>
         </is>
       </c>
-      <c r="D229" t="inlineStr"/>
       <c r="E229" s="2" t="n">
         <v>874</v>
       </c>
@@ -11094,7 +11057,6 @@
           <t>2022-23 Panini One And One Precision Rookie Jersey Autographs Ruby '25 Black Box #PRJ-PB5 Paolo Banchero Signed Patch Rookie Card (#1/1) - Panini Encased</t>
         </is>
       </c>
-      <c r="D230" t="inlineStr"/>
       <c r="E230" s="2" t="n">
         <v>868.25</v>
       </c>
@@ -11137,7 +11099,6 @@
           <t>2021-22 Panini Donruss Optic Fast Break Signatures Gold #FB-AEW Anthony Edwards Signed Card (#04/10) - PSA MINT 9 - Pop 3</t>
         </is>
       </c>
-      <c r="D231" t="inlineStr"/>
       <c r="E231" s="2" t="n">
         <v>868.25</v>
       </c>
@@ -11181,7 +11142,6 @@
 </t>
         </is>
       </c>
-      <c r="D232" t="inlineStr"/>
       <c r="E232" s="2" t="n">
         <v>862.5</v>
       </c>
@@ -11224,7 +11184,6 @@
           <t>2024-25 Panini One and One Logoman #LM-CDY Cody Williams Logoman Patch Rookie Card (#2/5) - Panini Encased</t>
         </is>
       </c>
-      <c r="D233" t="inlineStr"/>
       <c r="E233" s="2" t="n">
         <v>833.75</v>
       </c>
@@ -11267,7 +11226,6 @@
           <t>2023-24 Bowman Chrome U 2007-08 Bowman Gold #07B-22 Caitlin Clark Rookie Card (#32/50) - PSA GEM MT 10</t>
         </is>
       </c>
-      <c r="D234" t="inlineStr"/>
       <c r="E234" s="2" t="n">
         <v>829.15</v>
       </c>
@@ -11310,7 +11268,6 @@
           <t>2017-18 Panini Noir Rookie Patch Autograph (RPA) Black and White #303 Jayson Tatum Signed Patch Rookie Card (#05/99) - Panini Encased</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr"/>
       <c r="E235" s="2" t="n">
         <v>805</v>
       </c>
@@ -11353,7 +11310,6 @@
           <t>2017-18 Panini Flawless Momentous Autographs Gold #MA-GA Giannis Antetokounmpo Signed Card (#04/10) - Panini Encased</t>
         </is>
       </c>
-      <c r="D236" t="inlineStr"/>
       <c r="E236" s="2" t="n">
         <v>776.25</v>
       </c>
@@ -11396,7 +11352,6 @@
           <t>2017-18 Panini Flawless Premium Ink Signatures #PI-GA Giannis Antetokounmpo Signed Card (#12/25) - BGS GEM MINT 9.5, Beckett 10</t>
         </is>
       </c>
-      <c r="D237" t="inlineStr"/>
       <c r="E237" s="2" t="n">
         <v>776.25</v>
       </c>
@@ -11439,7 +11394,6 @@
           <t>2022-23 Panini Flawless Excellence Signatures '25 Black Box #ES-CHG Chet Holmgren Signed Rookie Card (#1/1) - Panini Encased</t>
         </is>
       </c>
-      <c r="D238" t="inlineStr"/>
       <c r="E238" s="2" t="n">
         <v>776.25</v>
       </c>
@@ -11482,7 +11436,6 @@
           <t>2025-26 Topps All Kings #AK-4 Giannis Antetokounmpo - PSA MINT 9</t>
         </is>
       </c>
-      <c r="D239" t="inlineStr"/>
       <c r="E239" s="2" t="n">
         <v>707.25</v>
       </c>
@@ -11525,7 +11478,6 @@
           <t xml:space="preserve">2023-24 Topps Chrome Sapphire Autograph Red Refractor #CG-TM Tyrese Maxey Signed Card (#5/5) - PSA GEM MT 10 - Pop 1 </t>
         </is>
       </c>
-      <c r="D240" t="inlineStr"/>
       <c r="E240" s="2" t="n">
         <v>633.65</v>
       </c>
@@ -11568,7 +11520,6 @@
           <t>2023-24 Panini Immaculate Collection Immaculate Legends #ILE-YM Yao Ming Signed Card (#31/49) - Panini Encased</t>
         </is>
       </c>
-      <c r="D241" t="inlineStr"/>
       <c r="E241" s="2" t="n">
         <v>575</v>
       </c>
@@ -11611,7 +11562,6 @@
           <t>2019-20 Panini Opulence City of Gold Signatures Gold #CG-NJ Nikola Jokic Signed Card (#10/25) - Panini Encased</t>
         </is>
       </c>
-      <c r="D242" t="inlineStr"/>
       <c r="E242" s="2" t="n">
         <v>575</v>
       </c>
@@ -11654,7 +11604,6 @@
           <t>2011-2012 Upper Deck Exquisite Collection Personal Touch #PTC-VC Vince Carter Signed Card (#01/30) - BGS MINT 9, Beckett 10</t>
         </is>
       </c>
-      <c r="D243" t="inlineStr"/>
       <c r="E243" s="2" t="n">
         <v>575</v>
       </c>
@@ -11697,7 +11646,6 @@
           <t>2025 Topps Chrome Black Autograph Gold Refractor #CBA-PS Paul Skenes Signed Card (#05/50) - PSA NM-MT+ 8.5, PSA/DNA GEM MT 10</t>
         </is>
       </c>
-      <c r="D244" t="inlineStr"/>
       <c r="E244" s="2" t="n">
         <v>517.5</v>
       </c>
@@ -11740,7 +11688,6 @@
           <t>2019-20 Panini One and One First-Team Signatures Blue #FT-FJK Nikola Jokic Signed Card (#08/49) - Panini Encased</t>
         </is>
       </c>
-      <c r="D245" t="inlineStr"/>
       <c r="E245" s="2" t="n">
         <v>517.5</v>
       </c>
@@ -11783,7 +11730,6 @@
           <t>2021-22 Panini Chronicles Hometown Heroes Gold #HHR-CCU Cade Cunningham Signed Rookie Card (#01/10) - Panini Encased</t>
         </is>
       </c>
-      <c r="D246" t="inlineStr"/>
       <c r="E246" s="2" t="n">
         <v>494.5</v>
       </c>
@@ -11826,7 +11772,6 @@
           <t>2023 Topps NPB Chrome Topps 2001 Orange Refractor #01-1 Yoshinobu Yamamoto (#01/25) - PSA MINT 9</t>
         </is>
       </c>
-      <c r="D247" t="inlineStr"/>
       <c r="E247" s="2" t="n">
         <v>488.75</v>
       </c>
@@ -11869,7 +11814,6 @@
           <t>2025-26 Topps Chrome Rock Stars #RS-17 Dylan Harper Rookie Card - PSA GEM MT 10</t>
         </is>
       </c>
-      <c r="D248" t="inlineStr"/>
       <c r="E248" s="2" t="n">
         <v>485.3</v>
       </c>
@@ -11912,7 +11856,6 @@
           <t>2019-20 Panini Prizm Sensational Swatches Prizms Orange Ice #SS-SCU Stephen Curry Signed Relic Card - BGS Authentic Sticker Autograph</t>
         </is>
       </c>
-      <c r="D249" t="inlineStr"/>
       <c r="E249" s="2" t="n">
         <v>485.3</v>
       </c>
@@ -11955,7 +11898,6 @@
           <t>2009-10 Upper Deck SP Game Used 3 Star Swatches #3S-BMJ Kobe Bryant/LeBron James/Oscar Robertson Relic Card (#182/299) - BGS NM-MT 8</t>
         </is>
       </c>
-      <c r="D250" t="inlineStr"/>
       <c r="E250" s="2" t="n">
         <v>440.45</v>
       </c>
@@ -11998,7 +11940,6 @@
           <t>2025 Topps Five Star Pentamerous Penmanship #PP-RS Roki Sasaki Signed Rookie Card (#20/25) - Topps Encased</t>
         </is>
       </c>
-      <c r="D251" t="inlineStr"/>
       <c r="E251" s="2" t="n">
         <v>379.5</v>
       </c>
@@ -12041,7 +11982,6 @@
           <t>2024-25 Panini Instant NIL Autographs #VJED-1 VJ Edgecombe Signed Rookie Card (#08/99) - Panini Encased</t>
         </is>
       </c>
-      <c r="D252" t="inlineStr"/>
       <c r="E252" s="2" t="n">
         <v>373.75</v>
       </c>
@@ -12084,7 +12024,6 @@
           <t>1996-97 Upper Deck Michael Jordan Greater Heights #GH6 Michael Jordan - BGS GEM MINT 9.5</t>
         </is>
       </c>
-      <c r="D253" t="inlineStr"/>
       <c r="E253" s="2" t="n">
         <v>316.25</v>
       </c>
@@ -12127,7 +12066,6 @@
           <t>2024-25 Panini NSCC VIP Gold Color Blast #EH Erling Haaland (#16/44) - PSA MINT 9</t>
         </is>
       </c>
-      <c r="D254" t="inlineStr"/>
       <c r="E254" s="2" t="n">
         <v>293.25</v>
       </c>
@@ -12170,7 +12108,6 @@
           <t>2014-15 Panini Flawless Association Autographs Gold #AA-JE Julius Erving Signed Card (#03/10) - BGS NM-MT 8</t>
         </is>
       </c>
-      <c r="D255" t="inlineStr"/>
       <c r="E255" s="2" t="n">
         <v>292.1</v>
       </c>
@@ -12213,7 +12150,6 @@
           <t>2019-20 Panini Immaculate Collection Shadowbox Signatures '25 Black Box #SS-VCT Vince Carter Signed Card (#1/1) - Panini Encased</t>
         </is>
       </c>
-      <c r="D256" t="inlineStr"/>
       <c r="E256" s="2" t="n">
         <v>281.75</v>
       </c>
@@ -12256,7 +12192,6 @@
           <t>2024-25 Panini Flawless Vault Memorabilia #FVM-KAT Karl-Anthony Towns Patch Card (#12/25) - PSA NM-MT 8</t>
         </is>
       </c>
-      <c r="D257" t="inlineStr"/>
       <c r="E257" s="2" t="n">
         <v>247.25</v>
       </c>
@@ -12299,7 +12234,6 @@
           <t>2013-14 Upper Deck All-Time Greats Signatures #ATG-J02 Magic Johnson Signed Card (#16/50) - BGS GEM MINT 9.5</t>
         </is>
       </c>
-      <c r="D258" t="inlineStr"/>
       <c r="E258" s="2" t="n">
         <v>235.75</v>
       </c>
@@ -12342,7 +12276,6 @@
           <t>2020-21 Panini Donruss Optic Signature Series #SS-LBL LaMelo Ball Signed Rookie Card - PSA Authentic, PSA/DNA GEM MT 10</t>
         </is>
       </c>
-      <c r="D259" t="inlineStr"/>
       <c r="E259" s="2" t="n">
         <v>195.5</v>
       </c>
@@ -12385,7 +12318,6 @@
           <t>2022-23 Panini Recon Rookie Recon Signatures Purple #RRS-PBC Paolo Banchero Signed Rookie Card (#12/25) - PSA NM-MT 8, PSA/DNA GEM MT 10</t>
         </is>
       </c>
-      <c r="D260" t="inlineStr"/>
       <c r="E260" s="2" t="n">
         <v>149.5</v>
       </c>
@@ -12428,7 +12360,6 @@
           <t>2025-26 Topps Rise To Stardom Black Rainbow #RTS-3 VJ Edgecombe Rookie Card (#01/10) - PSA NM-MT 8</t>
         </is>
       </c>
-      <c r="D261" t="inlineStr"/>
       <c r="E261" s="2" t="n">
         <v>149.5</v>
       </c>
@@ -12471,7 +12402,6 @@
           <t>2022-23 Topps Finest UCC The Man Blue Refractor #FTM-9 Lionel Messi (#072/150) - PSA MINT 9</t>
         </is>
       </c>
-      <c r="D262" t="inlineStr"/>
       <c r="E262" s="2" t="n">
         <v>138</v>
       </c>
@@ -12514,7 +12444,6 @@
           <t>2012-13 Upper Deck Exquisite Collection Dimensions #D-JE Julius Erving Signed Card</t>
         </is>
       </c>
-      <c r="D263" t="inlineStr"/>
       <c r="E263" s="2" t="n">
         <v>117.3</v>
       </c>
@@ -12557,7 +12486,6 @@
           <t>2022-23 Panini Immaculate Collection Patch Autographs Jersey Number #IPA-RGO Rudy Gobert Signed Relic Card (#06/27) - Panini Encased</t>
         </is>
       </c>
-      <c r="D264" t="inlineStr"/>
       <c r="E264" s="2" t="n">
         <v>27.6</v>
       </c>
@@ -12688,12 +12616,13 @@
           <t>2019 Panini Flawless Triple Legends Sapphire #TL-MRG Mickey Mantle/Babe Ruth/Lou Gehrig Relic Card (#05/15) - PSA GEM MT 10 - Pop 2</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" s="2" t="n">
         <v>8051.15</v>
       </c>
       <c r="F2" s="9" t="n"/>
-      <c r="G2" s="15" t="n"/>
+      <c r="G2" s="15" t="n">
+        <v>5000</v>
+      </c>
       <c r="H2" s="3">
         <f>IF(G2&lt;&gt;"",E2-G2,"")</f>
         <v/>
@@ -12715,12 +12644,13 @@
           <t>2025 Panini Impeccable WNBA Basketball Factory-Sealed Hobby Case (3 Boxes) - Possible Paige Bueckers, Hailey Van Lith, Kiki Iriafen Rookie Cards</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" s="2" t="n">
         <v>2876.15</v>
       </c>
       <c r="F3" s="9" t="n"/>
-      <c r="G3" s="15" t="n"/>
+      <c r="G3" s="15" t="n">
+        <v>3600</v>
+      </c>
       <c r="H3" s="3">
         <f>IF(G3&lt;&gt;"",E3-G3,"")</f>
         <v/>
@@ -12742,12 +12672,13 @@
           <t>Feb. 27, 2013 - Stephen Curry Signed Full Ticket - Golden State Warriors vs. New York Knicks - Season Highs of 54 Points and 11 3-Pointers - PSA Authentic</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" s="2" t="n">
         <v>529</v>
       </c>
       <c r="F4" s="9" t="n"/>
-      <c r="G4" s="15" t="n"/>
+      <c r="G4" s="15" t="n">
+        <v>0</v>
+      </c>
       <c r="H4" s="3">
         <f>IF(G4&lt;&gt;"",E4-G4,"")</f>
         <v/>
@@ -12769,12 +12700,13 @@
           <t>Stephen Curry Signed Trading Card - PSA/DNA Authentic</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" s="2" t="n">
         <v>380.65</v>
       </c>
       <c r="F5" s="9" t="n"/>
-      <c r="G5" s="15" t="n"/>
+      <c r="G5" s="15" t="n">
+        <v>0</v>
+      </c>
       <c r="H5" s="3">
         <f>IF(G5&lt;&gt;"",E5-G5,"")</f>
         <v/>
@@ -12796,12 +12728,13 @@
           <t>1997-98 Fleer Hoops 23k Gold Basketball Texture Bulls Starting Five - PSA GEM MT 10</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" s="2" t="n">
         <v>330.05</v>
       </c>
       <c r="F6" s="9" t="n"/>
-      <c r="G6" s="15" t="n"/>
+      <c r="G6" s="15" t="n">
+        <v>0</v>
+      </c>
       <c r="H6" s="3">
         <f>IF(G6&lt;&gt;"",E6-G6,"")</f>
         <v/>
@@ -12823,12 +12756,13 @@
           <t>2024-25 Topps Deluxe Manchester United Speak of the Devil Autograph Orange Refractor #SD-ZA Zlatan Ibrahimovic Signed Card (#07/25) - PSA MINT 9 - Pop 4</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" s="2" t="n">
         <v>178.25</v>
       </c>
       <c r="F7" s="9" t="n"/>
-      <c r="G7" s="15" t="n"/>
+      <c r="G7" s="15" t="n">
+        <v>0</v>
+      </c>
       <c r="H7" s="3">
         <f>IF(G7&lt;&gt;"",E7-G7,"")</f>
         <v/>
@@ -12850,12 +12784,13 @@
           <t>Mike Tyson Signed Everlast Boxing Glove - Fiterman Sports</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" s="2" t="n">
         <v>126.5</v>
       </c>
       <c r="F8" s="9" t="n"/>
-      <c r="G8" s="15" t="n"/>
+      <c r="G8" s="15" t="n">
+        <v>0</v>
+      </c>
       <c r="H8" s="3">
         <f>IF(G8&lt;&gt;"",E8-G8,"")</f>
         <v/>
@@ -12877,12 +12812,13 @@
           <t>2019-20 Panini One and One Dual Jersey Autographs Purple #DJA-DAF De'Aaron Fox Signed Relic Card (#06/35) - Panini Encased</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" s="2" t="n">
         <v>75.90000000000001</v>
       </c>
       <c r="F9" s="9" t="n"/>
-      <c r="G9" s="15" t="n"/>
+      <c r="G9" s="15" t="n">
+        <v>0</v>
+      </c>
       <c r="H9" s="3">
         <f>IF(G9&lt;&gt;"",E9-G9,"")</f>
         <v/>
@@ -12904,12 +12840,13 @@
           <t>Allen Iverson Signed Trading Card - PSA/DNA Authentic</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" s="2" t="n">
         <v>71.3</v>
       </c>
       <c r="F10" s="9" t="n"/>
-      <c r="G10" s="15" t="n"/>
+      <c r="G10" s="15" t="n">
+        <v>0</v>
+      </c>
       <c r="H10" s="3">
         <f>IF(G10&lt;&gt;"",E10-G10,"")</f>
         <v/>
@@ -13442,7 +13379,6 @@
       <c r="I83" s="2" t="n"/>
       <c r="J83" s="4" t="n"/>
     </row>
-    <row r="84"/>
     <row r="85">
       <c r="D85" s="1" t="n"/>
       <c r="E85" s="3" t="n"/>

--- a/Inventory/Cross_Platform_PL.xlsx
+++ b/Inventory/Cross_Platform_PL.xlsx
@@ -17711,7 +17711,9 @@
       <c r="H2" t="n">
         <v>12</v>
       </c>
-      <c r="I2" s="3" t="n"/>
+      <c r="I2" s="3" t="n">
+        <v>9.56</v>
+      </c>
       <c r="J2" s="2">
         <f>IF(I2&lt;&gt;"",I2,G2)</f>
         <v/>
@@ -17758,7 +17760,9 @@
       <c r="H3" t="n">
         <v>17</v>
       </c>
-      <c r="I3" s="3" t="n"/>
+      <c r="I3" s="3" t="n">
+        <v>49.99</v>
+      </c>
       <c r="J3" s="2">
         <f>IF(I3&lt;&gt;"",I3,G3)</f>
         <v/>
@@ -17805,7 +17809,9 @@
       <c r="H4" t="n">
         <v>17</v>
       </c>
-      <c r="I4" s="3" t="n"/>
+      <c r="I4" s="3" t="n">
+        <v>1.69</v>
+      </c>
       <c r="J4" s="2">
         <f>IF(I4&lt;&gt;"",I4,G4)</f>
         <v/>
@@ -17852,7 +17858,9 @@
       <c r="H5" t="n">
         <v>15</v>
       </c>
-      <c r="I5" s="3" t="n"/>
+      <c r="I5" s="3" t="n">
+        <v>12.71</v>
+      </c>
       <c r="J5" s="2">
         <f>IF(I5&lt;&gt;"",I5,G5)</f>
         <v/>
@@ -17899,7 +17907,9 @@
       <c r="H6" t="n">
         <v>28</v>
       </c>
-      <c r="I6" s="3" t="n"/>
+      <c r="I6" s="3" t="n">
+        <v>11.14</v>
+      </c>
       <c r="J6" s="2">
         <f>IF(I6&lt;&gt;"",I6,G6)</f>
         <v/>
@@ -17946,7 +17956,9 @@
       <c r="H7" t="n">
         <v>26</v>
       </c>
-      <c r="I7" s="3" t="n"/>
+      <c r="I7" s="3" t="n">
+        <v>24.53</v>
+      </c>
       <c r="J7" s="2">
         <f>IF(I7&lt;&gt;"",I7,G7)</f>
         <v/>
@@ -17993,7 +18005,9 @@
       <c r="H8" t="n">
         <v>15</v>
       </c>
-      <c r="I8" s="3" t="n"/>
+      <c r="I8" s="3" t="n">
+        <v>23.74</v>
+      </c>
       <c r="J8" s="2">
         <f>IF(I8&lt;&gt;"",I8,G8)</f>
         <v/>
@@ -18040,7 +18054,9 @@
       <c r="H9" t="n">
         <v>19</v>
       </c>
-      <c r="I9" s="3" t="n"/>
+      <c r="I9" s="3" t="n">
+        <v>13.5</v>
+      </c>
       <c r="J9" s="2">
         <f>IF(I9&lt;&gt;"",I9,G9)</f>
         <v/>
@@ -18087,7 +18103,9 @@
       <c r="H10" t="n">
         <v>30</v>
       </c>
-      <c r="I10" s="3" t="n"/>
+      <c r="I10" s="3" t="n">
+        <v>866.25</v>
+      </c>
       <c r="J10" s="2">
         <f>IF(I10&lt;&gt;"",I10,G10)</f>
         <v/>
@@ -18134,7 +18152,9 @@
       <c r="H11" t="n">
         <v>26</v>
       </c>
-      <c r="I11" s="3" t="n"/>
+      <c r="I11" s="3" t="n">
+        <v>11.93</v>
+      </c>
       <c r="J11" s="2">
         <f>IF(I11&lt;&gt;"",I11,G11)</f>
         <v/>
@@ -18181,7 +18201,9 @@
       <c r="H12" t="n">
         <v>19</v>
       </c>
-      <c r="I12" s="3" t="n"/>
+      <c r="I12" s="3" t="n">
+        <v>122.72</v>
+      </c>
       <c r="J12" s="2">
         <f>IF(I12&lt;&gt;"",I12,G12)</f>
         <v/>
@@ -18228,7 +18250,9 @@
       <c r="H13" t="n">
         <v>29</v>
       </c>
-      <c r="I13" s="3" t="n"/>
+      <c r="I13" s="3" t="n">
+        <v>1485</v>
+      </c>
       <c r="J13" s="2">
         <f>IF(I13&lt;&gt;"",I13,G13)</f>
         <v/>
@@ -18275,7 +18299,9 @@
       <c r="H14" t="n">
         <v>30</v>
       </c>
-      <c r="I14" s="3" t="n"/>
+      <c r="I14" s="3" t="n">
+        <v>297</v>
+      </c>
       <c r="J14" s="2">
         <f>IF(I14&lt;&gt;"",I14,G14)</f>
         <v/>
@@ -18322,7 +18348,9 @@
       <c r="H15" t="n">
         <v>23</v>
       </c>
-      <c r="I15" s="3" t="n"/>
+      <c r="I15" s="3" t="n">
+        <v>6.41</v>
+      </c>
       <c r="J15" s="2">
         <f>IF(I15&lt;&gt;"",I15,G15)</f>
         <v/>
@@ -18369,7 +18397,9 @@
       <c r="H16" t="n">
         <v>19</v>
       </c>
-      <c r="I16" s="3" t="n"/>
+      <c r="I16" s="3" t="n">
+        <v>4.05</v>
+      </c>
       <c r="J16" s="2">
         <f>IF(I16&lt;&gt;"",I16,G16)</f>
         <v/>
@@ -18416,7 +18446,9 @@
       <c r="H17" t="n">
         <v>28</v>
       </c>
-      <c r="I17" s="3" t="n"/>
+      <c r="I17" s="3" t="n">
+        <v>189.75</v>
+      </c>
       <c r="J17" s="2">
         <f>IF(I17&lt;&gt;"",I17,G17)</f>
         <v/>
@@ -18463,7 +18495,9 @@
       <c r="H18" t="n">
         <v>30</v>
       </c>
-      <c r="I18" s="3" t="n"/>
+      <c r="I18" s="3" t="n">
+        <v>1.69</v>
+      </c>
       <c r="J18" s="2">
         <f>IF(I18&lt;&gt;"",I18,G18)</f>
         <v/>
@@ -18510,7 +18544,9 @@
       <c r="H19" t="n">
         <v>32</v>
       </c>
-      <c r="I19" s="3" t="n"/>
+      <c r="I19" s="3" t="n">
+        <v>1.69</v>
+      </c>
       <c r="J19" s="2">
         <f>IF(I19&lt;&gt;"",I19,G19)</f>
         <v/>
@@ -18557,7 +18593,9 @@
       <c r="H20" t="n">
         <v>34</v>
       </c>
-      <c r="I20" s="3" t="n"/>
+      <c r="I20" s="3" t="n">
+        <v>11.02</v>
+      </c>
       <c r="J20" s="2">
         <f>IF(I20&lt;&gt;"",I20,G20)</f>
         <v/>
@@ -18604,7 +18642,9 @@
       <c r="H21" t="n">
         <v>25</v>
       </c>
-      <c r="I21" s="3" t="n"/>
+      <c r="I21" s="3" t="n">
+        <v>142.88</v>
+      </c>
       <c r="J21" s="2">
         <f>IF(I21&lt;&gt;"",I21,G21)</f>
         <v/>
@@ -18651,7 +18691,9 @@
       <c r="H22" t="n">
         <v>25</v>
       </c>
-      <c r="I22" s="3" t="n"/>
+      <c r="I22" s="3" t="n">
+        <v>228.75</v>
+      </c>
       <c r="J22" s="2">
         <f>IF(I22&lt;&gt;"",I22,G22)</f>
         <v/>
@@ -18698,7 +18740,9 @@
       <c r="H23" t="n">
         <v>21</v>
       </c>
-      <c r="I23" s="3" t="n"/>
+      <c r="I23" s="3" t="n">
+        <v>7.2</v>
+      </c>
       <c r="J23" s="2">
         <f>IF(I23&lt;&gt;"",I23,G23)</f>
         <v/>
@@ -18745,7 +18789,9 @@
       <c r="H24" t="n">
         <v>26</v>
       </c>
-      <c r="I24" s="3" t="n"/>
+      <c r="I24" s="3" t="n">
+        <v>2.48</v>
+      </c>
       <c r="J24" s="2">
         <f>IF(I24&lt;&gt;"",I24,G24)</f>
         <v/>
@@ -18792,7 +18838,9 @@
       <c r="H25" t="n">
         <v>25</v>
       </c>
-      <c r="I25" s="3" t="n"/>
+      <c r="I25" s="3" t="n">
+        <v>150.94</v>
+      </c>
       <c r="J25" s="2">
         <f>IF(I25&lt;&gt;"",I25,G25)</f>
         <v/>
@@ -18839,7 +18887,9 @@
       <c r="H26" t="n">
         <v>22</v>
       </c>
-      <c r="I26" s="3" t="n"/>
+      <c r="I26" s="3" t="n">
+        <v>1.69</v>
+      </c>
       <c r="J26" s="2">
         <f>IF(I26&lt;&gt;"",I26,G26)</f>
         <v/>
@@ -18886,7 +18936,9 @@
       <c r="H27" t="n">
         <v>17</v>
       </c>
-      <c r="I27" s="3" t="n"/>
+      <c r="I27" s="3" t="n">
+        <v>3.26</v>
+      </c>
       <c r="J27" s="2">
         <f>IF(I27&lt;&gt;"",I27,G27)</f>
         <v/>
@@ -18933,7 +18985,9 @@
       <c r="H28" t="n">
         <v>17</v>
       </c>
-      <c r="I28" s="3" t="n"/>
+      <c r="I28" s="3" t="n">
+        <v>7.2</v>
+      </c>
       <c r="J28" s="2">
         <f>IF(I28&lt;&gt;"",I28,G28)</f>
         <v/>
@@ -18980,7 +19034,9 @@
       <c r="H29" t="n">
         <v>15</v>
       </c>
-      <c r="I29" s="3" t="n"/>
+      <c r="I29" s="3" t="n">
+        <v>7.2</v>
+      </c>
       <c r="J29" s="2">
         <f>IF(I29&lt;&gt;"",I29,G29)</f>
         <v/>
@@ -19027,7 +19083,9 @@
       <c r="H30" t="n">
         <v>26</v>
       </c>
-      <c r="I30" s="3" t="n"/>
+      <c r="I30" s="3" t="n">
+        <v>20.59</v>
+      </c>
       <c r="J30" s="2">
         <f>IF(I30&lt;&gt;"",I30,G30)</f>
         <v/>
@@ -19074,7 +19132,9 @@
       <c r="H31" t="n">
         <v>26</v>
       </c>
-      <c r="I31" s="3" t="n"/>
+      <c r="I31" s="3" t="n">
+        <v>16.65</v>
+      </c>
       <c r="J31" s="2">
         <f>IF(I31&lt;&gt;"",I31,G31)</f>
         <v/>
@@ -19121,7 +19181,9 @@
       <c r="H32" t="n">
         <v>21</v>
       </c>
-      <c r="I32" s="3" t="n"/>
+      <c r="I32" s="3" t="n">
+        <v>63.86</v>
+      </c>
       <c r="J32" s="2">
         <f>IF(I32&lt;&gt;"",I32,G32)</f>
         <v/>
@@ -19168,7 +19230,9 @@
       <c r="H33" t="n">
         <v>28</v>
       </c>
-      <c r="I33" s="3" t="n"/>
+      <c r="I33" s="3" t="n">
+        <v>24.41</v>
+      </c>
       <c r="J33" s="2">
         <f>IF(I33&lt;&gt;"",I33,G33)</f>
         <v/>
@@ -19215,7 +19279,9 @@
       <c r="H34" t="n">
         <v>21</v>
       </c>
-      <c r="I34" s="3" t="n"/>
+      <c r="I34" s="3" t="n">
+        <v>118.69</v>
+      </c>
       <c r="J34" s="2">
         <f>IF(I34&lt;&gt;"",I34,G34)</f>
         <v/>
@@ -19262,7 +19328,9 @@
       <c r="H35" t="n">
         <v>28</v>
       </c>
-      <c r="I35" s="3" t="n"/>
+      <c r="I35" s="3" t="n">
+        <v>28.35</v>
+      </c>
       <c r="J35" s="2">
         <f>IF(I35&lt;&gt;"",I35,G35)</f>
         <v/>
@@ -19309,7 +19377,9 @@
       <c r="H36" t="n">
         <v>22</v>
       </c>
-      <c r="I36" s="3" t="n"/>
+      <c r="I36" s="3" t="n">
+        <v>41.92</v>
+      </c>
       <c r="J36" s="2">
         <f>IF(I36&lt;&gt;"",I36,G36)</f>
         <v/>
@@ -19356,7 +19426,9 @@
       <c r="H37" t="n">
         <v>24</v>
       </c>
-      <c r="I37" s="3" t="n"/>
+      <c r="I37" s="3" t="n">
+        <v>44.51</v>
+      </c>
       <c r="J37" s="2">
         <f>IF(I37&lt;&gt;"",I37,G37)</f>
         <v/>
@@ -19403,7 +19475,9 @@
       <c r="H38" t="n">
         <v>22</v>
       </c>
-      <c r="I38" s="3" t="n"/>
+      <c r="I38" s="3" t="n">
+        <v>53.21</v>
+      </c>
       <c r="J38" s="2">
         <f>IF(I38&lt;&gt;"",I38,G38)</f>
         <v/>
@@ -19450,7 +19524,9 @@
       <c r="H39" t="n">
         <v>22</v>
       </c>
-      <c r="I39" s="3" t="n"/>
+      <c r="I39" s="3" t="n">
+        <v>598.13</v>
+      </c>
       <c r="J39" s="2">
         <f>IF(I39&lt;&gt;"",I39,G39)</f>
         <v/>
@@ -19497,7 +19573,9 @@
       <c r="H40" t="n">
         <v>28</v>
       </c>
-      <c r="I40" s="3" t="n"/>
+      <c r="I40" s="3" t="n">
+        <v>54.19</v>
+      </c>
       <c r="J40" s="2">
         <f>IF(I40&lt;&gt;"",I40,G40)</f>
         <v/>
@@ -19544,7 +19622,9 @@
       <c r="H41" t="n">
         <v>25</v>
       </c>
-      <c r="I41" s="3" t="n"/>
+      <c r="I41" s="3" t="n">
+        <v>26.88</v>
+      </c>
       <c r="J41" s="2">
         <f>IF(I41&lt;&gt;"",I41,G41)</f>
         <v/>
@@ -19591,7 +19671,9 @@
       <c r="H42" t="n">
         <v>28</v>
       </c>
-      <c r="I42" s="3" t="n"/>
+      <c r="I42" s="3" t="n">
+        <v>7.99</v>
+      </c>
       <c r="J42" s="2">
         <f>IF(I42&lt;&gt;"",I42,G42)</f>
         <v/>
@@ -19638,7 +19720,9 @@
       <c r="H43" t="n">
         <v>28</v>
       </c>
-      <c r="I43" s="3" t="n"/>
+      <c r="I43" s="3" t="n">
+        <v>129</v>
+      </c>
       <c r="J43" s="2">
         <f>IF(I43&lt;&gt;"",I43,G43)</f>
         <v/>
@@ -19685,7 +19769,9 @@
       <c r="H44" t="n">
         <v>32</v>
       </c>
-      <c r="I44" s="3" t="n"/>
+      <c r="I44" s="3" t="n">
+        <v>187.5</v>
+      </c>
       <c r="J44" s="2">
         <f>IF(I44&lt;&gt;"",I44,G44)</f>
         <v/>
@@ -19732,7 +19818,9 @@
       <c r="H45" t="n">
         <v>24</v>
       </c>
-      <c r="I45" s="3" t="n"/>
+      <c r="I45" s="3" t="n">
+        <v>90.47</v>
+      </c>
       <c r="J45" s="2">
         <f>IF(I45&lt;&gt;"",I45,G45)</f>
         <v/>
@@ -19779,7 +19867,9 @@
       <c r="H46" t="n">
         <v>17</v>
       </c>
-      <c r="I46" s="3" t="n"/>
+      <c r="I46" s="3" t="n">
+        <v>10.35</v>
+      </c>
       <c r="J46" s="2">
         <f>IF(I46&lt;&gt;"",I46,G46)</f>
         <v/>
@@ -19826,7 +19916,9 @@
       <c r="H47" t="n">
         <v>26</v>
       </c>
-      <c r="I47" s="3" t="n"/>
+      <c r="I47" s="3" t="n">
+        <v>106.59</v>
+      </c>
       <c r="J47" s="2">
         <f>IF(I47&lt;&gt;"",I47,G47)</f>
         <v/>
@@ -19873,7 +19965,9 @@
       <c r="H48" t="n">
         <v>16</v>
       </c>
-      <c r="I48" s="3" t="n"/>
+      <c r="I48" s="3" t="n">
+        <v>33.97</v>
+      </c>
       <c r="J48" s="2">
         <f>IF(I48&lt;&gt;"",I48,G48)</f>
         <v/>
@@ -19920,7 +20014,9 @@
       <c r="H49" t="n">
         <v>12</v>
       </c>
-      <c r="I49" s="3" t="n"/>
+      <c r="I49" s="3" t="n">
+        <v>14.29</v>
+      </c>
       <c r="J49" s="2">
         <f>IF(I49&lt;&gt;"",I49,G49)</f>
         <v/>
@@ -19967,7 +20063,9 @@
       <c r="H50" t="n">
         <v>24</v>
       </c>
-      <c r="I50" s="3" t="n"/>
+      <c r="I50" s="3" t="n">
+        <v>120.94</v>
+      </c>
       <c r="J50" s="2">
         <f>IF(I50&lt;&gt;"",I50,G50)</f>
         <v/>
@@ -20014,7 +20112,9 @@
       <c r="H51" t="n">
         <v>23</v>
       </c>
-      <c r="I51" s="3" t="n"/>
+      <c r="I51" s="3" t="n">
+        <v>41.29</v>
+      </c>
       <c r="J51" s="2">
         <f>IF(I51&lt;&gt;"",I51,G51)</f>
         <v/>
@@ -20061,7 +20161,9 @@
       <c r="H52" t="n">
         <v>21</v>
       </c>
-      <c r="I52" s="3" t="n"/>
+      <c r="I52" s="3" t="n">
+        <v>171</v>
+      </c>
       <c r="J52" s="2">
         <f>IF(I52&lt;&gt;"",I52,G52)</f>
         <v/>
@@ -20108,7 +20210,9 @@
       <c r="H53" t="n">
         <v>25</v>
       </c>
-      <c r="I53" s="3" t="n"/>
+      <c r="I53" s="3" t="n">
+        <v>162.75</v>
+      </c>
       <c r="J53" s="2">
         <f>IF(I53&lt;&gt;"",I53,G53)</f>
         <v/>
@@ -20155,7 +20259,9 @@
       <c r="H54" t="n">
         <v>28</v>
       </c>
-      <c r="I54" s="3" t="n"/>
+      <c r="I54" s="3" t="n">
+        <v>73.54000000000001</v>
+      </c>
       <c r="J54" s="2">
         <f>IF(I54&lt;&gt;"",I54,G54)</f>
         <v/>
@@ -20202,7 +20308,9 @@
       <c r="H55" t="n">
         <v>29</v>
       </c>
-      <c r="I55" s="3" t="n"/>
+      <c r="I55" s="3" t="n">
+        <v>33.19</v>
+      </c>
       <c r="J55" s="2">
         <f>IF(I55&lt;&gt;"",I55,G55)</f>
         <v/>
@@ -20249,7 +20357,9 @@
       <c r="H56" t="n">
         <v>28</v>
       </c>
-      <c r="I56" s="3" t="n"/>
+      <c r="I56" s="3" t="n">
+        <v>49.99</v>
+      </c>
       <c r="J56" s="2">
         <f>IF(I56&lt;&gt;"",I56,G56)</f>
         <v/>
@@ -20296,7 +20406,9 @@
       <c r="H57" t="n">
         <v>15</v>
       </c>
-      <c r="I57" s="3" t="n"/>
+      <c r="I57" s="3" t="n">
+        <v>1.69</v>
+      </c>
       <c r="J57" s="2">
         <f>IF(I57&lt;&gt;"",I57,G57)</f>
         <v/>
@@ -20343,7 +20455,9 @@
       <c r="H58" t="n">
         <v>15</v>
       </c>
-      <c r="I58" s="3" t="n"/>
+      <c r="I58" s="3" t="n">
+        <v>14.29</v>
+      </c>
       <c r="J58" s="2">
         <f>IF(I58&lt;&gt;"",I58,G58)</f>
         <v/>
@@ -20390,7 +20504,9 @@
       <c r="H59" t="n">
         <v>26</v>
       </c>
-      <c r="I59" s="3" t="n"/>
+      <c r="I59" s="3" t="n">
+        <v>41.29</v>
+      </c>
       <c r="J59" s="2">
         <f>IF(I59&lt;&gt;"",I59,G59)</f>
         <v/>
@@ -20437,7 +20553,9 @@
       <c r="H60" t="n">
         <v>28</v>
       </c>
-      <c r="I60" s="3" t="n"/>
+      <c r="I60" s="3" t="n">
+        <v>39.67</v>
+      </c>
       <c r="J60" s="2">
         <f>IF(I60&lt;&gt;"",I60,G60)</f>
         <v/>
@@ -20484,7 +20602,9 @@
       <c r="H61" t="n">
         <v>17</v>
       </c>
-      <c r="I61" s="3" t="n"/>
+      <c r="I61" s="3" t="n">
+        <v>6.41</v>
+      </c>
       <c r="J61" s="2">
         <f>IF(I61&lt;&gt;"",I61,G61)</f>
         <v/>
@@ -20531,7 +20651,9 @@
       <c r="H62" t="n">
         <v>28</v>
       </c>
-      <c r="I62" s="3" t="n"/>
+      <c r="I62" s="3" t="n">
+        <v>60.64</v>
+      </c>
       <c r="J62" s="2">
         <f>IF(I62&lt;&gt;"",I62,G62)</f>
         <v/>
@@ -20578,7 +20700,9 @@
       <c r="H63" t="n">
         <v>30</v>
       </c>
-      <c r="I63" s="3" t="n"/>
+      <c r="I63" s="3" t="n">
+        <v>16.65</v>
+      </c>
       <c r="J63" s="2">
         <f>IF(I63&lt;&gt;"",I63,G63)</f>
         <v/>
@@ -20625,7 +20749,9 @@
       <c r="H64" t="n">
         <v>32</v>
       </c>
-      <c r="I64" s="3" t="n"/>
+      <c r="I64" s="3" t="n">
+        <v>6.41</v>
+      </c>
       <c r="J64" s="2">
         <f>IF(I64&lt;&gt;"",I64,G64)</f>
         <v/>
@@ -20672,7 +20798,9 @@
       <c r="H65" t="n">
         <v>30</v>
       </c>
-      <c r="I65" s="3" t="n"/>
+      <c r="I65" s="3" t="n">
+        <v>50.96</v>
+      </c>
       <c r="J65" s="2">
         <f>IF(I65&lt;&gt;"",I65,G65)</f>
         <v/>
@@ -20719,7 +20847,9 @@
       <c r="H66" t="n">
         <v>34</v>
       </c>
-      <c r="I66" s="3" t="n"/>
+      <c r="I66" s="3" t="n">
+        <v>10.24</v>
+      </c>
       <c r="J66" s="2">
         <f>IF(I66&lt;&gt;"",I66,G66)</f>
         <v/>
@@ -20766,7 +20896,9 @@
       <c r="H67" t="n">
         <v>28</v>
       </c>
-      <c r="I67" s="3" t="n"/>
+      <c r="I67" s="3" t="n">
+        <v>34.76</v>
+      </c>
       <c r="J67" s="2">
         <f>IF(I67&lt;&gt;"",I67,G67)</f>
         <v/>
@@ -20813,7 +20945,9 @@
       <c r="H68" t="n">
         <v>32</v>
       </c>
-      <c r="I68" s="3" t="n"/>
+      <c r="I68" s="3" t="n">
+        <v>72.56</v>
+      </c>
       <c r="J68" s="2">
         <f>IF(I68&lt;&gt;"",I68,G68)</f>
         <v/>
@@ -20860,7 +20994,9 @@
       <c r="H69" t="n">
         <v>23</v>
       </c>
-      <c r="I69" s="3" t="n"/>
+      <c r="I69" s="3" t="n">
+        <v>23.74</v>
+      </c>
       <c r="J69" s="2">
         <f>IF(I69&lt;&gt;"",I69,G69)</f>
         <v/>
@@ -20907,7 +21043,9 @@
       <c r="H70" t="n">
         <v>23</v>
       </c>
-      <c r="I70" s="3" t="n"/>
+      <c r="I70" s="3" t="n">
+        <v>154.97</v>
+      </c>
       <c r="J70" s="2">
         <f>IF(I70&lt;&gt;"",I70,G70)</f>
         <v/>
@@ -20954,7 +21092,9 @@
       <c r="H71" t="n">
         <v>30</v>
       </c>
-      <c r="I71" s="3" t="n"/>
+      <c r="I71" s="3" t="n">
+        <v>75.15000000000001</v>
+      </c>
       <c r="J71" s="2">
         <f>IF(I71&lt;&gt;"",I71,G71)</f>
         <v/>
@@ -21001,7 +21141,9 @@
       <c r="H72" t="n">
         <v>19</v>
       </c>
-      <c r="I72" s="3" t="n"/>
+      <c r="I72" s="3" t="n">
+        <v>122.72</v>
+      </c>
       <c r="J72" s="2">
         <f>IF(I72&lt;&gt;"",I72,G72)</f>
         <v/>
@@ -21048,7 +21190,9 @@
       <c r="H73" t="n">
         <v>23</v>
       </c>
-      <c r="I73" s="3" t="n"/>
+      <c r="I73" s="3" t="n">
+        <v>118.69</v>
+      </c>
       <c r="J73" s="2">
         <f>IF(I73&lt;&gt;"",I73,G73)</f>
         <v/>
@@ -21095,7 +21239,9 @@
       <c r="H74" t="n">
         <v>20</v>
       </c>
-      <c r="I74" s="3" t="n"/>
+      <c r="I74" s="3" t="n">
+        <v>59.03</v>
+      </c>
       <c r="J74" s="2">
         <f>IF(I74&lt;&gt;"",I74,G74)</f>
         <v/>
@@ -21142,7 +21288,9 @@
       <c r="H75" t="n">
         <v>30</v>
       </c>
-      <c r="I75" s="3" t="n"/>
+      <c r="I75" s="3" t="n">
+        <v>41.29</v>
+      </c>
       <c r="J75" s="2">
         <f>IF(I75&lt;&gt;"",I75,G75)</f>
         <v/>
@@ -21189,7 +21337,9 @@
       <c r="H76" t="n">
         <v>26</v>
       </c>
-      <c r="I76" s="3" t="n"/>
+      <c r="I76" s="3" t="n">
+        <v>66.11</v>
+      </c>
       <c r="J76" s="2">
         <f>IF(I76&lt;&gt;"",I76,G76)</f>
         <v/>
@@ -21236,7 +21386,9 @@
       <c r="H77" t="n">
         <v>36</v>
       </c>
-      <c r="I77" s="3" t="n"/>
+      <c r="I77" s="3" t="n">
+        <v>1.69</v>
+      </c>
       <c r="J77" s="2">
         <f>IF(I77&lt;&gt;"",I77,G77)</f>
         <v/>
@@ -21283,7 +21435,9 @@
       <c r="H78" t="n">
         <v>28</v>
       </c>
-      <c r="I78" s="3" t="n"/>
+      <c r="I78" s="3" t="n">
+        <v>106.59</v>
+      </c>
       <c r="J78" s="2">
         <f>IF(I78&lt;&gt;"",I78,G78)</f>
         <v/>
@@ -21330,7 +21484,9 @@
       <c r="H79" t="n">
         <v>30</v>
       </c>
-      <c r="I79" s="3" t="n"/>
+      <c r="I79" s="3" t="n">
+        <v>10.35</v>
+      </c>
       <c r="J79" s="2">
         <f>IF(I79&lt;&gt;"",I79,G79)</f>
         <v/>
@@ -21377,7 +21533,9 @@
       <c r="H80" t="n">
         <v>28</v>
       </c>
-      <c r="I80" s="3" t="n"/>
+      <c r="I80" s="3" t="n">
+        <v>10.35</v>
+      </c>
       <c r="J80" s="2">
         <f>IF(I80&lt;&gt;"",I80,G80)</f>
         <v/>
@@ -21424,7 +21582,9 @@
       <c r="H81" t="n">
         <v>26</v>
       </c>
-      <c r="I81" s="3" t="n"/>
+      <c r="I81" s="3" t="n">
+        <v>14.29</v>
+      </c>
       <c r="J81" s="2">
         <f>IF(I81&lt;&gt;"",I81,G81)</f>
         <v/>
@@ -21471,7 +21631,9 @@
       <c r="H82" t="n">
         <v>28</v>
       </c>
-      <c r="I82" s="3" t="n"/>
+      <c r="I82" s="3" t="n">
+        <v>1.69</v>
+      </c>
       <c r="J82" s="2">
         <f>IF(I82&lt;&gt;"",I82,G82)</f>
         <v/>
@@ -21518,7 +21680,9 @@
       <c r="H83" t="n">
         <v>16</v>
       </c>
-      <c r="I83" s="3" t="n"/>
+      <c r="I83" s="3" t="n">
+        <v>133.03</v>
+      </c>
       <c r="J83" s="2">
         <f>IF(I83&lt;&gt;"",I83,G83)</f>
         <v/>
@@ -21565,7 +21729,9 @@
       <c r="H84" t="n">
         <v>12</v>
       </c>
-      <c r="I84" s="3" t="n"/>
+      <c r="I84" s="3" t="n">
+        <v>3.26</v>
+      </c>
       <c r="J84" s="2">
         <f>IF(I84&lt;&gt;"",I84,G84)</f>
         <v/>
@@ -21612,7 +21778,9 @@
       <c r="H85" t="n">
         <v>28</v>
       </c>
-      <c r="I85" s="3" t="n"/>
+      <c r="I85" s="3" t="n">
+        <v>28.46</v>
+      </c>
       <c r="J85" s="2">
         <f>IF(I85&lt;&gt;"",I85,G85)</f>
         <v/>
@@ -21659,7 +21827,9 @@
       <c r="H86" t="n">
         <v>24</v>
       </c>
-      <c r="I86" s="3" t="n"/>
+      <c r="I86" s="3" t="n">
+        <v>15.08</v>
+      </c>
       <c r="J86" s="2">
         <f>IF(I86&lt;&gt;"",I86,G86)</f>
         <v/>
@@ -21706,7 +21876,9 @@
       <c r="H87" t="n">
         <v>26</v>
       </c>
-      <c r="I87" s="3" t="n"/>
+      <c r="I87" s="3" t="n">
+        <v>9.56</v>
+      </c>
       <c r="J87" s="2">
         <f>IF(I87&lt;&gt;"",I87,G87)</f>
         <v/>
@@ -21753,7 +21925,9 @@
       <c r="H88" t="n">
         <v>27</v>
       </c>
-      <c r="I88" s="3" t="n"/>
+      <c r="I88" s="3" t="n">
+        <v>2.48</v>
+      </c>
       <c r="J88" s="2">
         <f>IF(I88&lt;&gt;"",I88,G88)</f>
         <v/>
@@ -21800,7 +21974,9 @@
       <c r="H89" t="n">
         <v>24</v>
       </c>
-      <c r="I89" s="3" t="n"/>
+      <c r="I89" s="3" t="n">
+        <v>19.01</v>
+      </c>
       <c r="J89" s="2">
         <f>IF(I89&lt;&gt;"",I89,G89)</f>
         <v/>
@@ -21847,7 +22023,9 @@
       <c r="H90" t="n">
         <v>21</v>
       </c>
-      <c r="I90" s="3" t="n"/>
+      <c r="I90" s="3" t="n">
+        <v>19.8</v>
+      </c>
       <c r="J90" s="2">
         <f>IF(I90&lt;&gt;"",I90,G90)</f>
         <v/>
@@ -21894,7 +22072,9 @@
       <c r="H91" t="n">
         <v>27</v>
       </c>
-      <c r="I91" s="3" t="n"/>
+      <c r="I91" s="3" t="n">
+        <v>7.99</v>
+      </c>
       <c r="J91" s="2">
         <f>IF(I91&lt;&gt;"",I91,G91)</f>
         <v/>
@@ -21941,7 +22121,9 @@
       <c r="H92" t="n">
         <v>27</v>
       </c>
-      <c r="I92" s="3" t="n"/>
+      <c r="I92" s="3" t="n">
+        <v>7.99</v>
+      </c>
       <c r="J92" s="2">
         <f>IF(I92&lt;&gt;"",I92,G92)</f>
         <v/>
@@ -21988,7 +22170,9 @@
       <c r="H93" t="n">
         <v>18</v>
       </c>
-      <c r="I93" s="3" t="n"/>
+      <c r="I93" s="3" t="n">
+        <v>44.51</v>
+      </c>
       <c r="J93" s="2">
         <f>IF(I93&lt;&gt;"",I93,G93)</f>
         <v/>
@@ -22035,7 +22219,9 @@
       <c r="H94" t="n">
         <v>30</v>
       </c>
-      <c r="I94" s="3" t="n"/>
+      <c r="I94" s="3" t="n">
+        <v>5.62</v>
+      </c>
       <c r="J94" s="2">
         <f>IF(I94&lt;&gt;"",I94,G94)</f>
         <v/>
@@ -22082,7 +22268,9 @@
       <c r="H95" t="n">
         <v>23</v>
       </c>
-      <c r="I95" s="3" t="n"/>
+      <c r="I95" s="3" t="n">
+        <v>11.93</v>
+      </c>
       <c r="J95" s="2">
         <f>IF(I95&lt;&gt;"",I95,G95)</f>
         <v/>
@@ -22129,7 +22317,9 @@
       <c r="H96" t="n">
         <v>30</v>
       </c>
-      <c r="I96" s="3" t="n"/>
+      <c r="I96" s="3" t="n">
+        <v>4.84</v>
+      </c>
       <c r="J96" s="2">
         <f>IF(I96&lt;&gt;"",I96,G96)</f>
         <v/>
@@ -22176,7 +22366,9 @@
       <c r="H97" t="n">
         <v>23</v>
       </c>
-      <c r="I97" s="3" t="n"/>
+      <c r="I97" s="3" t="n">
+        <v>82.42</v>
+      </c>
       <c r="J97" s="2">
         <f>IF(I97&lt;&gt;"",I97,G97)</f>
         <v/>
@@ -22223,7 +22415,9 @@
       <c r="H98" t="n">
         <v>28</v>
       </c>
-      <c r="I98" s="3" t="n"/>
+      <c r="I98" s="3" t="n">
+        <v>75.15000000000001</v>
+      </c>
       <c r="J98" s="2">
         <f>IF(I98&lt;&gt;"",I98,G98)</f>
         <v/>
@@ -22270,7 +22464,9 @@
       <c r="H99" t="n">
         <v>24</v>
       </c>
-      <c r="I99" s="3" t="n"/>
+      <c r="I99" s="3" t="n">
+        <v>26.89</v>
+      </c>
       <c r="J99" s="2">
         <f>IF(I99&lt;&gt;"",I99,G99)</f>
         <v/>
@@ -22317,7 +22513,9 @@
       <c r="H100" t="n">
         <v>29</v>
       </c>
-      <c r="I100" s="3" t="n"/>
+      <c r="I100" s="3" t="n">
+        <v>11.93</v>
+      </c>
       <c r="J100" s="2">
         <f>IF(I100&lt;&gt;"",I100,G100)</f>
         <v/>
@@ -22364,7 +22562,9 @@
       <c r="H101" t="n">
         <v>27</v>
       </c>
-      <c r="I101" s="3" t="n"/>
+      <c r="I101" s="3" t="n">
+        <v>1.69</v>
+      </c>
       <c r="J101" s="2">
         <f>IF(I101&lt;&gt;"",I101,G101)</f>
         <v/>
@@ -22411,7 +22611,9 @@
       <c r="H102" t="n">
         <v>24</v>
       </c>
-      <c r="I102" s="3" t="n"/>
+      <c r="I102" s="3" t="n">
+        <v>29.25</v>
+      </c>
       <c r="J102" s="2">
         <f>IF(I102&lt;&gt;"",I102,G102)</f>
         <v/>
@@ -22458,7 +22660,9 @@
       <c r="H103" t="n">
         <v>29</v>
       </c>
-      <c r="I103" s="3" t="n"/>
+      <c r="I103" s="3" t="n">
+        <v>14.17</v>
+      </c>
       <c r="J103" s="2">
         <f>IF(I103&lt;&gt;"",I103,G103)</f>
         <v/>
@@ -22505,7 +22709,9 @@
       <c r="H104" t="n">
         <v>27</v>
       </c>
-      <c r="I104" s="3" t="n"/>
+      <c r="I104" s="3" t="n">
+        <v>14.29</v>
+      </c>
       <c r="J104" s="2">
         <f>IF(I104&lt;&gt;"",I104,G104)</f>
         <v/>
@@ -22552,7 +22758,9 @@
       <c r="H105" t="n">
         <v>27</v>
       </c>
-      <c r="I105" s="3" t="n"/>
+      <c r="I105" s="3" t="n">
+        <v>14.29</v>
+      </c>
       <c r="J105" s="2">
         <f>IF(I105&lt;&gt;"",I105,G105)</f>
         <v/>
@@ -22599,7 +22807,9 @@
       <c r="H106" t="n">
         <v>32</v>
       </c>
-      <c r="I106" s="3" t="n"/>
+      <c r="I106" s="3" t="n">
+        <v>5.62</v>
+      </c>
       <c r="J106" s="2">
         <f>IF(I106&lt;&gt;"",I106,G106)</f>
         <v/>
@@ -22646,7 +22856,9 @@
       <c r="H107" t="n">
         <v>30</v>
       </c>
-      <c r="I107" s="3" t="n"/>
+      <c r="I107" s="3" t="n">
+        <v>9.56</v>
+      </c>
       <c r="J107" s="2">
         <f>IF(I107&lt;&gt;"",I107,G107)</f>
         <v/>
@@ -22693,7 +22905,9 @@
       <c r="H108" t="n">
         <v>27</v>
       </c>
-      <c r="I108" s="3" t="n"/>
+      <c r="I108" s="3" t="n">
+        <v>4.84</v>
+      </c>
       <c r="J108" s="2">
         <f>IF(I108&lt;&gt;"",I108,G108)</f>
         <v/>
@@ -22740,7 +22954,9 @@
       <c r="H109" t="n">
         <v>29</v>
       </c>
-      <c r="I109" s="3" t="n"/>
+      <c r="I109" s="3" t="n">
+        <v>14.96</v>
+      </c>
       <c r="J109" s="2">
         <f>IF(I109&lt;&gt;"",I109,G109)</f>
         <v/>
@@ -22787,7 +23003,9 @@
       <c r="H110" t="n">
         <v>30</v>
       </c>
-      <c r="I110" s="3" t="n"/>
+      <c r="I110" s="3" t="n">
+        <v>7.99</v>
+      </c>
       <c r="J110" s="2">
         <f>IF(I110&lt;&gt;"",I110,G110)</f>
         <v/>
@@ -22834,7 +23052,9 @@
       <c r="H111" t="n">
         <v>25</v>
       </c>
-      <c r="I111" s="3" t="n"/>
+      <c r="I111" s="3" t="n">
+        <v>7.2</v>
+      </c>
       <c r="J111" s="2">
         <f>IF(I111&lt;&gt;"",I111,G111)</f>
         <v/>
@@ -22881,7 +23101,9 @@
       <c r="H112" t="n">
         <v>25</v>
       </c>
-      <c r="I112" s="3" t="n"/>
+      <c r="I112" s="3" t="n">
+        <v>2.48</v>
+      </c>
       <c r="J112" s="2">
         <f>IF(I112&lt;&gt;"",I112,G112)</f>
         <v/>
@@ -22928,7 +23150,9 @@
       <c r="H113" t="n">
         <v>26</v>
       </c>
-      <c r="I113" s="3" t="n"/>
+      <c r="I113" s="3" t="n">
+        <v>55.8</v>
+      </c>
       <c r="J113" s="2">
         <f>IF(I113&lt;&gt;"",I113,G113)</f>
         <v/>
@@ -22975,7 +23199,9 @@
       <c r="H114" t="n">
         <v>32</v>
       </c>
-      <c r="I114" s="3" t="n"/>
+      <c r="I114" s="3" t="n">
+        <v>2.48</v>
+      </c>
       <c r="J114" s="2">
         <f>IF(I114&lt;&gt;"",I114,G114)</f>
         <v/>
@@ -23022,7 +23248,9 @@
       <c r="H115" t="n">
         <v>34</v>
       </c>
-      <c r="I115" s="3" t="n"/>
+      <c r="I115" s="3" t="n">
+        <v>110.62</v>
+      </c>
       <c r="J115" s="2">
         <f>IF(I115&lt;&gt;"",I115,G115)</f>
         <v/>
@@ -23069,7 +23297,9 @@
       <c r="H116" t="n">
         <v>30</v>
       </c>
-      <c r="I116" s="3" t="n"/>
+      <c r="I116" s="3" t="n">
+        <v>8.77</v>
+      </c>
       <c r="J116" s="2">
         <f>IF(I116&lt;&gt;"",I116,G116)</f>
         <v/>
@@ -23116,7 +23346,9 @@
       <c r="H117" t="n">
         <v>26</v>
       </c>
-      <c r="I117" s="3" t="n"/>
+      <c r="I117" s="3" t="n">
+        <v>5.62</v>
+      </c>
       <c r="J117" s="2">
         <f>IF(I117&lt;&gt;"",I117,G117)</f>
         <v/>
@@ -23163,7 +23395,9 @@
       <c r="H118" t="n">
         <v>28</v>
       </c>
-      <c r="I118" s="3" t="n"/>
+      <c r="I118" s="3" t="n">
+        <v>171</v>
+      </c>
       <c r="J118" s="2">
         <f>IF(I118&lt;&gt;"",I118,G118)</f>
         <v/>
@@ -23210,7 +23444,9 @@
       <c r="H119" t="n">
         <v>29</v>
       </c>
-      <c r="I119" s="3" t="n"/>
+      <c r="I119" s="3" t="n">
+        <v>26.1</v>
+      </c>
       <c r="J119" s="2">
         <f>IF(I119&lt;&gt;"",I119,G119)</f>
         <v/>
@@ -23257,7 +23493,9 @@
       <c r="H120" t="n">
         <v>28</v>
       </c>
-      <c r="I120" s="3" t="n"/>
+      <c r="I120" s="3" t="n">
+        <v>12.71</v>
+      </c>
       <c r="J120" s="2">
         <f>IF(I120&lt;&gt;"",I120,G120)</f>
         <v/>
@@ -23304,7 +23542,9 @@
       <c r="H121" t="n">
         <v>34</v>
       </c>
-      <c r="I121" s="3" t="n"/>
+      <c r="I121" s="3" t="n">
+        <v>5.62</v>
+      </c>
       <c r="J121" s="2">
         <f>IF(I121&lt;&gt;"",I121,G121)</f>
         <v/>
@@ -23351,7 +23591,9 @@
       <c r="H122" t="n">
         <v>27</v>
       </c>
-      <c r="I122" s="3" t="n"/>
+      <c r="I122" s="3" t="n">
+        <v>20.48</v>
+      </c>
       <c r="J122" s="2">
         <f>IF(I122&lt;&gt;"",I122,G122)</f>
         <v/>
@@ -23398,7 +23640,9 @@
       <c r="H123" t="n">
         <v>26</v>
       </c>
-      <c r="I123" s="3" t="n"/>
+      <c r="I123" s="3" t="n">
+        <v>7.2</v>
+      </c>
       <c r="J123" s="2">
         <f>IF(I123&lt;&gt;"",I123,G123)</f>
         <v/>
@@ -23445,7 +23689,9 @@
       <c r="H124" t="n">
         <v>25</v>
       </c>
-      <c r="I124" s="3" t="n"/>
+      <c r="I124" s="3" t="n">
+        <v>1.69</v>
+      </c>
       <c r="J124" s="2">
         <f>IF(I124&lt;&gt;"",I124,G124)</f>
         <v/>
@@ -23492,7 +23738,9 @@
       <c r="H125" t="n">
         <v>28</v>
       </c>
-      <c r="I125" s="3" t="n"/>
+      <c r="I125" s="3" t="n">
+        <v>21.38</v>
+      </c>
       <c r="J125" s="2">
         <f>IF(I125&lt;&gt;"",I125,G125)</f>
         <v/>
@@ -23539,7 +23787,9 @@
       <c r="H126" t="n">
         <v>28</v>
       </c>
-      <c r="I126" s="3" t="n"/>
+      <c r="I126" s="3" t="n">
+        <v>126.75</v>
+      </c>
       <c r="J126" s="2">
         <f>IF(I126&lt;&gt;"",I126,G126)</f>
         <v/>
@@ -23586,7 +23836,9 @@
       <c r="H127" t="n">
         <v>32</v>
       </c>
-      <c r="I127" s="3" t="n"/>
+      <c r="I127" s="3" t="n">
+        <v>134.81</v>
+      </c>
       <c r="J127" s="2">
         <f>IF(I127&lt;&gt;"",I127,G127)</f>
         <v/>
@@ -23633,7 +23885,9 @@
       <c r="H128" t="n">
         <v>12</v>
       </c>
-      <c r="I128" s="3" t="n"/>
+      <c r="I128" s="3" t="n">
+        <v>65.47</v>
+      </c>
       <c r="J128" s="2">
         <f>IF(I128&lt;&gt;"",I128,G128)</f>
         <v/>
@@ -23680,7 +23934,9 @@
       <c r="H129" t="n">
         <v>34</v>
       </c>
-      <c r="I129" s="3" t="n"/>
+      <c r="I129" s="3" t="n">
+        <v>65.47</v>
+      </c>
       <c r="J129" s="2">
         <f>IF(I129&lt;&gt;"",I129,G129)</f>
         <v/>
@@ -23727,7 +23983,9 @@
       <c r="H130" t="n">
         <v>17</v>
       </c>
-      <c r="I130" s="3" t="n"/>
+      <c r="I130" s="3" t="n">
+        <v>130.79</v>
+      </c>
       <c r="J130" s="2">
         <f>IF(I130&lt;&gt;"",I130,G130)</f>
         <v/>
@@ -23774,7 +24032,9 @@
       <c r="H131" t="n">
         <v>34</v>
       </c>
-      <c r="I131" s="3" t="n"/>
+      <c r="I131" s="3" t="n">
+        <v>73.54000000000001</v>
+      </c>
       <c r="J131" s="2">
         <f>IF(I131&lt;&gt;"",I131,G131)</f>
         <v/>
@@ -23821,7 +24081,9 @@
       <c r="H132" t="n">
         <v>21</v>
       </c>
-      <c r="I132" s="3" t="n"/>
+      <c r="I132" s="3" t="n">
+        <v>98.54000000000001</v>
+      </c>
       <c r="J132" s="2">
         <f>IF(I132&lt;&gt;"",I132,G132)</f>
         <v/>
@@ -23868,7 +24130,9 @@
       <c r="H133" t="n">
         <v>23</v>
       </c>
-      <c r="I133" s="3" t="n"/>
+      <c r="I133" s="3" t="n">
+        <v>204</v>
+      </c>
       <c r="J133" s="2">
         <f>IF(I133&lt;&gt;"",I133,G133)</f>
         <v/>
@@ -23915,7 +24179,9 @@
       <c r="H134" t="n">
         <v>14</v>
       </c>
-      <c r="I134" s="3" t="n"/>
+      <c r="I134" s="3" t="n">
+        <v>330</v>
+      </c>
       <c r="J134" s="2">
         <f>IF(I134&lt;&gt;"",I134,G134)</f>
         <v/>
@@ -23962,7 +24228,9 @@
       <c r="H135" t="n">
         <v>32</v>
       </c>
-      <c r="I135" s="3" t="n"/>
+      <c r="I135" s="3" t="n">
+        <v>554.63</v>
+      </c>
       <c r="J135" s="2">
         <f>IF(I135&lt;&gt;"",I135,G135)</f>
         <v/>
@@ -24009,7 +24277,9 @@
       <c r="H136" t="n">
         <v>17</v>
       </c>
-      <c r="I136" s="3" t="n"/>
+      <c r="I136" s="3" t="n">
+        <v>598.13</v>
+      </c>
       <c r="J136" s="2">
         <f>IF(I136&lt;&gt;"",I136,G136)</f>
         <v/>
@@ -24056,7 +24326,9 @@
       <c r="H137" t="n">
         <v>29</v>
       </c>
-      <c r="I137" s="3" t="n"/>
+      <c r="I137" s="3" t="n">
+        <v>556.88</v>
+      </c>
       <c r="J137" s="2">
         <f>IF(I137&lt;&gt;"",I137,G137)</f>
         <v/>
@@ -24103,7 +24375,9 @@
       <c r="H138" t="n">
         <v>22</v>
       </c>
-      <c r="I138" s="3" t="n"/>
+      <c r="I138" s="3" t="n">
+        <v>556.88</v>
+      </c>
       <c r="J138" s="2">
         <f>IF(I138&lt;&gt;"",I138,G138)</f>
         <v/>
@@ -24150,7 +24424,9 @@
       <c r="H139" t="n">
         <v>17</v>
       </c>
-      <c r="I139" s="3" t="n"/>
+      <c r="I139" s="3" t="n">
+        <v>595.88</v>
+      </c>
       <c r="J139" s="2">
         <f>IF(I139&lt;&gt;"",I139,G139)</f>
         <v/>
@@ -24197,7 +24473,9 @@
       <c r="H140" t="n">
         <v>14</v>
       </c>
-      <c r="I140" s="3" t="n"/>
+      <c r="I140" s="3" t="n">
+        <v>742.5</v>
+      </c>
       <c r="J140" s="2">
         <f>IF(I140&lt;&gt;"",I140,G140)</f>
         <v/>
@@ -24211,6 +24489,7 @@
         <v/>
       </c>
     </row>
+    <row r="141"/>
     <row r="142">
       <c r="D142" s="1" t="inlineStr">
         <is>
@@ -24325,7 +24604,9 @@
       <c r="G2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H2" s="3" t="n"/>
+      <c r="H2" s="3" t="n">
+        <v>2145</v>
+      </c>
       <c r="I2" s="2">
         <f>IF(H2&lt;&gt;"",E2-H2,"")</f>
         <v/>
@@ -24360,7 +24641,9 @@
       <c r="G3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H3" s="3" t="n"/>
+      <c r="H3" s="3" t="n">
+        <v>866.25</v>
+      </c>
       <c r="I3" s="2">
         <f>IF(H3&lt;&gt;"",E3-H3,"")</f>
         <v/>
@@ -24395,7 +24678,9 @@
       <c r="G4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H4" s="3" t="n"/>
+      <c r="H4" s="3" t="n">
+        <v>657.75</v>
+      </c>
       <c r="I4" s="2">
         <f>IF(H4&lt;&gt;"",E4-H4,"")</f>
         <v/>
@@ -24430,7 +24715,9 @@
       <c r="G5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H5" s="3" t="n"/>
+      <c r="H5" s="3" t="n">
+        <v>616.5</v>
+      </c>
       <c r="I5" s="2">
         <f>IF(H5&lt;&gt;"",E5-H5,"")</f>
         <v/>
@@ -24465,7 +24752,9 @@
       <c r="G6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H6" s="3" t="n"/>
+      <c r="H6" s="3" t="n">
+        <v>577.5</v>
+      </c>
       <c r="I6" s="2">
         <f>IF(H6&lt;&gt;"",E6-H6,"")</f>
         <v/>
@@ -24500,7 +24789,9 @@
       <c r="G7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H7" s="3" t="n"/>
+      <c r="H7" s="3" t="n">
+        <v>453.75</v>
+      </c>
       <c r="I7" s="2">
         <f>IF(H7&lt;&gt;"",E7-H7,"")</f>
         <v/>
@@ -24535,7 +24826,9 @@
       <c r="G8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H8" s="3" t="n"/>
+      <c r="H8" s="3" t="n">
+        <v>379.5</v>
+      </c>
       <c r="I8" s="2">
         <f>IF(H8&lt;&gt;"",E8-H8,"")</f>
         <v/>
@@ -24570,7 +24863,9 @@
       <c r="G9" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H9" s="3" t="n"/>
+      <c r="H9" s="3" t="n">
+        <v>261.75</v>
+      </c>
       <c r="I9" s="2">
         <f>IF(H9&lt;&gt;"",E9-H9,"")</f>
         <v/>
@@ -24605,7 +24900,9 @@
       <c r="G10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H10" s="3" t="n"/>
+      <c r="H10" s="3" t="n">
+        <v>261.75</v>
+      </c>
       <c r="I10" s="2">
         <f>IF(H10&lt;&gt;"",E10-H10,"")</f>
         <v/>
@@ -24640,7 +24937,9 @@
       <c r="G11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H11" s="3" t="n"/>
+      <c r="H11" s="3" t="n">
+        <v>253.5</v>
+      </c>
       <c r="I11" s="2">
         <f>IF(H11&lt;&gt;"",E11-H11,"")</f>
         <v/>
@@ -24675,7 +24974,9 @@
       <c r="G12" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H12" s="3" t="n"/>
+      <c r="H12" s="3" t="n">
+        <v>228.75</v>
+      </c>
       <c r="I12" s="2">
         <f>IF(H12&lt;&gt;"",E12-H12,"")</f>
         <v/>
@@ -24710,7 +25011,9 @@
       <c r="G13" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H13" s="3" t="n"/>
+      <c r="H13" s="3" t="n">
+        <v>214.5</v>
+      </c>
       <c r="I13" s="2">
         <f>IF(H13&lt;&gt;"",E13-H13,"")</f>
         <v/>
@@ -24745,7 +25048,9 @@
       <c r="G14" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H14" s="3" t="n"/>
+      <c r="H14" s="3" t="n">
+        <v>179.25</v>
+      </c>
       <c r="I14" s="2">
         <f>IF(H14&lt;&gt;"",E14-H14,"")</f>
         <v/>
@@ -24780,7 +25085,9 @@
       <c r="G15" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H15" s="3" t="n"/>
+      <c r="H15" s="3" t="n">
+        <v>173.25</v>
+      </c>
       <c r="I15" s="2">
         <f>IF(H15&lt;&gt;"",E15-H15,"")</f>
         <v/>
@@ -24815,7 +25122,9 @@
       <c r="G16" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H16" s="3" t="n"/>
+      <c r="H16" s="3" t="n">
+        <v>162.75</v>
+      </c>
       <c r="I16" s="2">
         <f>IF(H16&lt;&gt;"",E16-H16,"")</f>
         <v/>
@@ -24850,7 +25159,9 @@
       <c r="G17" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H17" s="3" t="n"/>
+      <c r="H17" s="3" t="n">
+        <v>141.09</v>
+      </c>
       <c r="I17" s="2">
         <f>IF(H17&lt;&gt;"",E17-H17,"")</f>
         <v/>
@@ -24885,7 +25196,9 @@
       <c r="G18" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H18" s="3" t="n"/>
+      <c r="H18" s="3" t="n">
+        <v>133.03</v>
+      </c>
       <c r="I18" s="2">
         <f>IF(H18&lt;&gt;"",E18-H18,"")</f>
         <v/>
@@ -24920,7 +25233,9 @@
       <c r="G19" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H19" s="3" t="n"/>
+      <c r="H19" s="3" t="n">
+        <v>126.75</v>
+      </c>
       <c r="I19" s="2">
         <f>IF(H19&lt;&gt;"",E19-H19,"")</f>
         <v/>
@@ -24955,7 +25270,9 @@
       <c r="G20" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H20" s="3" t="n"/>
+      <c r="H20" s="3" t="n">
+        <v>102.56</v>
+      </c>
       <c r="I20" s="2">
         <f>IF(H20&lt;&gt;"",E20-H20,"")</f>
         <v/>
@@ -24990,7 +25307,9 @@
       <c r="G21" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H21" s="3" t="n"/>
+      <c r="H21" s="3" t="n">
+        <v>98.53</v>
+      </c>
       <c r="I21" s="2">
         <f>IF(H21&lt;&gt;"",E21-H21,"")</f>
         <v/>
@@ -25025,7 +25344,9 @@
       <c r="G22" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H22" s="3" t="n"/>
+      <c r="H22" s="3" t="n">
+        <v>90.48</v>
+      </c>
       <c r="I22" s="2">
         <f>IF(H22&lt;&gt;"",E22-H22,"")</f>
         <v/>
@@ -25060,7 +25381,9 @@
       <c r="G23" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H23" s="3" t="n"/>
+      <c r="H23" s="3" t="n">
+        <v>86.44</v>
+      </c>
       <c r="I23" s="2">
         <f>IF(H23&lt;&gt;"",E23-H23,"")</f>
         <v/>
@@ -25095,7 +25418,9 @@
       <c r="G24" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H24" s="3" t="n"/>
+      <c r="H24" s="3" t="n">
+        <v>78.38</v>
+      </c>
       <c r="I24" s="2">
         <f>IF(H24&lt;&gt;"",E24-H24,"")</f>
         <v/>
@@ -25130,7 +25455,9 @@
       <c r="G25" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H25" s="3" t="n"/>
+      <c r="H25" s="3" t="n">
+        <v>70.31</v>
+      </c>
       <c r="I25" s="2">
         <f>IF(H25&lt;&gt;"",E25-H25,"")</f>
         <v/>
@@ -25165,7 +25492,9 @@
       <c r="G26" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H26" s="3" t="n"/>
+      <c r="H26" s="3" t="n">
+        <v>68.7</v>
+      </c>
       <c r="I26" s="2">
         <f>IF(H26&lt;&gt;"",E26-H26,"")</f>
         <v/>
@@ -25200,7 +25529,9 @@
       <c r="G27" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H27" s="3" t="n"/>
+      <c r="H27" s="3" t="n">
+        <v>68.7</v>
+      </c>
       <c r="I27" s="2">
         <f>IF(H27&lt;&gt;"",E27-H27,"")</f>
         <v/>
@@ -25235,7 +25566,9 @@
       <c r="G28" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H28" s="3" t="n"/>
+      <c r="H28" s="3" t="n">
+        <v>68.7</v>
+      </c>
       <c r="I28" s="2">
         <f>IF(H28&lt;&gt;"",E28-H28,"")</f>
         <v/>
@@ -25270,7 +25603,9 @@
       <c r="G29" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H29" s="3" t="n"/>
+      <c r="H29" s="3" t="n">
+        <v>65.47</v>
+      </c>
       <c r="I29" s="2">
         <f>IF(H29&lt;&gt;"",E29-H29,"")</f>
         <v/>
@@ -25305,7 +25640,9 @@
       <c r="G30" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H30" s="3" t="n"/>
+      <c r="H30" s="3" t="n">
+        <v>63.86</v>
+      </c>
       <c r="I30" s="2">
         <f>IF(H30&lt;&gt;"",E30-H30,"")</f>
         <v/>
@@ -25340,7 +25677,9 @@
       <c r="G31" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H31" s="3" t="n"/>
+      <c r="H31" s="3" t="n">
+        <v>59.66</v>
+      </c>
       <c r="I31" s="2">
         <f>IF(H31&lt;&gt;"",E31-H31,"")</f>
         <v/>
@@ -25375,7 +25714,9 @@
       <c r="G32" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H32" s="3" t="n"/>
+      <c r="H32" s="3" t="n">
+        <v>55.8</v>
+      </c>
       <c r="I32" s="2">
         <f>IF(H32&lt;&gt;"",E32-H32,"")</f>
         <v/>
@@ -25410,7 +25751,9 @@
       <c r="G33" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H33" s="3" t="n"/>
+      <c r="H33" s="3" t="n">
+        <v>54.19</v>
+      </c>
       <c r="I33" s="2">
         <f>IF(H33&lt;&gt;"",E33-H33,"")</f>
         <v/>
@@ -25445,7 +25788,9 @@
       <c r="G34" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H34" s="3" t="n"/>
+      <c r="H34" s="3" t="n">
+        <v>52.57</v>
+      </c>
       <c r="I34" s="2">
         <f>IF(H34&lt;&gt;"",E34-H34,"")</f>
         <v/>
@@ -25480,7 +25825,9 @@
       <c r="G35" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H35" s="3" t="n"/>
+      <c r="H35" s="3" t="n">
+        <v>52.57</v>
+      </c>
       <c r="I35" s="2">
         <f>IF(H35&lt;&gt;"",E35-H35,"")</f>
         <v/>
@@ -25515,7 +25862,9 @@
       <c r="G36" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H36" s="3" t="n"/>
+      <c r="H36" s="3" t="n">
+        <v>50.96</v>
+      </c>
       <c r="I36" s="2">
         <f>IF(H36&lt;&gt;"",E36-H36,"")</f>
         <v/>
@@ -25550,7 +25899,9 @@
       <c r="G37" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H37" s="3" t="n"/>
+      <c r="H37" s="3" t="n">
+        <v>49.99</v>
+      </c>
       <c r="I37" s="2">
         <f>IF(H37&lt;&gt;"",E37-H37,"")</f>
         <v/>
@@ -25585,7 +25936,9 @@
       <c r="G38" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H38" s="3" t="n"/>
+      <c r="H38" s="3" t="n">
+        <v>49.35</v>
+      </c>
       <c r="I38" s="2">
         <f>IF(H38&lt;&gt;"",E38-H38,"")</f>
         <v/>
@@ -25620,7 +25973,9 @@
       <c r="G39" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H39" s="3" t="n"/>
+      <c r="H39" s="3" t="n">
+        <v>48.15</v>
+      </c>
       <c r="I39" s="2">
         <f>IF(H39&lt;&gt;"",E39-H39,"")</f>
         <v/>
@@ -25655,7 +26010,9 @@
       <c r="G40" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H40" s="3" t="n"/>
+      <c r="H40" s="3" t="n">
+        <v>47.74</v>
+      </c>
       <c r="I40" s="2">
         <f>IF(H40&lt;&gt;"",E40-H40,"")</f>
         <v/>
@@ -25690,7 +26047,9 @@
       <c r="G41" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H41" s="3" t="n"/>
+      <c r="H41" s="3" t="n">
+        <v>46.12</v>
+      </c>
       <c r="I41" s="2">
         <f>IF(H41&lt;&gt;"",E41-H41,"")</f>
         <v/>
@@ -25725,7 +26084,9 @@
       <c r="G42" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H42" s="3" t="n"/>
+      <c r="H42" s="3" t="n">
+        <v>39.67</v>
+      </c>
       <c r="I42" s="2">
         <f>IF(H42&lt;&gt;"",E42-H42,"")</f>
         <v/>
@@ -25760,7 +26121,9 @@
       <c r="G43" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H43" s="3" t="n"/>
+      <c r="H43" s="3" t="n">
+        <v>39.67</v>
+      </c>
       <c r="I43" s="2">
         <f>IF(H43&lt;&gt;"",E43-H43,"")</f>
         <v/>
@@ -25795,7 +26158,9 @@
       <c r="G44" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H44" s="3" t="n"/>
+      <c r="H44" s="3" t="n">
+        <v>39.67</v>
+      </c>
       <c r="I44" s="2">
         <f>IF(H44&lt;&gt;"",E44-H44,"")</f>
         <v/>
@@ -25830,7 +26195,9 @@
       <c r="G45" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H45" s="3" t="n"/>
+      <c r="H45" s="3" t="n">
+        <v>38.06</v>
+      </c>
       <c r="I45" s="2">
         <f>IF(H45&lt;&gt;"",E45-H45,"")</f>
         <v/>
@@ -25865,7 +26232,9 @@
       <c r="G46" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H46" s="3" t="n"/>
+      <c r="H46" s="3" t="n">
+        <v>36.34</v>
+      </c>
       <c r="I46" s="2">
         <f>IF(H46&lt;&gt;"",E46-H46,"")</f>
         <v/>
@@ -25900,7 +26269,9 @@
       <c r="G47" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H47" s="3" t="n"/>
+      <c r="H47" s="3" t="n">
+        <v>35.44</v>
+      </c>
       <c r="I47" s="2">
         <f>IF(H47&lt;&gt;"",E47-H47,"")</f>
         <v/>
@@ -25935,7 +26306,9 @@
       <c r="G48" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H48" s="3" t="n"/>
+      <c r="H48" s="3" t="n">
+        <v>33.97</v>
+      </c>
       <c r="I48" s="2">
         <f>IF(H48&lt;&gt;"",E48-H48,"")</f>
         <v/>
@@ -25970,7 +26343,9 @@
       <c r="G49" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H49" s="3" t="n"/>
+      <c r="H49" s="3" t="n">
+        <v>33.19</v>
+      </c>
       <c r="I49" s="2">
         <f>IF(H49&lt;&gt;"",E49-H49,"")</f>
         <v/>
@@ -26005,7 +26380,9 @@
       <c r="G50" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H50" s="3" t="n"/>
+      <c r="H50" s="3" t="n">
+        <v>33.19</v>
+      </c>
       <c r="I50" s="2">
         <f>IF(H50&lt;&gt;"",E50-H50,"")</f>
         <v/>
@@ -26040,7 +26417,9 @@
       <c r="G51" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H51" s="3" t="n"/>
+      <c r="H51" s="3" t="n">
+        <v>32.4</v>
+      </c>
       <c r="I51" s="2">
         <f>IF(H51&lt;&gt;"",E51-H51,"")</f>
         <v/>
@@ -26075,7 +26454,9 @@
       <c r="G52" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H52" s="3" t="n"/>
+      <c r="H52" s="3" t="n">
+        <v>30.04</v>
+      </c>
       <c r="I52" s="2">
         <f>IF(H52&lt;&gt;"",E52-H52,"")</f>
         <v/>
@@ -26110,7 +26491,9 @@
       <c r="G53" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H53" s="3" t="n"/>
+      <c r="H53" s="3" t="n">
+        <v>30.04</v>
+      </c>
       <c r="I53" s="2">
         <f>IF(H53&lt;&gt;"",E53-H53,"")</f>
         <v/>
@@ -26145,7 +26528,9 @@
       <c r="G54" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H54" s="3" t="n"/>
+      <c r="H54" s="3" t="n">
+        <v>26.89</v>
+      </c>
       <c r="I54" s="2">
         <f>IF(H54&lt;&gt;"",E54-H54,"")</f>
         <v/>
@@ -26180,7 +26565,9 @@
       <c r="G55" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H55" s="3" t="n"/>
+      <c r="H55" s="3" t="n">
+        <v>26.1</v>
+      </c>
       <c r="I55" s="2">
         <f>IF(H55&lt;&gt;"",E55-H55,"")</f>
         <v/>
@@ -26215,7 +26602,9 @@
       <c r="G56" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H56" s="3" t="n"/>
+      <c r="H56" s="3" t="n">
+        <v>25.31</v>
+      </c>
       <c r="I56" s="2">
         <f>IF(H56&lt;&gt;"",E56-H56,"")</f>
         <v/>
@@ -26250,7 +26639,9 @@
       <c r="G57" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H57" s="3" t="n"/>
+      <c r="H57" s="3" t="n">
+        <v>24.53</v>
+      </c>
       <c r="I57" s="2">
         <f>IF(H57&lt;&gt;"",E57-H57,"")</f>
         <v/>
@@ -26285,7 +26676,9 @@
       <c r="G58" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H58" s="3" t="n"/>
+      <c r="H58" s="3" t="n">
+        <v>24.41</v>
+      </c>
       <c r="I58" s="2">
         <f>IF(H58&lt;&gt;"",E58-H58,"")</f>
         <v/>
@@ -26320,7 +26713,9 @@
       <c r="G59" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H59" s="3" t="n"/>
+      <c r="H59" s="3" t="n">
+        <v>23.74</v>
+      </c>
       <c r="I59" s="2">
         <f>IF(H59&lt;&gt;"",E59-H59,"")</f>
         <v/>
@@ -26355,7 +26750,9 @@
       <c r="G60" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H60" s="3" t="n"/>
+      <c r="H60" s="3" t="n">
+        <v>22.16</v>
+      </c>
       <c r="I60" s="2">
         <f>IF(H60&lt;&gt;"",E60-H60,"")</f>
         <v/>
@@ -26390,7 +26787,9 @@
       <c r="G61" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H61" s="3" t="n"/>
+      <c r="H61" s="3" t="n">
+        <v>22.16</v>
+      </c>
       <c r="I61" s="2">
         <f>IF(H61&lt;&gt;"",E61-H61,"")</f>
         <v/>
@@ -26425,7 +26824,9 @@
       <c r="G62" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H62" s="3" t="n"/>
+      <c r="H62" s="3" t="n">
+        <v>20.59</v>
+      </c>
       <c r="I62" s="2">
         <f>IF(H62&lt;&gt;"",E62-H62,"")</f>
         <v/>
@@ -26460,7 +26861,9 @@
       <c r="G63" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H63" s="3" t="n"/>
+      <c r="H63" s="3" t="n">
+        <v>20.59</v>
+      </c>
       <c r="I63" s="2">
         <f>IF(H63&lt;&gt;"",E63-H63,"")</f>
         <v/>
@@ -26495,7 +26898,9 @@
       <c r="G64" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H64" s="3" t="n"/>
+      <c r="H64" s="3" t="n">
+        <v>18.23</v>
+      </c>
       <c r="I64" s="2">
         <f>IF(H64&lt;&gt;"",E64-H64,"")</f>
         <v/>
@@ -26530,7 +26935,9 @@
       <c r="G65" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H65" s="3" t="n"/>
+      <c r="H65" s="3" t="n">
+        <v>18.23</v>
+      </c>
       <c r="I65" s="2">
         <f>IF(H65&lt;&gt;"",E65-H65,"")</f>
         <v/>
@@ -26565,7 +26972,9 @@
       <c r="G66" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H66" s="3" t="n"/>
+      <c r="H66" s="3" t="n">
+        <v>15.08</v>
+      </c>
       <c r="I66" s="2">
         <f>IF(H66&lt;&gt;"",E66-H66,"")</f>
         <v/>
@@ -26600,7 +27009,9 @@
       <c r="G67" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H67" s="3" t="n"/>
+      <c r="H67" s="3" t="n">
+        <v>14.29</v>
+      </c>
       <c r="I67" s="2">
         <f>IF(H67&lt;&gt;"",E67-H67,"")</f>
         <v/>
@@ -26635,7 +27046,9 @@
       <c r="G68" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H68" s="3" t="n"/>
+      <c r="H68" s="3" t="n">
+        <v>13.5</v>
+      </c>
       <c r="I68" s="2">
         <f>IF(H68&lt;&gt;"",E68-H68,"")</f>
         <v/>
@@ -26670,7 +27083,9 @@
       <c r="G69" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H69" s="3" t="n"/>
+      <c r="H69" s="3" t="n">
+        <v>13.5</v>
+      </c>
       <c r="I69" s="2">
         <f>IF(H69&lt;&gt;"",E69-H69,"")</f>
         <v/>
@@ -26705,7 +27120,9 @@
       <c r="G70" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H70" s="3" t="n"/>
+      <c r="H70" s="3" t="n">
+        <v>12.71</v>
+      </c>
       <c r="I70" s="2">
         <f>IF(H70&lt;&gt;"",E70-H70,"")</f>
         <v/>
@@ -26740,7 +27157,9 @@
       <c r="G71" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H71" s="3" t="n"/>
+      <c r="H71" s="3" t="n">
+        <v>12.6</v>
+      </c>
       <c r="I71" s="2">
         <f>IF(H71&lt;&gt;"",E71-H71,"")</f>
         <v/>
@@ -26775,7 +27194,9 @@
       <c r="G72" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H72" s="3" t="n"/>
+      <c r="H72" s="3" t="n">
+        <v>11.93</v>
+      </c>
       <c r="I72" s="2">
         <f>IF(H72&lt;&gt;"",E72-H72,"")</f>
         <v/>
@@ -26810,7 +27231,9 @@
       <c r="G73" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H73" s="3" t="n"/>
+      <c r="H73" s="3" t="n">
+        <v>11.14</v>
+      </c>
       <c r="I73" s="2">
         <f>IF(H73&lt;&gt;"",E73-H73,"")</f>
         <v/>
@@ -26845,7 +27268,9 @@
       <c r="G74" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H74" s="3" t="n"/>
+      <c r="H74" s="3" t="n">
+        <v>11.14</v>
+      </c>
       <c r="I74" s="2">
         <f>IF(H74&lt;&gt;"",E74-H74,"")</f>
         <v/>
@@ -26880,7 +27305,9 @@
       <c r="G75" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H75" s="3" t="n"/>
+      <c r="H75" s="3" t="n">
+        <v>10.35</v>
+      </c>
       <c r="I75" s="2">
         <f>IF(H75&lt;&gt;"",E75-H75,"")</f>
         <v/>
@@ -26915,7 +27342,9 @@
       <c r="G76" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H76" s="3" t="n"/>
+      <c r="H76" s="3" t="n">
+        <v>9.56</v>
+      </c>
       <c r="I76" s="2">
         <f>IF(H76&lt;&gt;"",E76-H76,"")</f>
         <v/>
@@ -26950,7 +27379,9 @@
       <c r="G77" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H77" s="3" t="n"/>
+      <c r="H77" s="3" t="n">
+        <v>8.77</v>
+      </c>
       <c r="I77" s="2">
         <f>IF(H77&lt;&gt;"",E77-H77,"")</f>
         <v/>
@@ -26985,7 +27416,9 @@
       <c r="G78" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H78" s="3" t="n"/>
+      <c r="H78" s="3" t="n">
+        <v>7.99</v>
+      </c>
       <c r="I78" s="2">
         <f>IF(H78&lt;&gt;"",E78-H78,"")</f>
         <v/>
@@ -27020,7 +27453,9 @@
       <c r="G79" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H79" s="3" t="n"/>
+      <c r="H79" s="3" t="n">
+        <v>7.2</v>
+      </c>
       <c r="I79" s="2">
         <f>IF(H79&lt;&gt;"",E79-H79,"")</f>
         <v/>
@@ -27055,7 +27490,9 @@
       <c r="G80" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H80" s="3" t="n"/>
+      <c r="H80" s="3" t="n">
+        <v>6.41</v>
+      </c>
       <c r="I80" s="2">
         <f>IF(H80&lt;&gt;"",E80-H80,"")</f>
         <v/>
@@ -27090,7 +27527,9 @@
       <c r="G81" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H81" s="3" t="n"/>
+      <c r="H81" s="3" t="n">
+        <v>6.41</v>
+      </c>
       <c r="I81" s="2">
         <f>IF(H81&lt;&gt;"",E81-H81,"")</f>
         <v/>
@@ -27125,7 +27564,9 @@
       <c r="G82" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H82" s="3" t="n"/>
+      <c r="H82" s="3" t="n">
+        <v>6.41</v>
+      </c>
       <c r="I82" s="2">
         <f>IF(H82&lt;&gt;"",E82-H82,"")</f>
         <v/>
@@ -27160,7 +27601,9 @@
       <c r="G83" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H83" s="3" t="n"/>
+      <c r="H83" s="3" t="n">
+        <v>5.62</v>
+      </c>
       <c r="I83" s="2">
         <f>IF(H83&lt;&gt;"",E83-H83,"")</f>
         <v/>
@@ -27195,7 +27638,9 @@
       <c r="G84" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H84" s="3" t="n"/>
+      <c r="H84" s="3" t="n">
+        <v>5.62</v>
+      </c>
       <c r="I84" s="2">
         <f>IF(H84&lt;&gt;"",E84-H84,"")</f>
         <v/>
@@ -27230,7 +27675,9 @@
       <c r="G85" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H85" s="3" t="n"/>
+      <c r="H85" s="3" t="n">
+        <v>4.05</v>
+      </c>
       <c r="I85" s="2">
         <f>IF(H85&lt;&gt;"",E85-H85,"")</f>
         <v/>
@@ -27265,7 +27712,9 @@
       <c r="G86" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H86" s="3" t="n"/>
+      <c r="H86" s="3" t="n">
+        <v>4.05</v>
+      </c>
       <c r="I86" s="2">
         <f>IF(H86&lt;&gt;"",E86-H86,"")</f>
         <v/>
@@ -27300,7 +27749,9 @@
       <c r="G87" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H87" s="3" t="n"/>
+      <c r="H87" s="3" t="n">
+        <v>4.05</v>
+      </c>
       <c r="I87" s="2">
         <f>IF(H87&lt;&gt;"",E87-H87,"")</f>
         <v/>
@@ -27335,7 +27786,9 @@
       <c r="G88" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H88" s="3" t="n"/>
+      <c r="H88" s="3" t="n">
+        <v>4.05</v>
+      </c>
       <c r="I88" s="2">
         <f>IF(H88&lt;&gt;"",E88-H88,"")</f>
         <v/>
@@ -27370,7 +27823,9 @@
       <c r="G89" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H89" s="3" t="n"/>
+      <c r="H89" s="3" t="n">
+        <v>4.05</v>
+      </c>
       <c r="I89" s="2">
         <f>IF(H89&lt;&gt;"",E89-H89,"")</f>
         <v/>
@@ -27405,7 +27860,9 @@
       <c r="G90" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H90" s="3" t="n"/>
+      <c r="H90" s="3" t="n">
+        <v>4.05</v>
+      </c>
       <c r="I90" s="2">
         <f>IF(H90&lt;&gt;"",E90-H90,"")</f>
         <v/>
@@ -27440,7 +27897,9 @@
       <c r="G91" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H91" s="3" t="n"/>
+      <c r="H91" s="3" t="n">
+        <v>2.48</v>
+      </c>
       <c r="I91" s="2">
         <f>IF(H91&lt;&gt;"",E91-H91,"")</f>
         <v/>
@@ -27475,7 +27934,9 @@
       <c r="G92" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H92" s="3" t="n"/>
+      <c r="H92" s="3" t="n">
+        <v>2.48</v>
+      </c>
       <c r="I92" s="2">
         <f>IF(H92&lt;&gt;"",E92-H92,"")</f>
         <v/>
@@ -27510,7 +27971,9 @@
       <c r="G93" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H93" s="3" t="n"/>
+      <c r="H93" s="3" t="n">
+        <v>1.69</v>
+      </c>
       <c r="I93" s="2">
         <f>IF(H93&lt;&gt;"",E93-H93,"")</f>
         <v/>
@@ -27545,7 +28008,9 @@
       <c r="G94" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H94" s="3" t="n"/>
+      <c r="H94" s="3" t="n">
+        <v>1.69</v>
+      </c>
       <c r="I94" s="2">
         <f>IF(H94&lt;&gt;"",E94-H94,"")</f>
         <v/>

--- a/Inventory/Cross_Platform_PL.xlsx
+++ b/Inventory/Cross_Platform_PL.xlsx
@@ -17712,7 +17712,7 @@
         <v>12</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>9.56</v>
+        <v>17</v>
       </c>
       <c r="J2" s="2">
         <f>IF(I2&lt;&gt;"",I2,G2)</f>
@@ -17761,7 +17761,7 @@
         <v>17</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>49.99</v>
+        <v>88.87</v>
       </c>
       <c r="J3" s="2">
         <f>IF(I3&lt;&gt;"",I3,G3)</f>
@@ -17810,7 +17810,7 @@
         <v>17</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>1.69</v>
+        <v>3</v>
       </c>
       <c r="J4" s="2">
         <f>IF(I4&lt;&gt;"",I4,G4)</f>
@@ -17859,7 +17859,7 @@
         <v>15</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>12.71</v>
+        <v>22.6</v>
       </c>
       <c r="J5" s="2">
         <f>IF(I5&lt;&gt;"",I5,G5)</f>
@@ -17908,7 +17908,7 @@
         <v>28</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>11.14</v>
+        <v>19.8</v>
       </c>
       <c r="J6" s="2">
         <f>IF(I6&lt;&gt;"",I6,G6)</f>
@@ -17957,7 +17957,7 @@
         <v>26</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>24.53</v>
+        <v>43.6</v>
       </c>
       <c r="J7" s="2">
         <f>IF(I7&lt;&gt;"",I7,G7)</f>
@@ -18006,7 +18006,7 @@
         <v>15</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>23.74</v>
+        <v>42.2</v>
       </c>
       <c r="J8" s="2">
         <f>IF(I8&lt;&gt;"",I8,G8)</f>
@@ -18055,7 +18055,7 @@
         <v>19</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>13.5</v>
+        <v>24</v>
       </c>
       <c r="J9" s="2">
         <f>IF(I9&lt;&gt;"",I9,G9)</f>
@@ -18104,7 +18104,7 @@
         <v>30</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>866.25</v>
+        <v>1540</v>
       </c>
       <c r="J10" s="2">
         <f>IF(I10&lt;&gt;"",I10,G10)</f>
@@ -18153,7 +18153,7 @@
         <v>26</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>11.93</v>
+        <v>21.2</v>
       </c>
       <c r="J11" s="2">
         <f>IF(I11&lt;&gt;"",I11,G11)</f>
@@ -18202,7 +18202,7 @@
         <v>19</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>122.72</v>
+        <v>218.17</v>
       </c>
       <c r="J12" s="2">
         <f>IF(I12&lt;&gt;"",I12,G12)</f>
@@ -18251,7 +18251,7 @@
         <v>29</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>1485</v>
+        <v>2640</v>
       </c>
       <c r="J13" s="2">
         <f>IF(I13&lt;&gt;"",I13,G13)</f>
@@ -18300,7 +18300,7 @@
         <v>30</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>297</v>
+        <v>528</v>
       </c>
       <c r="J14" s="2">
         <f>IF(I14&lt;&gt;"",I14,G14)</f>
@@ -18349,7 +18349,7 @@
         <v>23</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>6.41</v>
+        <v>11.4</v>
       </c>
       <c r="J15" s="2">
         <f>IF(I15&lt;&gt;"",I15,G15)</f>
@@ -18398,7 +18398,7 @@
         <v>19</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>4.05</v>
+        <v>7.2</v>
       </c>
       <c r="J16" s="2">
         <f>IF(I16&lt;&gt;"",I16,G16)</f>
@@ -18447,7 +18447,7 @@
         <v>28</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>189.75</v>
+        <v>337.33</v>
       </c>
       <c r="J17" s="2">
         <f>IF(I17&lt;&gt;"",I17,G17)</f>
@@ -18496,7 +18496,7 @@
         <v>30</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>1.69</v>
+        <v>3</v>
       </c>
       <c r="J18" s="2">
         <f>IF(I18&lt;&gt;"",I18,G18)</f>
@@ -18545,7 +18545,7 @@
         <v>32</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>1.69</v>
+        <v>3</v>
       </c>
       <c r="J19" s="2">
         <f>IF(I19&lt;&gt;"",I19,G19)</f>
@@ -18594,7 +18594,7 @@
         <v>34</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>11.02</v>
+        <v>19.6</v>
       </c>
       <c r="J20" s="2">
         <f>IF(I20&lt;&gt;"",I20,G20)</f>
@@ -18643,7 +18643,7 @@
         <v>25</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>142.88</v>
+        <v>254</v>
       </c>
       <c r="J21" s="2">
         <f>IF(I21&lt;&gt;"",I21,G21)</f>
@@ -18692,7 +18692,7 @@
         <v>25</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>228.75</v>
+        <v>406.67</v>
       </c>
       <c r="J22" s="2">
         <f>IF(I22&lt;&gt;"",I22,G22)</f>
@@ -18741,7 +18741,7 @@
         <v>21</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>7.2</v>
+        <v>12.8</v>
       </c>
       <c r="J23" s="2">
         <f>IF(I23&lt;&gt;"",I23,G23)</f>
@@ -18790,7 +18790,7 @@
         <v>26</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>2.48</v>
+        <v>4.4</v>
       </c>
       <c r="J24" s="2">
         <f>IF(I24&lt;&gt;"",I24,G24)</f>
@@ -18839,7 +18839,7 @@
         <v>25</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>150.94</v>
+        <v>268.33</v>
       </c>
       <c r="J25" s="2">
         <f>IF(I25&lt;&gt;"",I25,G25)</f>
@@ -18888,7 +18888,7 @@
         <v>22</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>1.69</v>
+        <v>3</v>
       </c>
       <c r="J26" s="2">
         <f>IF(I26&lt;&gt;"",I26,G26)</f>
@@ -18937,7 +18937,7 @@
         <v>17</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>3.26</v>
+        <v>5.8</v>
       </c>
       <c r="J27" s="2">
         <f>IF(I27&lt;&gt;"",I27,G27)</f>
@@ -18986,7 +18986,7 @@
         <v>17</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>7.2</v>
+        <v>12.8</v>
       </c>
       <c r="J28" s="2">
         <f>IF(I28&lt;&gt;"",I28,G28)</f>
@@ -19035,7 +19035,7 @@
         <v>15</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>7.2</v>
+        <v>12.8</v>
       </c>
       <c r="J29" s="2">
         <f>IF(I29&lt;&gt;"",I29,G29)</f>
@@ -19084,7 +19084,7 @@
         <v>26</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>20.59</v>
+        <v>36.6</v>
       </c>
       <c r="J30" s="2">
         <f>IF(I30&lt;&gt;"",I30,G30)</f>
@@ -19133,7 +19133,7 @@
         <v>26</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>16.65</v>
+        <v>29.6</v>
       </c>
       <c r="J31" s="2">
         <f>IF(I31&lt;&gt;"",I31,G31)</f>
@@ -19182,7 +19182,7 @@
         <v>21</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>63.86</v>
+        <v>113.53</v>
       </c>
       <c r="J32" s="2">
         <f>IF(I32&lt;&gt;"",I32,G32)</f>
@@ -19231,7 +19231,7 @@
         <v>28</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>24.41</v>
+        <v>43.4</v>
       </c>
       <c r="J33" s="2">
         <f>IF(I33&lt;&gt;"",I33,G33)</f>
@@ -19280,7 +19280,7 @@
         <v>21</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>118.69</v>
+        <v>211</v>
       </c>
       <c r="J34" s="2">
         <f>IF(I34&lt;&gt;"",I34,G34)</f>
@@ -19329,7 +19329,7 @@
         <v>28</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>28.35</v>
+        <v>50.4</v>
       </c>
       <c r="J35" s="2">
         <f>IF(I35&lt;&gt;"",I35,G35)</f>
@@ -19378,7 +19378,7 @@
         <v>22</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>41.92</v>
+        <v>74.53</v>
       </c>
       <c r="J36" s="2">
         <f>IF(I36&lt;&gt;"",I36,G36)</f>
@@ -19427,7 +19427,7 @@
         <v>24</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>44.51</v>
+        <v>79.13</v>
       </c>
       <c r="J37" s="2">
         <f>IF(I37&lt;&gt;"",I37,G37)</f>
@@ -19476,7 +19476,7 @@
         <v>22</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>53.21</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="J38" s="2">
         <f>IF(I38&lt;&gt;"",I38,G38)</f>
@@ -19525,7 +19525,7 @@
         <v>22</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>598.13</v>
+        <v>1063.33</v>
       </c>
       <c r="J39" s="2">
         <f>IF(I39&lt;&gt;"",I39,G39)</f>
@@ -19574,7 +19574,7 @@
         <v>28</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>54.19</v>
+        <v>96.33</v>
       </c>
       <c r="J40" s="2">
         <f>IF(I40&lt;&gt;"",I40,G40)</f>
@@ -19623,7 +19623,7 @@
         <v>25</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>26.88</v>
+        <v>47.79</v>
       </c>
       <c r="J41" s="2">
         <f>IF(I41&lt;&gt;"",I41,G41)</f>
@@ -19672,7 +19672,7 @@
         <v>28</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>7.99</v>
+        <v>14.2</v>
       </c>
       <c r="J42" s="2">
         <f>IF(I42&lt;&gt;"",I42,G42)</f>
@@ -19721,7 +19721,7 @@
         <v>28</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>129</v>
+        <v>229.33</v>
       </c>
       <c r="J43" s="2">
         <f>IF(I43&lt;&gt;"",I43,G43)</f>
@@ -19770,7 +19770,7 @@
         <v>32</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>187.5</v>
+        <v>333.33</v>
       </c>
       <c r="J44" s="2">
         <f>IF(I44&lt;&gt;"",I44,G44)</f>
@@ -19819,7 +19819,7 @@
         <v>24</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>90.47</v>
+        <v>160.84</v>
       </c>
       <c r="J45" s="2">
         <f>IF(I45&lt;&gt;"",I45,G45)</f>
@@ -19868,7 +19868,7 @@
         <v>17</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>10.35</v>
+        <v>18.4</v>
       </c>
       <c r="J46" s="2">
         <f>IF(I46&lt;&gt;"",I46,G46)</f>
@@ -19917,7 +19917,7 @@
         <v>26</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>106.59</v>
+        <v>189.5</v>
       </c>
       <c r="J47" s="2">
         <f>IF(I47&lt;&gt;"",I47,G47)</f>
@@ -19966,7 +19966,7 @@
         <v>16</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>33.97</v>
+        <v>60.4</v>
       </c>
       <c r="J48" s="2">
         <f>IF(I48&lt;&gt;"",I48,G48)</f>
@@ -20015,7 +20015,7 @@
         <v>12</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>14.29</v>
+        <v>25.4</v>
       </c>
       <c r="J49" s="2">
         <f>IF(I49&lt;&gt;"",I49,G49)</f>
@@ -20064,7 +20064,7 @@
         <v>24</v>
       </c>
       <c r="I50" s="3" t="n">
-        <v>120.94</v>
+        <v>215</v>
       </c>
       <c r="J50" s="2">
         <f>IF(I50&lt;&gt;"",I50,G50)</f>
@@ -20113,7 +20113,7 @@
         <v>23</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>41.29</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="J51" s="2">
         <f>IF(I51&lt;&gt;"",I51,G51)</f>
@@ -20162,7 +20162,7 @@
         <v>21</v>
       </c>
       <c r="I52" s="3" t="n">
-        <v>171</v>
+        <v>304</v>
       </c>
       <c r="J52" s="2">
         <f>IF(I52&lt;&gt;"",I52,G52)</f>
@@ -20211,7 +20211,7 @@
         <v>25</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>162.75</v>
+        <v>289.33</v>
       </c>
       <c r="J53" s="2">
         <f>IF(I53&lt;&gt;"",I53,G53)</f>
@@ -20260,7 +20260,7 @@
         <v>28</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>73.54000000000001</v>
+        <v>130.73</v>
       </c>
       <c r="J54" s="2">
         <f>IF(I54&lt;&gt;"",I54,G54)</f>
@@ -20309,7 +20309,7 @@
         <v>29</v>
       </c>
       <c r="I55" s="3" t="n">
-        <v>33.19</v>
+        <v>59</v>
       </c>
       <c r="J55" s="2">
         <f>IF(I55&lt;&gt;"",I55,G55)</f>
@@ -20358,7 +20358,7 @@
         <v>28</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>49.99</v>
+        <v>88.87</v>
       </c>
       <c r="J56" s="2">
         <f>IF(I56&lt;&gt;"",I56,G56)</f>
@@ -20407,7 +20407,7 @@
         <v>15</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>1.69</v>
+        <v>3</v>
       </c>
       <c r="J57" s="2">
         <f>IF(I57&lt;&gt;"",I57,G57)</f>
@@ -20456,7 +20456,7 @@
         <v>15</v>
       </c>
       <c r="I58" s="3" t="n">
-        <v>14.29</v>
+        <v>25.4</v>
       </c>
       <c r="J58" s="2">
         <f>IF(I58&lt;&gt;"",I58,G58)</f>
@@ -20505,7 +20505,7 @@
         <v>26</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>41.29</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="J59" s="2">
         <f>IF(I59&lt;&gt;"",I59,G59)</f>
@@ -20554,7 +20554,7 @@
         <v>28</v>
       </c>
       <c r="I60" s="3" t="n">
-        <v>39.67</v>
+        <v>70.53</v>
       </c>
       <c r="J60" s="2">
         <f>IF(I60&lt;&gt;"",I60,G60)</f>
@@ -20603,7 +20603,7 @@
         <v>17</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>6.41</v>
+        <v>11.4</v>
       </c>
       <c r="J61" s="2">
         <f>IF(I61&lt;&gt;"",I61,G61)</f>
@@ -20652,7 +20652,7 @@
         <v>28</v>
       </c>
       <c r="I62" s="3" t="n">
-        <v>60.64</v>
+        <v>107.8</v>
       </c>
       <c r="J62" s="2">
         <f>IF(I62&lt;&gt;"",I62,G62)</f>
@@ -20701,7 +20701,7 @@
         <v>30</v>
       </c>
       <c r="I63" s="3" t="n">
-        <v>16.65</v>
+        <v>29.6</v>
       </c>
       <c r="J63" s="2">
         <f>IF(I63&lt;&gt;"",I63,G63)</f>
@@ -20750,7 +20750,7 @@
         <v>32</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>6.41</v>
+        <v>11.4</v>
       </c>
       <c r="J64" s="2">
         <f>IF(I64&lt;&gt;"",I64,G64)</f>
@@ -20799,7 +20799,7 @@
         <v>30</v>
       </c>
       <c r="I65" s="3" t="n">
-        <v>50.96</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="J65" s="2">
         <f>IF(I65&lt;&gt;"",I65,G65)</f>
@@ -20848,7 +20848,7 @@
         <v>34</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>10.24</v>
+        <v>18.2</v>
       </c>
       <c r="J66" s="2">
         <f>IF(I66&lt;&gt;"",I66,G66)</f>
@@ -20897,7 +20897,7 @@
         <v>28</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>34.76</v>
+        <v>61.8</v>
       </c>
       <c r="J67" s="2">
         <f>IF(I67&lt;&gt;"",I67,G67)</f>
@@ -20946,7 +20946,7 @@
         <v>32</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>72.56</v>
+        <v>129</v>
       </c>
       <c r="J68" s="2">
         <f>IF(I68&lt;&gt;"",I68,G68)</f>
@@ -20995,7 +20995,7 @@
         <v>23</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>23.74</v>
+        <v>42.2</v>
       </c>
       <c r="J69" s="2">
         <f>IF(I69&lt;&gt;"",I69,G69)</f>
@@ -21044,7 +21044,7 @@
         <v>23</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>154.97</v>
+        <v>275.51</v>
       </c>
       <c r="J70" s="2">
         <f>IF(I70&lt;&gt;"",I70,G70)</f>
@@ -21093,7 +21093,7 @@
         <v>30</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>75.15000000000001</v>
+        <v>133.6</v>
       </c>
       <c r="J71" s="2">
         <f>IF(I71&lt;&gt;"",I71,G71)</f>
@@ -21142,7 +21142,7 @@
         <v>19</v>
       </c>
       <c r="I72" s="3" t="n">
-        <v>122.72</v>
+        <v>218.17</v>
       </c>
       <c r="J72" s="2">
         <f>IF(I72&lt;&gt;"",I72,G72)</f>
@@ -21191,7 +21191,7 @@
         <v>23</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>118.69</v>
+        <v>211</v>
       </c>
       <c r="J73" s="2">
         <f>IF(I73&lt;&gt;"",I73,G73)</f>
@@ -21240,7 +21240,7 @@
         <v>20</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>59.03</v>
+        <v>104.93</v>
       </c>
       <c r="J74" s="2">
         <f>IF(I74&lt;&gt;"",I74,G74)</f>
@@ -21289,7 +21289,7 @@
         <v>30</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>41.29</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="J75" s="2">
         <f>IF(I75&lt;&gt;"",I75,G75)</f>
@@ -21338,7 +21338,7 @@
         <v>26</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>66.11</v>
+        <v>117.53</v>
       </c>
       <c r="J76" s="2">
         <f>IF(I76&lt;&gt;"",I76,G76)</f>
@@ -21387,7 +21387,7 @@
         <v>36</v>
       </c>
       <c r="I77" s="3" t="n">
-        <v>1.69</v>
+        <v>3</v>
       </c>
       <c r="J77" s="2">
         <f>IF(I77&lt;&gt;"",I77,G77)</f>
@@ -21436,7 +21436,7 @@
         <v>28</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>106.59</v>
+        <v>189.5</v>
       </c>
       <c r="J78" s="2">
         <f>IF(I78&lt;&gt;"",I78,G78)</f>
@@ -21485,7 +21485,7 @@
         <v>30</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>10.35</v>
+        <v>18.4</v>
       </c>
       <c r="J79" s="2">
         <f>IF(I79&lt;&gt;"",I79,G79)</f>
@@ -21534,7 +21534,7 @@
         <v>28</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>10.35</v>
+        <v>18.4</v>
       </c>
       <c r="J80" s="2">
         <f>IF(I80&lt;&gt;"",I80,G80)</f>
@@ -21583,7 +21583,7 @@
         <v>26</v>
       </c>
       <c r="I81" s="3" t="n">
-        <v>14.29</v>
+        <v>25.4</v>
       </c>
       <c r="J81" s="2">
         <f>IF(I81&lt;&gt;"",I81,G81)</f>
@@ -21632,7 +21632,7 @@
         <v>28</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>1.69</v>
+        <v>3</v>
       </c>
       <c r="J82" s="2">
         <f>IF(I82&lt;&gt;"",I82,G82)</f>
@@ -21681,7 +21681,7 @@
         <v>16</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>133.03</v>
+        <v>236.5</v>
       </c>
       <c r="J83" s="2">
         <f>IF(I83&lt;&gt;"",I83,G83)</f>
@@ -21730,7 +21730,7 @@
         <v>12</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>3.26</v>
+        <v>5.8</v>
       </c>
       <c r="J84" s="2">
         <f>IF(I84&lt;&gt;"",I84,G84)</f>
@@ -21779,7 +21779,7 @@
         <v>28</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>28.46</v>
+        <v>50.6</v>
       </c>
       <c r="J85" s="2">
         <f>IF(I85&lt;&gt;"",I85,G85)</f>
@@ -21828,7 +21828,7 @@
         <v>24</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>15.08</v>
+        <v>26.8</v>
       </c>
       <c r="J86" s="2">
         <f>IF(I86&lt;&gt;"",I86,G86)</f>
@@ -21877,7 +21877,7 @@
         <v>26</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>9.56</v>
+        <v>17</v>
       </c>
       <c r="J87" s="2">
         <f>IF(I87&lt;&gt;"",I87,G87)</f>
@@ -21926,7 +21926,7 @@
         <v>27</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>2.48</v>
+        <v>4.4</v>
       </c>
       <c r="J88" s="2">
         <f>IF(I88&lt;&gt;"",I88,G88)</f>
@@ -21975,7 +21975,7 @@
         <v>24</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>19.01</v>
+        <v>33.8</v>
       </c>
       <c r="J89" s="2">
         <f>IF(I89&lt;&gt;"",I89,G89)</f>
@@ -22024,7 +22024,7 @@
         <v>21</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>19.8</v>
+        <v>35.2</v>
       </c>
       <c r="J90" s="2">
         <f>IF(I90&lt;&gt;"",I90,G90)</f>
@@ -22073,7 +22073,7 @@
         <v>27</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>7.99</v>
+        <v>14.2</v>
       </c>
       <c r="J91" s="2">
         <f>IF(I91&lt;&gt;"",I91,G91)</f>
@@ -22122,7 +22122,7 @@
         <v>27</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>7.99</v>
+        <v>14.2</v>
       </c>
       <c r="J92" s="2">
         <f>IF(I92&lt;&gt;"",I92,G92)</f>
@@ -22171,7 +22171,7 @@
         <v>18</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>44.51</v>
+        <v>79.13</v>
       </c>
       <c r="J93" s="2">
         <f>IF(I93&lt;&gt;"",I93,G93)</f>
@@ -22220,7 +22220,7 @@
         <v>30</v>
       </c>
       <c r="I94" s="3" t="n">
-        <v>5.62</v>
+        <v>10</v>
       </c>
       <c r="J94" s="2">
         <f>IF(I94&lt;&gt;"",I94,G94)</f>
@@ -22269,7 +22269,7 @@
         <v>23</v>
       </c>
       <c r="I95" s="3" t="n">
-        <v>11.93</v>
+        <v>21.2</v>
       </c>
       <c r="J95" s="2">
         <f>IF(I95&lt;&gt;"",I95,G95)</f>
@@ -22318,7 +22318,7 @@
         <v>30</v>
       </c>
       <c r="I96" s="3" t="n">
-        <v>4.84</v>
+        <v>8.6</v>
       </c>
       <c r="J96" s="2">
         <f>IF(I96&lt;&gt;"",I96,G96)</f>
@@ -22367,7 +22367,7 @@
         <v>23</v>
       </c>
       <c r="I97" s="3" t="n">
-        <v>82.42</v>
+        <v>146.52</v>
       </c>
       <c r="J97" s="2">
         <f>IF(I97&lt;&gt;"",I97,G97)</f>
@@ -22416,7 +22416,7 @@
         <v>28</v>
       </c>
       <c r="I98" s="3" t="n">
-        <v>75.15000000000001</v>
+        <v>133.6</v>
       </c>
       <c r="J98" s="2">
         <f>IF(I98&lt;&gt;"",I98,G98)</f>
@@ -22465,7 +22465,7 @@
         <v>24</v>
       </c>
       <c r="I99" s="3" t="n">
-        <v>26.89</v>
+        <v>47.8</v>
       </c>
       <c r="J99" s="2">
         <f>IF(I99&lt;&gt;"",I99,G99)</f>
@@ -22514,7 +22514,7 @@
         <v>29</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>11.93</v>
+        <v>21.2</v>
       </c>
       <c r="J100" s="2">
         <f>IF(I100&lt;&gt;"",I100,G100)</f>
@@ -22563,7 +22563,7 @@
         <v>27</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>1.69</v>
+        <v>3</v>
       </c>
       <c r="J101" s="2">
         <f>IF(I101&lt;&gt;"",I101,G101)</f>
@@ -22612,7 +22612,7 @@
         <v>24</v>
       </c>
       <c r="I102" s="3" t="n">
-        <v>29.25</v>
+        <v>52</v>
       </c>
       <c r="J102" s="2">
         <f>IF(I102&lt;&gt;"",I102,G102)</f>
@@ -22661,7 +22661,7 @@
         <v>29</v>
       </c>
       <c r="I103" s="3" t="n">
-        <v>14.17</v>
+        <v>25.2</v>
       </c>
       <c r="J103" s="2">
         <f>IF(I103&lt;&gt;"",I103,G103)</f>
@@ -22710,7 +22710,7 @@
         <v>27</v>
       </c>
       <c r="I104" s="3" t="n">
-        <v>14.29</v>
+        <v>25.4</v>
       </c>
       <c r="J104" s="2">
         <f>IF(I104&lt;&gt;"",I104,G104)</f>
@@ -22759,7 +22759,7 @@
         <v>27</v>
       </c>
       <c r="I105" s="3" t="n">
-        <v>14.29</v>
+        <v>25.4</v>
       </c>
       <c r="J105" s="2">
         <f>IF(I105&lt;&gt;"",I105,G105)</f>
@@ -22808,7 +22808,7 @@
         <v>32</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>5.62</v>
+        <v>10</v>
       </c>
       <c r="J106" s="2">
         <f>IF(I106&lt;&gt;"",I106,G106)</f>
@@ -22857,7 +22857,7 @@
         <v>30</v>
       </c>
       <c r="I107" s="3" t="n">
-        <v>9.56</v>
+        <v>17</v>
       </c>
       <c r="J107" s="2">
         <f>IF(I107&lt;&gt;"",I107,G107)</f>
@@ -22906,7 +22906,7 @@
         <v>27</v>
       </c>
       <c r="I108" s="3" t="n">
-        <v>4.84</v>
+        <v>8.6</v>
       </c>
       <c r="J108" s="2">
         <f>IF(I108&lt;&gt;"",I108,G108)</f>
@@ -22955,7 +22955,7 @@
         <v>29</v>
       </c>
       <c r="I109" s="3" t="n">
-        <v>14.96</v>
+        <v>26.6</v>
       </c>
       <c r="J109" s="2">
         <f>IF(I109&lt;&gt;"",I109,G109)</f>
@@ -23004,7 +23004,7 @@
         <v>30</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>7.99</v>
+        <v>14.2</v>
       </c>
       <c r="J110" s="2">
         <f>IF(I110&lt;&gt;"",I110,G110)</f>
@@ -23053,7 +23053,7 @@
         <v>25</v>
       </c>
       <c r="I111" s="3" t="n">
-        <v>7.2</v>
+        <v>12.8</v>
       </c>
       <c r="J111" s="2">
         <f>IF(I111&lt;&gt;"",I111,G111)</f>
@@ -23102,7 +23102,7 @@
         <v>25</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>2.48</v>
+        <v>4.4</v>
       </c>
       <c r="J112" s="2">
         <f>IF(I112&lt;&gt;"",I112,G112)</f>
@@ -23151,7 +23151,7 @@
         <v>26</v>
       </c>
       <c r="I113" s="3" t="n">
-        <v>55.8</v>
+        <v>99.2</v>
       </c>
       <c r="J113" s="2">
         <f>IF(I113&lt;&gt;"",I113,G113)</f>
@@ -23200,7 +23200,7 @@
         <v>32</v>
       </c>
       <c r="I114" s="3" t="n">
-        <v>2.48</v>
+        <v>4.4</v>
       </c>
       <c r="J114" s="2">
         <f>IF(I114&lt;&gt;"",I114,G114)</f>
@@ -23249,7 +23249,7 @@
         <v>34</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>110.62</v>
+        <v>196.67</v>
       </c>
       <c r="J115" s="2">
         <f>IF(I115&lt;&gt;"",I115,G115)</f>
@@ -23298,7 +23298,7 @@
         <v>30</v>
       </c>
       <c r="I116" s="3" t="n">
-        <v>8.77</v>
+        <v>15.6</v>
       </c>
       <c r="J116" s="2">
         <f>IF(I116&lt;&gt;"",I116,G116)</f>
@@ -23347,7 +23347,7 @@
         <v>26</v>
       </c>
       <c r="I117" s="3" t="n">
-        <v>5.62</v>
+        <v>10</v>
       </c>
       <c r="J117" s="2">
         <f>IF(I117&lt;&gt;"",I117,G117)</f>
@@ -23396,7 +23396,7 @@
         <v>28</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>171</v>
+        <v>304</v>
       </c>
       <c r="J118" s="2">
         <f>IF(I118&lt;&gt;"",I118,G118)</f>
@@ -23445,7 +23445,7 @@
         <v>29</v>
       </c>
       <c r="I119" s="3" t="n">
-        <v>26.1</v>
+        <v>46.4</v>
       </c>
       <c r="J119" s="2">
         <f>IF(I119&lt;&gt;"",I119,G119)</f>
@@ -23494,7 +23494,7 @@
         <v>28</v>
       </c>
       <c r="I120" s="3" t="n">
-        <v>12.71</v>
+        <v>22.6</v>
       </c>
       <c r="J120" s="2">
         <f>IF(I120&lt;&gt;"",I120,G120)</f>
@@ -23543,7 +23543,7 @@
         <v>34</v>
       </c>
       <c r="I121" s="3" t="n">
-        <v>5.62</v>
+        <v>10</v>
       </c>
       <c r="J121" s="2">
         <f>IF(I121&lt;&gt;"",I121,G121)</f>
@@ -23592,7 +23592,7 @@
         <v>27</v>
       </c>
       <c r="I122" s="3" t="n">
-        <v>20.48</v>
+        <v>36.4</v>
       </c>
       <c r="J122" s="2">
         <f>IF(I122&lt;&gt;"",I122,G122)</f>
@@ -23641,7 +23641,7 @@
         <v>26</v>
       </c>
       <c r="I123" s="3" t="n">
-        <v>7.2</v>
+        <v>12.8</v>
       </c>
       <c r="J123" s="2">
         <f>IF(I123&lt;&gt;"",I123,G123)</f>
@@ -23690,7 +23690,7 @@
         <v>25</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>1.69</v>
+        <v>3</v>
       </c>
       <c r="J124" s="2">
         <f>IF(I124&lt;&gt;"",I124,G124)</f>
@@ -23739,7 +23739,7 @@
         <v>28</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>21.38</v>
+        <v>38</v>
       </c>
       <c r="J125" s="2">
         <f>IF(I125&lt;&gt;"",I125,G125)</f>
@@ -23788,7 +23788,7 @@
         <v>28</v>
       </c>
       <c r="I126" s="3" t="n">
-        <v>126.75</v>
+        <v>225.33</v>
       </c>
       <c r="J126" s="2">
         <f>IF(I126&lt;&gt;"",I126,G126)</f>
@@ -23837,7 +23837,7 @@
         <v>32</v>
       </c>
       <c r="I127" s="3" t="n">
-        <v>134.81</v>
+        <v>239.67</v>
       </c>
       <c r="J127" s="2">
         <f>IF(I127&lt;&gt;"",I127,G127)</f>
@@ -23886,7 +23886,7 @@
         <v>12</v>
       </c>
       <c r="I128" s="3" t="n">
-        <v>65.47</v>
+        <v>116.4</v>
       </c>
       <c r="J128" s="2">
         <f>IF(I128&lt;&gt;"",I128,G128)</f>
@@ -23935,7 +23935,7 @@
         <v>34</v>
       </c>
       <c r="I129" s="3" t="n">
-        <v>65.47</v>
+        <v>116.4</v>
       </c>
       <c r="J129" s="2">
         <f>IF(I129&lt;&gt;"",I129,G129)</f>
@@ -23984,7 +23984,7 @@
         <v>17</v>
       </c>
       <c r="I130" s="3" t="n">
-        <v>130.79</v>
+        <v>232.52</v>
       </c>
       <c r="J130" s="2">
         <f>IF(I130&lt;&gt;"",I130,G130)</f>
@@ -24033,7 +24033,7 @@
         <v>34</v>
       </c>
       <c r="I131" s="3" t="n">
-        <v>73.54000000000001</v>
+        <v>130.73</v>
       </c>
       <c r="J131" s="2">
         <f>IF(I131&lt;&gt;"",I131,G131)</f>
@@ -24082,7 +24082,7 @@
         <v>21</v>
       </c>
       <c r="I132" s="3" t="n">
-        <v>98.54000000000001</v>
+        <v>175.19</v>
       </c>
       <c r="J132" s="2">
         <f>IF(I132&lt;&gt;"",I132,G132)</f>
@@ -24131,7 +24131,7 @@
         <v>23</v>
       </c>
       <c r="I133" s="3" t="n">
-        <v>204</v>
+        <v>362.67</v>
       </c>
       <c r="J133" s="2">
         <f>IF(I133&lt;&gt;"",I133,G133)</f>
@@ -24180,7 +24180,7 @@
         <v>14</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>330</v>
+        <v>586.67</v>
       </c>
       <c r="J134" s="2">
         <f>IF(I134&lt;&gt;"",I134,G134)</f>
@@ -24229,7 +24229,7 @@
         <v>32</v>
       </c>
       <c r="I135" s="3" t="n">
-        <v>554.63</v>
+        <v>986</v>
       </c>
       <c r="J135" s="2">
         <f>IF(I135&lt;&gt;"",I135,G135)</f>
@@ -24278,7 +24278,7 @@
         <v>17</v>
       </c>
       <c r="I136" s="3" t="n">
-        <v>598.13</v>
+        <v>1063.33</v>
       </c>
       <c r="J136" s="2">
         <f>IF(I136&lt;&gt;"",I136,G136)</f>
@@ -24327,7 +24327,7 @@
         <v>29</v>
       </c>
       <c r="I137" s="3" t="n">
-        <v>556.88</v>
+        <v>990</v>
       </c>
       <c r="J137" s="2">
         <f>IF(I137&lt;&gt;"",I137,G137)</f>
@@ -24376,7 +24376,7 @@
         <v>22</v>
       </c>
       <c r="I138" s="3" t="n">
-        <v>556.88</v>
+        <v>990</v>
       </c>
       <c r="J138" s="2">
         <f>IF(I138&lt;&gt;"",I138,G138)</f>
@@ -24425,7 +24425,7 @@
         <v>17</v>
       </c>
       <c r="I139" s="3" t="n">
-        <v>595.88</v>
+        <v>1059.33</v>
       </c>
       <c r="J139" s="2">
         <f>IF(I139&lt;&gt;"",I139,G139)</f>
@@ -24474,7 +24474,7 @@
         <v>14</v>
       </c>
       <c r="I140" s="3" t="n">
-        <v>742.5</v>
+        <v>1320</v>
       </c>
       <c r="J140" s="2">
         <f>IF(I140&lt;&gt;"",I140,G140)</f>
@@ -24605,7 +24605,7 @@
         <v>0</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>2145</v>
+        <v>3813.33</v>
       </c>
       <c r="I2" s="2">
         <f>IF(H2&lt;&gt;"",E2-H2,"")</f>
@@ -24642,7 +24642,7 @@
         <v>0</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>866.25</v>
+        <v>1540</v>
       </c>
       <c r="I3" s="2">
         <f>IF(H3&lt;&gt;"",E3-H3,"")</f>
@@ -24679,7 +24679,7 @@
         <v>0</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>657.75</v>
+        <v>1169.33</v>
       </c>
       <c r="I4" s="2">
         <f>IF(H4&lt;&gt;"",E4-H4,"")</f>
@@ -24716,7 +24716,7 @@
         <v>0</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>616.5</v>
+        <v>1096</v>
       </c>
       <c r="I5" s="2">
         <f>IF(H5&lt;&gt;"",E5-H5,"")</f>
@@ -24753,7 +24753,7 @@
         <v>0</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>577.5</v>
+        <v>1026.67</v>
       </c>
       <c r="I6" s="2">
         <f>IF(H6&lt;&gt;"",E6-H6,"")</f>
@@ -24790,7 +24790,7 @@
         <v>0</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>453.75</v>
+        <v>806.67</v>
       </c>
       <c r="I7" s="2">
         <f>IF(H7&lt;&gt;"",E7-H7,"")</f>
@@ -24827,7 +24827,7 @@
         <v>0</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>379.5</v>
+        <v>674.67</v>
       </c>
       <c r="I8" s="2">
         <f>IF(H8&lt;&gt;"",E8-H8,"")</f>
@@ -24864,7 +24864,7 @@
         <v>0</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>261.75</v>
+        <v>465.33</v>
       </c>
       <c r="I9" s="2">
         <f>IF(H9&lt;&gt;"",E9-H9,"")</f>
@@ -24901,7 +24901,7 @@
         <v>0</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>261.75</v>
+        <v>465.33</v>
       </c>
       <c r="I10" s="2">
         <f>IF(H10&lt;&gt;"",E10-H10,"")</f>
@@ -24938,7 +24938,7 @@
         <v>0</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>253.5</v>
+        <v>450.67</v>
       </c>
       <c r="I11" s="2">
         <f>IF(H11&lt;&gt;"",E11-H11,"")</f>
@@ -24975,7 +24975,7 @@
         <v>0</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>228.75</v>
+        <v>406.67</v>
       </c>
       <c r="I12" s="2">
         <f>IF(H12&lt;&gt;"",E12-H12,"")</f>
@@ -25012,7 +25012,7 @@
         <v>0</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>214.5</v>
+        <v>381.33</v>
       </c>
       <c r="I13" s="2">
         <f>IF(H13&lt;&gt;"",E13-H13,"")</f>
@@ -25049,7 +25049,7 @@
         <v>0</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>179.25</v>
+        <v>318.67</v>
       </c>
       <c r="I14" s="2">
         <f>IF(H14&lt;&gt;"",E14-H14,"")</f>
@@ -25086,7 +25086,7 @@
         <v>0</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>173.25</v>
+        <v>308</v>
       </c>
       <c r="I15" s="2">
         <f>IF(H15&lt;&gt;"",E15-H15,"")</f>
@@ -25123,7 +25123,7 @@
         <v>0</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>162.75</v>
+        <v>289.33</v>
       </c>
       <c r="I16" s="2">
         <f>IF(H16&lt;&gt;"",E16-H16,"")</f>
@@ -25160,7 +25160,7 @@
         <v>0</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>141.09</v>
+        <v>250.83</v>
       </c>
       <c r="I17" s="2">
         <f>IF(H17&lt;&gt;"",E17-H17,"")</f>
@@ -25197,7 +25197,7 @@
         <v>0</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>133.03</v>
+        <v>236.5</v>
       </c>
       <c r="I18" s="2">
         <f>IF(H18&lt;&gt;"",E18-H18,"")</f>
@@ -25234,7 +25234,7 @@
         <v>0</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>126.75</v>
+        <v>225.33</v>
       </c>
       <c r="I19" s="2">
         <f>IF(H19&lt;&gt;"",E19-H19,"")</f>
@@ -25271,7 +25271,7 @@
         <v>0</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>102.56</v>
+        <v>182.33</v>
       </c>
       <c r="I20" s="2">
         <f>IF(H20&lt;&gt;"",E20-H20,"")</f>
@@ -25308,7 +25308,7 @@
         <v>0</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>98.53</v>
+        <v>175.17</v>
       </c>
       <c r="I21" s="2">
         <f>IF(H21&lt;&gt;"",E21-H21,"")</f>
@@ -25345,7 +25345,7 @@
         <v>0</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>90.48</v>
+        <v>160.85</v>
       </c>
       <c r="I22" s="2">
         <f>IF(H22&lt;&gt;"",E22-H22,"")</f>
@@ -25382,7 +25382,7 @@
         <v>0</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>86.44</v>
+        <v>153.67</v>
       </c>
       <c r="I23" s="2">
         <f>IF(H23&lt;&gt;"",E23-H23,"")</f>
@@ -25419,7 +25419,7 @@
         <v>0</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>78.38</v>
+        <v>139.33</v>
       </c>
       <c r="I24" s="2">
         <f>IF(H24&lt;&gt;"",E24-H24,"")</f>
@@ -25456,7 +25456,7 @@
         <v>0</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>70.31</v>
+        <v>125</v>
       </c>
       <c r="I25" s="2">
         <f>IF(H25&lt;&gt;"",E25-H25,"")</f>
@@ -25493,7 +25493,7 @@
         <v>0</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>68.7</v>
+        <v>122.13</v>
       </c>
       <c r="I26" s="2">
         <f>IF(H26&lt;&gt;"",E26-H26,"")</f>
@@ -25530,7 +25530,7 @@
         <v>0</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>68.7</v>
+        <v>122.13</v>
       </c>
       <c r="I27" s="2">
         <f>IF(H27&lt;&gt;"",E27-H27,"")</f>
@@ -25567,7 +25567,7 @@
         <v>0</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>68.7</v>
+        <v>122.13</v>
       </c>
       <c r="I28" s="2">
         <f>IF(H28&lt;&gt;"",E28-H28,"")</f>
@@ -25604,7 +25604,7 @@
         <v>0</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>65.47</v>
+        <v>116.4</v>
       </c>
       <c r="I29" s="2">
         <f>IF(H29&lt;&gt;"",E29-H29,"")</f>
@@ -25641,7 +25641,7 @@
         <v>0</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>63.86</v>
+        <v>113.53</v>
       </c>
       <c r="I30" s="2">
         <f>IF(H30&lt;&gt;"",E30-H30,"")</f>
@@ -25678,7 +25678,7 @@
         <v>0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>59.66</v>
+        <v>106.07</v>
       </c>
       <c r="I31" s="2">
         <f>IF(H31&lt;&gt;"",E31-H31,"")</f>
@@ -25715,7 +25715,7 @@
         <v>0</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>55.8</v>
+        <v>99.2</v>
       </c>
       <c r="I32" s="2">
         <f>IF(H32&lt;&gt;"",E32-H32,"")</f>
@@ -25752,7 +25752,7 @@
         <v>0</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>54.19</v>
+        <v>96.33</v>
       </c>
       <c r="I33" s="2">
         <f>IF(H33&lt;&gt;"",E33-H33,"")</f>
@@ -25789,7 +25789,7 @@
         <v>0</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>52.57</v>
+        <v>93.47</v>
       </c>
       <c r="I34" s="2">
         <f>IF(H34&lt;&gt;"",E34-H34,"")</f>
@@ -25826,7 +25826,7 @@
         <v>0</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>52.57</v>
+        <v>93.47</v>
       </c>
       <c r="I35" s="2">
         <f>IF(H35&lt;&gt;"",E35-H35,"")</f>
@@ -25863,7 +25863,7 @@
         <v>0</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>50.96</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="I36" s="2">
         <f>IF(H36&lt;&gt;"",E36-H36,"")</f>
@@ -25900,7 +25900,7 @@
         <v>0</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>49.99</v>
+        <v>88.87</v>
       </c>
       <c r="I37" s="2">
         <f>IF(H37&lt;&gt;"",E37-H37,"")</f>
@@ -25937,7 +25937,7 @@
         <v>0</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>49.35</v>
+        <v>87.73</v>
       </c>
       <c r="I38" s="2">
         <f>IF(H38&lt;&gt;"",E38-H38,"")</f>
@@ -25974,7 +25974,7 @@
         <v>0</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>48.15</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="I39" s="2">
         <f>IF(H39&lt;&gt;"",E39-H39,"")</f>
@@ -26011,7 +26011,7 @@
         <v>0</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>47.74</v>
+        <v>84.87</v>
       </c>
       <c r="I40" s="2">
         <f>IF(H40&lt;&gt;"",E40-H40,"")</f>
@@ -26048,7 +26048,7 @@
         <v>0</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>46.12</v>
+        <v>82</v>
       </c>
       <c r="I41" s="2">
         <f>IF(H41&lt;&gt;"",E41-H41,"")</f>
@@ -26085,7 +26085,7 @@
         <v>0</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>39.67</v>
+        <v>70.53</v>
       </c>
       <c r="I42" s="2">
         <f>IF(H42&lt;&gt;"",E42-H42,"")</f>
@@ -26122,7 +26122,7 @@
         <v>0</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>39.67</v>
+        <v>70.53</v>
       </c>
       <c r="I43" s="2">
         <f>IF(H43&lt;&gt;"",E43-H43,"")</f>
@@ -26159,7 +26159,7 @@
         <v>0</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>39.67</v>
+        <v>70.53</v>
       </c>
       <c r="I44" s="2">
         <f>IF(H44&lt;&gt;"",E44-H44,"")</f>
@@ -26196,7 +26196,7 @@
         <v>0</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>38.06</v>
+        <v>67.67</v>
       </c>
       <c r="I45" s="2">
         <f>IF(H45&lt;&gt;"",E45-H45,"")</f>
@@ -26233,7 +26233,7 @@
         <v>0</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>36.34</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="I46" s="2">
         <f>IF(H46&lt;&gt;"",E46-H46,"")</f>
@@ -26270,7 +26270,7 @@
         <v>0</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>35.44</v>
+        <v>63</v>
       </c>
       <c r="I47" s="2">
         <f>IF(H47&lt;&gt;"",E47-H47,"")</f>
@@ -26307,7 +26307,7 @@
         <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>33.97</v>
+        <v>60.4</v>
       </c>
       <c r="I48" s="2">
         <f>IF(H48&lt;&gt;"",E48-H48,"")</f>
@@ -26344,7 +26344,7 @@
         <v>0</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>33.19</v>
+        <v>59</v>
       </c>
       <c r="I49" s="2">
         <f>IF(H49&lt;&gt;"",E49-H49,"")</f>
@@ -26381,7 +26381,7 @@
         <v>0</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>33.19</v>
+        <v>59</v>
       </c>
       <c r="I50" s="2">
         <f>IF(H50&lt;&gt;"",E50-H50,"")</f>
@@ -26418,7 +26418,7 @@
         <v>0</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>32.4</v>
+        <v>57.6</v>
       </c>
       <c r="I51" s="2">
         <f>IF(H51&lt;&gt;"",E51-H51,"")</f>
@@ -26455,7 +26455,7 @@
         <v>0</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>30.04</v>
+        <v>53.4</v>
       </c>
       <c r="I52" s="2">
         <f>IF(H52&lt;&gt;"",E52-H52,"")</f>
@@ -26492,7 +26492,7 @@
         <v>0</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>30.04</v>
+        <v>53.4</v>
       </c>
       <c r="I53" s="2">
         <f>IF(H53&lt;&gt;"",E53-H53,"")</f>
@@ -26529,7 +26529,7 @@
         <v>0</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>26.89</v>
+        <v>47.8</v>
       </c>
       <c r="I54" s="2">
         <f>IF(H54&lt;&gt;"",E54-H54,"")</f>
@@ -26566,7 +26566,7 @@
         <v>0</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>26.1</v>
+        <v>46.4</v>
       </c>
       <c r="I55" s="2">
         <f>IF(H55&lt;&gt;"",E55-H55,"")</f>
@@ -26603,7 +26603,7 @@
         <v>0</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>25.31</v>
+        <v>45</v>
       </c>
       <c r="I56" s="2">
         <f>IF(H56&lt;&gt;"",E56-H56,"")</f>
@@ -26640,7 +26640,7 @@
         <v>0</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>24.53</v>
+        <v>43.6</v>
       </c>
       <c r="I57" s="2">
         <f>IF(H57&lt;&gt;"",E57-H57,"")</f>
@@ -26677,7 +26677,7 @@
         <v>0</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>24.41</v>
+        <v>43.4</v>
       </c>
       <c r="I58" s="2">
         <f>IF(H58&lt;&gt;"",E58-H58,"")</f>
@@ -26714,7 +26714,7 @@
         <v>0</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>23.74</v>
+        <v>42.2</v>
       </c>
       <c r="I59" s="2">
         <f>IF(H59&lt;&gt;"",E59-H59,"")</f>
@@ -26751,7 +26751,7 @@
         <v>0</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>22.16</v>
+        <v>39.4</v>
       </c>
       <c r="I60" s="2">
         <f>IF(H60&lt;&gt;"",E60-H60,"")</f>
@@ -26788,7 +26788,7 @@
         <v>0</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>22.16</v>
+        <v>39.4</v>
       </c>
       <c r="I61" s="2">
         <f>IF(H61&lt;&gt;"",E61-H61,"")</f>
@@ -26825,7 +26825,7 @@
         <v>0</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>20.59</v>
+        <v>36.6</v>
       </c>
       <c r="I62" s="2">
         <f>IF(H62&lt;&gt;"",E62-H62,"")</f>
@@ -26862,7 +26862,7 @@
         <v>0</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>20.59</v>
+        <v>36.6</v>
       </c>
       <c r="I63" s="2">
         <f>IF(H63&lt;&gt;"",E63-H63,"")</f>
@@ -26899,7 +26899,7 @@
         <v>0</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>18.23</v>
+        <v>32.4</v>
       </c>
       <c r="I64" s="2">
         <f>IF(H64&lt;&gt;"",E64-H64,"")</f>
@@ -26936,7 +26936,7 @@
         <v>0</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>18.23</v>
+        <v>32.4</v>
       </c>
       <c r="I65" s="2">
         <f>IF(H65&lt;&gt;"",E65-H65,"")</f>
@@ -26973,7 +26973,7 @@
         <v>0</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>15.08</v>
+        <v>26.8</v>
       </c>
       <c r="I66" s="2">
         <f>IF(H66&lt;&gt;"",E66-H66,"")</f>
@@ -27010,7 +27010,7 @@
         <v>0</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>14.29</v>
+        <v>25.4</v>
       </c>
       <c r="I67" s="2">
         <f>IF(H67&lt;&gt;"",E67-H67,"")</f>
@@ -27047,7 +27047,7 @@
         <v>0</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>13.5</v>
+        <v>24</v>
       </c>
       <c r="I68" s="2">
         <f>IF(H68&lt;&gt;"",E68-H68,"")</f>
@@ -27084,7 +27084,7 @@
         <v>0</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>13.5</v>
+        <v>24</v>
       </c>
       <c r="I69" s="2">
         <f>IF(H69&lt;&gt;"",E69-H69,"")</f>
@@ -27121,7 +27121,7 @@
         <v>0</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>12.71</v>
+        <v>22.6</v>
       </c>
       <c r="I70" s="2">
         <f>IF(H70&lt;&gt;"",E70-H70,"")</f>
@@ -27158,7 +27158,7 @@
         <v>0</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>12.6</v>
+        <v>22.4</v>
       </c>
       <c r="I71" s="2">
         <f>IF(H71&lt;&gt;"",E71-H71,"")</f>
@@ -27195,7 +27195,7 @@
         <v>0</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>11.93</v>
+        <v>21.2</v>
       </c>
       <c r="I72" s="2">
         <f>IF(H72&lt;&gt;"",E72-H72,"")</f>
@@ -27232,7 +27232,7 @@
         <v>0</v>
       </c>
       <c r="H73" s="3" t="n">
-        <v>11.14</v>
+        <v>19.8</v>
       </c>
       <c r="I73" s="2">
         <f>IF(H73&lt;&gt;"",E73-H73,"")</f>
@@ -27269,7 +27269,7 @@
         <v>0</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>11.14</v>
+        <v>19.8</v>
       </c>
       <c r="I74" s="2">
         <f>IF(H74&lt;&gt;"",E74-H74,"")</f>
@@ -27306,7 +27306,7 @@
         <v>0</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>10.35</v>
+        <v>18.4</v>
       </c>
       <c r="I75" s="2">
         <f>IF(H75&lt;&gt;"",E75-H75,"")</f>
@@ -27343,7 +27343,7 @@
         <v>0</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>9.56</v>
+        <v>17</v>
       </c>
       <c r="I76" s="2">
         <f>IF(H76&lt;&gt;"",E76-H76,"")</f>
@@ -27380,7 +27380,7 @@
         <v>0</v>
       </c>
       <c r="H77" s="3" t="n">
-        <v>8.77</v>
+        <v>15.6</v>
       </c>
       <c r="I77" s="2">
         <f>IF(H77&lt;&gt;"",E77-H77,"")</f>
@@ -27417,7 +27417,7 @@
         <v>0</v>
       </c>
       <c r="H78" s="3" t="n">
-        <v>7.99</v>
+        <v>14.2</v>
       </c>
       <c r="I78" s="2">
         <f>IF(H78&lt;&gt;"",E78-H78,"")</f>
@@ -27454,7 +27454,7 @@
         <v>0</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>7.2</v>
+        <v>12.8</v>
       </c>
       <c r="I79" s="2">
         <f>IF(H79&lt;&gt;"",E79-H79,"")</f>
@@ -27491,7 +27491,7 @@
         <v>0</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>6.41</v>
+        <v>11.4</v>
       </c>
       <c r="I80" s="2">
         <f>IF(H80&lt;&gt;"",E80-H80,"")</f>
@@ -27528,7 +27528,7 @@
         <v>0</v>
       </c>
       <c r="H81" s="3" t="n">
-        <v>6.41</v>
+        <v>11.4</v>
       </c>
       <c r="I81" s="2">
         <f>IF(H81&lt;&gt;"",E81-H81,"")</f>
@@ -27565,7 +27565,7 @@
         <v>0</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>6.41</v>
+        <v>11.4</v>
       </c>
       <c r="I82" s="2">
         <f>IF(H82&lt;&gt;"",E82-H82,"")</f>
@@ -27602,7 +27602,7 @@
         <v>0</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>5.62</v>
+        <v>10</v>
       </c>
       <c r="I83" s="2">
         <f>IF(H83&lt;&gt;"",E83-H83,"")</f>
@@ -27639,7 +27639,7 @@
         <v>0</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>5.62</v>
+        <v>10</v>
       </c>
       <c r="I84" s="2">
         <f>IF(H84&lt;&gt;"",E84-H84,"")</f>
@@ -27676,7 +27676,7 @@
         <v>0</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>4.05</v>
+        <v>7.2</v>
       </c>
       <c r="I85" s="2">
         <f>IF(H85&lt;&gt;"",E85-H85,"")</f>
@@ -27713,7 +27713,7 @@
         <v>0</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>4.05</v>
+        <v>7.2</v>
       </c>
       <c r="I86" s="2">
         <f>IF(H86&lt;&gt;"",E86-H86,"")</f>
@@ -27750,7 +27750,7 @@
         <v>0</v>
       </c>
       <c r="H87" s="3" t="n">
-        <v>4.05</v>
+        <v>7.2</v>
       </c>
       <c r="I87" s="2">
         <f>IF(H87&lt;&gt;"",E87-H87,"")</f>
@@ -27787,7 +27787,7 @@
         <v>0</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>4.05</v>
+        <v>7.2</v>
       </c>
       <c r="I88" s="2">
         <f>IF(H88&lt;&gt;"",E88-H88,"")</f>
@@ -27824,7 +27824,7 @@
         <v>0</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>4.05</v>
+        <v>7.2</v>
       </c>
       <c r="I89" s="2">
         <f>IF(H89&lt;&gt;"",E89-H89,"")</f>
@@ -27861,7 +27861,7 @@
         <v>0</v>
       </c>
       <c r="H90" s="3" t="n">
-        <v>4.05</v>
+        <v>7.2</v>
       </c>
       <c r="I90" s="2">
         <f>IF(H90&lt;&gt;"",E90-H90,"")</f>
@@ -27898,7 +27898,7 @@
         <v>0</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>2.48</v>
+        <v>4.4</v>
       </c>
       <c r="I91" s="2">
         <f>IF(H91&lt;&gt;"",E91-H91,"")</f>
@@ -27935,7 +27935,7 @@
         <v>0</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>2.48</v>
+        <v>4.4</v>
       </c>
       <c r="I92" s="2">
         <f>IF(H92&lt;&gt;"",E92-H92,"")</f>
@@ -27972,7 +27972,7 @@
         <v>0</v>
       </c>
       <c r="H93" s="3" t="n">
-        <v>1.69</v>
+        <v>3</v>
       </c>
       <c r="I93" s="2">
         <f>IF(H93&lt;&gt;"",E93-H93,"")</f>
@@ -28009,7 +28009,7 @@
         <v>0</v>
       </c>
       <c r="H94" s="3" t="n">
-        <v>1.69</v>
+        <v>3</v>
       </c>
       <c r="I94" s="2">
         <f>IF(H94&lt;&gt;"",E94-H94,"")</f>
@@ -28020,6 +28020,7 @@
         <v/>
       </c>
     </row>
+    <row r="95"/>
     <row r="96">
       <c r="D96" s="1" t="inlineStr">
         <is>
